--- a/report/Linh kiện .xlsx
+++ b/report/Linh kiện .xlsx
@@ -1,14 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1.Projects\Egg_incubator_project\report\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EA57FCB-99F0-4537-872E-0808BF0F581E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Trang tính1" sheetId="1" r:id="rId4"/>
+    <sheet name="Trang tính1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Trang tính1'!$B$1:$F$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Trang tính1'!$B$1:$F$29</definedName>
   </definedNames>
-  <calcPr/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -114,28 +140,29 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$đ-42A]_-;\-* #,##0.00\ [$đ-42A]_-;_-* &quot;-&quot;??\ [$đ-42A]_-;_-@"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="13.0"/>
+      <sz val="13"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
     </font>
     <font>
-      <sz val="13.0"/>
+      <sz val="13"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -146,11 +173,17 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="2">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -164,49 +197,51 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="11">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
@@ -217,11 +252,17 @@
     <xdr:ext cx="3162300" cy="3629025"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.jpg" title="Hình ảnh"/>
+        <xdr:cNvPr id="2" name="image1.jpg" title="Hình ảnh">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -239,7 +280,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -429,24 +470,27 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:AB990"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="50.25"/>
-    <col customWidth="1" min="3" max="3" width="10.88"/>
-    <col customWidth="1" min="4" max="4" width="11.75"/>
-    <col customWidth="1" min="5" max="5" width="13.63"/>
-    <col customWidth="1" min="6" max="6" width="11.63"/>
+    <col min="2" max="2" width="57.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" customWidth="1"/>
+    <col min="6" max="6" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -486,19 +530,19 @@
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="4">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D2" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="5">
-        <f t="shared" ref="E2:E27" si="1">C2*D2</f>
+        <f t="shared" ref="E2:E27" si="0">C2*D2</f>
         <v>1</v>
       </c>
       <c r="F2" s="6"/>
@@ -525,19 +569,19 @@
       <c r="AA2" s="1"/>
       <c r="AB2" s="1"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="8" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="4">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E3" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="F3" s="6"/>
@@ -564,19 +608,19 @@
       <c r="AA3" s="7"/>
       <c r="AB3" s="7"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="4">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D4" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="F4" s="9"/>
@@ -603,19 +647,19 @@
       <c r="AA4" s="1"/>
       <c r="AB4" s="1"/>
     </row>
-    <row r="5">
+    <row r="5" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C5" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D5" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="F5" s="6"/>
@@ -642,19 +686,19 @@
       <c r="AA5" s="1"/>
       <c r="AB5" s="1"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D6" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="F6" s="6"/>
@@ -681,19 +725,19 @@
       <c r="AA6" s="1"/>
       <c r="AB6" s="1"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C7" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D7" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="F7" s="6"/>
@@ -720,19 +764,19 @@
       <c r="AA7" s="1"/>
       <c r="AB7" s="1"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C8" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D8" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="F8" s="6"/>
@@ -759,19 +803,19 @@
       <c r="AA8" s="1"/>
       <c r="AB8" s="1"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="8" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D9" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="F9" s="6"/>
@@ -798,19 +842,19 @@
       <c r="AA9" s="1"/>
       <c r="AB9" s="1"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C10" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D10" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="F10" s="6"/>
@@ -837,19 +881,19 @@
       <c r="AA10" s="1"/>
       <c r="AB10" s="1"/>
     </row>
-    <row r="11">
+    <row r="11" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C11" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D11" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E11" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="F11" s="6"/>
@@ -876,19 +920,19 @@
       <c r="AA11" s="1"/>
       <c r="AB11" s="1"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="8" t="s">
         <v>15</v>
       </c>
       <c r="C12" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D12" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="F12" s="6"/>
@@ -915,19 +959,19 @@
       <c r="AA12" s="1"/>
       <c r="AB12" s="1"/>
     </row>
-    <row r="13">
+    <row r="13" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="8" t="s">
         <v>16</v>
       </c>
       <c r="C13" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D13" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E13" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="F13" s="6"/>
@@ -954,19 +998,19 @@
       <c r="AA13" s="1"/>
       <c r="AB13" s="1"/>
     </row>
-    <row r="14">
+    <row r="14" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="8" t="s">
         <v>17</v>
       </c>
       <c r="C14" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D14" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E14" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="F14" s="6"/>
@@ -993,19 +1037,19 @@
       <c r="AA14" s="1"/>
       <c r="AB14" s="1"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="8" t="s">
         <v>18</v>
       </c>
       <c r="C15" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D15" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E15" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="F15" s="9"/>
@@ -1032,19 +1076,19 @@
       <c r="AA15" s="1"/>
       <c r="AB15" s="1"/>
     </row>
-    <row r="16">
+    <row r="16" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C16" s="4">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="D16" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="F16" s="6"/>
@@ -1071,19 +1115,19 @@
       <c r="AA16" s="1"/>
       <c r="AB16" s="1"/>
     </row>
-    <row r="17">
+    <row r="17" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C17" s="4">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="D17" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="F17" s="6"/>
@@ -1110,19 +1154,19 @@
       <c r="AA17" s="1"/>
       <c r="AB17" s="1"/>
     </row>
-    <row r="18">
+    <row r="18" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="8" t="s">
         <v>21</v>
       </c>
       <c r="C18" s="4">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="D18" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E18" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="F18" s="6"/>
@@ -1149,19 +1193,19 @@
       <c r="AA18" s="1"/>
       <c r="AB18" s="1"/>
     </row>
-    <row r="19">
+    <row r="19" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C19" s="4">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="D19" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="F19" s="6"/>
@@ -1188,19 +1232,19 @@
       <c r="AA19" s="1"/>
       <c r="AB19" s="1"/>
     </row>
-    <row r="20">
+    <row r="20" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="8" t="s">
         <v>23</v>
       </c>
       <c r="C20" s="4">
-        <v>63.0</v>
+        <v>63</v>
       </c>
       <c r="D20" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E20" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>126</v>
       </c>
       <c r="F20" s="6"/>
@@ -1227,19 +1271,19 @@
       <c r="AA20" s="1"/>
       <c r="AB20" s="1"/>
     </row>
-    <row r="21">
+    <row r="21" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="8" t="s">
         <v>24</v>
       </c>
       <c r="C21" s="4">
-        <v>89.0</v>
+        <v>89</v>
       </c>
       <c r="D21" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E21" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>89</v>
       </c>
       <c r="F21" s="6"/>
@@ -1266,19 +1310,19 @@
       <c r="AA21" s="1"/>
       <c r="AB21" s="1"/>
     </row>
-    <row r="22">
+    <row r="22" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="8" t="s">
         <v>25</v>
       </c>
       <c r="C22" s="4">
-        <v>40.0</v>
+        <v>40</v>
       </c>
       <c r="D22" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E22" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>80</v>
       </c>
       <c r="F22" s="9"/>
@@ -1305,23 +1349,23 @@
       <c r="AA22" s="1"/>
       <c r="AB22" s="1"/>
     </row>
-    <row r="23">
+    <row r="23" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C23" s="4">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="D23" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="F23" s="6"/>
     </row>
-    <row r="24">
+    <row r="24" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="3" t="s">
         <v>27</v>
@@ -1330,10 +1374,10 @@
         <v>2.5</v>
       </c>
       <c r="D24" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E24" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="F24" s="6"/>
@@ -1360,19 +1404,19 @@
       <c r="AA24" s="1"/>
       <c r="AB24" s="1"/>
     </row>
-    <row r="25">
+    <row r="25" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C25" s="4">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="D25" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E25" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="F25" s="6"/>
@@ -1399,19 +1443,19 @@
       <c r="AA25" s="1"/>
       <c r="AB25" s="1"/>
     </row>
-    <row r="26">
+    <row r="26" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="8" t="s">
         <v>29</v>
       </c>
       <c r="C26" s="4">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="D26" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E26" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="F26" s="6"/>
@@ -1438,7 +1482,7 @@
       <c r="AA26" s="1"/>
       <c r="AB26" s="1"/>
     </row>
-    <row r="27">
+    <row r="27" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="8" t="s">
         <v>30</v>
@@ -1447,10 +1491,10 @@
         <v>1.5</v>
       </c>
       <c r="D27" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E27" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.5</v>
       </c>
       <c r="F27" s="6"/>
@@ -1477,7 +1521,7 @@
       <c r="AA27" s="1"/>
       <c r="AB27" s="1"/>
     </row>
-    <row r="28">
+    <row r="28" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="7"/>
@@ -1510,7 +1554,7 @@
       <c r="AA28" s="1"/>
       <c r="AB28" s="1"/>
     </row>
-    <row r="29">
+    <row r="29" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="10" t="s">
         <v>31</v>
@@ -1519,7 +1563,7 @@
       <c r="D29" s="7"/>
       <c r="E29" s="5">
         <f>E28/5-50</f>
-        <v>29.1</v>
+        <v>29.099999999999994</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
@@ -1545,7 +1589,7 @@
       <c r="AA29" s="1"/>
       <c r="AB29" s="1"/>
     </row>
-    <row r="30">
+    <row r="30" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="7"/>
@@ -1575,7 +1619,7 @@
       <c r="AA30" s="1"/>
       <c r="AB30" s="1"/>
     </row>
-    <row r="31">
+    <row r="31" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="7"/>
@@ -1605,7 +1649,7 @@
       <c r="AA31" s="1"/>
       <c r="AB31" s="1"/>
     </row>
-    <row r="32">
+    <row r="32" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="7"/>
@@ -1635,7 +1679,7 @@
       <c r="AA32" s="1"/>
       <c r="AB32" s="1"/>
     </row>
-    <row r="33">
+    <row r="33" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="7"/>
@@ -1665,7 +1709,7 @@
       <c r="AA33" s="1"/>
       <c r="AB33" s="1"/>
     </row>
-    <row r="34">
+    <row r="34" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="7"/>
@@ -1695,7 +1739,7 @@
       <c r="AA34" s="1"/>
       <c r="AB34" s="1"/>
     </row>
-    <row r="35">
+    <row r="35" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="7"/>
@@ -1725,7 +1769,7 @@
       <c r="AA35" s="1"/>
       <c r="AB35" s="1"/>
     </row>
-    <row r="36">
+    <row r="36" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="7"/>
@@ -1755,7 +1799,7 @@
       <c r="AA36" s="1"/>
       <c r="AB36" s="1"/>
     </row>
-    <row r="37">
+    <row r="37" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="7"/>
@@ -1785,7 +1829,7 @@
       <c r="AA37" s="1"/>
       <c r="AB37" s="1"/>
     </row>
-    <row r="38">
+    <row r="38" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="7"/>
@@ -1815,7 +1859,7 @@
       <c r="AA38" s="1"/>
       <c r="AB38" s="1"/>
     </row>
-    <row r="39">
+    <row r="39" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="7"/>
@@ -1845,7 +1889,7 @@
       <c r="AA39" s="1"/>
       <c r="AB39" s="1"/>
     </row>
-    <row r="40">
+    <row r="40" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="7"/>
@@ -1875,7 +1919,7 @@
       <c r="AA40" s="1"/>
       <c r="AB40" s="1"/>
     </row>
-    <row r="41">
+    <row r="41" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="7"/>
@@ -1905,7 +1949,7 @@
       <c r="AA41" s="1"/>
       <c r="AB41" s="1"/>
     </row>
-    <row r="42">
+    <row r="42" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="7"/>
@@ -1935,7 +1979,7 @@
       <c r="AA42" s="1"/>
       <c r="AB42" s="1"/>
     </row>
-    <row r="43">
+    <row r="43" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="7"/>
@@ -1965,7 +2009,7 @@
       <c r="AA43" s="1"/>
       <c r="AB43" s="1"/>
     </row>
-    <row r="44">
+    <row r="44" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="7"/>
@@ -1995,7 +2039,7 @@
       <c r="AA44" s="1"/>
       <c r="AB44" s="1"/>
     </row>
-    <row r="45">
+    <row r="45" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="7"/>
@@ -2025,7 +2069,7 @@
       <c r="AA45" s="1"/>
       <c r="AB45" s="1"/>
     </row>
-    <row r="46">
+    <row r="46" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="7"/>
@@ -2055,7 +2099,7 @@
       <c r="AA46" s="1"/>
       <c r="AB46" s="1"/>
     </row>
-    <row r="47">
+    <row r="47" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="7"/>
@@ -2085,7 +2129,7 @@
       <c r="AA47" s="1"/>
       <c r="AB47" s="1"/>
     </row>
-    <row r="48">
+    <row r="48" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="7"/>
@@ -2115,7 +2159,7 @@
       <c r="AA48" s="1"/>
       <c r="AB48" s="1"/>
     </row>
-    <row r="49">
+    <row r="49" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="7"/>
@@ -2145,7 +2189,7 @@
       <c r="AA49" s="1"/>
       <c r="AB49" s="1"/>
     </row>
-    <row r="50">
+    <row r="50" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="7"/>
@@ -2175,7 +2219,7 @@
       <c r="AA50" s="1"/>
       <c r="AB50" s="1"/>
     </row>
-    <row r="51">
+    <row r="51" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="7"/>
@@ -2205,7 +2249,7 @@
       <c r="AA51" s="1"/>
       <c r="AB51" s="1"/>
     </row>
-    <row r="52">
+    <row r="52" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="7"/>
@@ -2235,7 +2279,7 @@
       <c r="AA52" s="1"/>
       <c r="AB52" s="1"/>
     </row>
-    <row r="53">
+    <row r="53" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="7"/>
@@ -2265,7 +2309,7 @@
       <c r="AA53" s="1"/>
       <c r="AB53" s="1"/>
     </row>
-    <row r="54">
+    <row r="54" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="7"/>
@@ -2295,7 +2339,7 @@
       <c r="AA54" s="1"/>
       <c r="AB54" s="1"/>
     </row>
-    <row r="55">
+    <row r="55" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="7"/>
@@ -2325,7 +2369,7 @@
       <c r="AA55" s="1"/>
       <c r="AB55" s="1"/>
     </row>
-    <row r="56">
+    <row r="56" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="7"/>
@@ -2355,7 +2399,7 @@
       <c r="AA56" s="1"/>
       <c r="AB56" s="1"/>
     </row>
-    <row r="57">
+    <row r="57" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="7"/>
@@ -2385,7 +2429,7 @@
       <c r="AA57" s="1"/>
       <c r="AB57" s="1"/>
     </row>
-    <row r="58">
+    <row r="58" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="7"/>
@@ -2415,7 +2459,7 @@
       <c r="AA58" s="1"/>
       <c r="AB58" s="1"/>
     </row>
-    <row r="59">
+    <row r="59" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="7"/>
@@ -2445,7 +2489,7 @@
       <c r="AA59" s="1"/>
       <c r="AB59" s="1"/>
     </row>
-    <row r="60">
+    <row r="60" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="7"/>
@@ -2475,7 +2519,7 @@
       <c r="AA60" s="1"/>
       <c r="AB60" s="1"/>
     </row>
-    <row r="61">
+    <row r="61" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="7"/>
@@ -2505,7 +2549,7 @@
       <c r="AA61" s="1"/>
       <c r="AB61" s="1"/>
     </row>
-    <row r="62">
+    <row r="62" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="7"/>
@@ -2535,7 +2579,7 @@
       <c r="AA62" s="1"/>
       <c r="AB62" s="1"/>
     </row>
-    <row r="63">
+    <row r="63" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="7"/>
@@ -2565,7 +2609,7 @@
       <c r="AA63" s="1"/>
       <c r="AB63" s="1"/>
     </row>
-    <row r="64">
+    <row r="64" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="7"/>
@@ -2595,7 +2639,7 @@
       <c r="AA64" s="1"/>
       <c r="AB64" s="1"/>
     </row>
-    <row r="65">
+    <row r="65" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="7"/>
@@ -2625,7 +2669,7 @@
       <c r="AA65" s="1"/>
       <c r="AB65" s="1"/>
     </row>
-    <row r="66">
+    <row r="66" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="7"/>
@@ -2655,7 +2699,7 @@
       <c r="AA66" s="1"/>
       <c r="AB66" s="1"/>
     </row>
-    <row r="67">
+    <row r="67" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="7"/>
@@ -2685,7 +2729,7 @@
       <c r="AA67" s="1"/>
       <c r="AB67" s="1"/>
     </row>
-    <row r="68">
+    <row r="68" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="7"/>
@@ -2715,7 +2759,7 @@
       <c r="AA68" s="1"/>
       <c r="AB68" s="1"/>
     </row>
-    <row r="69">
+    <row r="69" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="7"/>
@@ -2745,7 +2789,7 @@
       <c r="AA69" s="1"/>
       <c r="AB69" s="1"/>
     </row>
-    <row r="70">
+    <row r="70" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="7"/>
@@ -2775,7 +2819,7 @@
       <c r="AA70" s="1"/>
       <c r="AB70" s="1"/>
     </row>
-    <row r="71">
+    <row r="71" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="7"/>
@@ -2805,7 +2849,7 @@
       <c r="AA71" s="1"/>
       <c r="AB71" s="1"/>
     </row>
-    <row r="72">
+    <row r="72" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="7"/>
@@ -2835,7 +2879,7 @@
       <c r="AA72" s="1"/>
       <c r="AB72" s="1"/>
     </row>
-    <row r="73">
+    <row r="73" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="7"/>
@@ -2865,7 +2909,7 @@
       <c r="AA73" s="1"/>
       <c r="AB73" s="1"/>
     </row>
-    <row r="74">
+    <row r="74" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="7"/>
@@ -2895,7 +2939,7 @@
       <c r="AA74" s="1"/>
       <c r="AB74" s="1"/>
     </row>
-    <row r="75">
+    <row r="75" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="7"/>
@@ -2925,7 +2969,7 @@
       <c r="AA75" s="1"/>
       <c r="AB75" s="1"/>
     </row>
-    <row r="76">
+    <row r="76" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="7"/>
@@ -2955,7 +2999,7 @@
       <c r="AA76" s="1"/>
       <c r="AB76" s="1"/>
     </row>
-    <row r="77">
+    <row r="77" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="7"/>
@@ -2985,7 +3029,7 @@
       <c r="AA77" s="1"/>
       <c r="AB77" s="1"/>
     </row>
-    <row r="78">
+    <row r="78" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="7"/>
@@ -3015,7 +3059,7 @@
       <c r="AA78" s="1"/>
       <c r="AB78" s="1"/>
     </row>
-    <row r="79">
+    <row r="79" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="7"/>
@@ -3045,7 +3089,7 @@
       <c r="AA79" s="1"/>
       <c r="AB79" s="1"/>
     </row>
-    <row r="80">
+    <row r="80" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="7"/>
@@ -3075,7 +3119,7 @@
       <c r="AA80" s="1"/>
       <c r="AB80" s="1"/>
     </row>
-    <row r="81">
+    <row r="81" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="7"/>
@@ -3105,7 +3149,7 @@
       <c r="AA81" s="1"/>
       <c r="AB81" s="1"/>
     </row>
-    <row r="82">
+    <row r="82" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="7"/>
@@ -3135,7 +3179,7 @@
       <c r="AA82" s="1"/>
       <c r="AB82" s="1"/>
     </row>
-    <row r="83">
+    <row r="83" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="7"/>
@@ -3165,7 +3209,7 @@
       <c r="AA83" s="1"/>
       <c r="AB83" s="1"/>
     </row>
-    <row r="84">
+    <row r="84" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="7"/>
@@ -3195,7 +3239,7 @@
       <c r="AA84" s="1"/>
       <c r="AB84" s="1"/>
     </row>
-    <row r="85">
+    <row r="85" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="7"/>
@@ -3225,7 +3269,7 @@
       <c r="AA85" s="1"/>
       <c r="AB85" s="1"/>
     </row>
-    <row r="86">
+    <row r="86" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="7"/>
@@ -3255,7 +3299,7 @@
       <c r="AA86" s="1"/>
       <c r="AB86" s="1"/>
     </row>
-    <row r="87">
+    <row r="87" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="7"/>
@@ -3285,7 +3329,7 @@
       <c r="AA87" s="1"/>
       <c r="AB87" s="1"/>
     </row>
-    <row r="88">
+    <row r="88" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="7"/>
@@ -3315,7 +3359,7 @@
       <c r="AA88" s="1"/>
       <c r="AB88" s="1"/>
     </row>
-    <row r="89">
+    <row r="89" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="7"/>
@@ -3345,7 +3389,7 @@
       <c r="AA89" s="1"/>
       <c r="AB89" s="1"/>
     </row>
-    <row r="90">
+    <row r="90" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="7"/>
@@ -3375,7 +3419,7 @@
       <c r="AA90" s="1"/>
       <c r="AB90" s="1"/>
     </row>
-    <row r="91">
+    <row r="91" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="7"/>
@@ -3405,7 +3449,7 @@
       <c r="AA91" s="1"/>
       <c r="AB91" s="1"/>
     </row>
-    <row r="92">
+    <row r="92" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="7"/>
@@ -3435,7 +3479,7 @@
       <c r="AA92" s="1"/>
       <c r="AB92" s="1"/>
     </row>
-    <row r="93">
+    <row r="93" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="7"/>
@@ -3465,7 +3509,7 @@
       <c r="AA93" s="1"/>
       <c r="AB93" s="1"/>
     </row>
-    <row r="94">
+    <row r="94" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="7"/>
@@ -3495,7 +3539,7 @@
       <c r="AA94" s="1"/>
       <c r="AB94" s="1"/>
     </row>
-    <row r="95">
+    <row r="95" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="7"/>
@@ -3525,7 +3569,7 @@
       <c r="AA95" s="1"/>
       <c r="AB95" s="1"/>
     </row>
-    <row r="96">
+    <row r="96" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="7"/>
@@ -3555,7 +3599,7 @@
       <c r="AA96" s="1"/>
       <c r="AB96" s="1"/>
     </row>
-    <row r="97">
+    <row r="97" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="7"/>
@@ -3585,7 +3629,7 @@
       <c r="AA97" s="1"/>
       <c r="AB97" s="1"/>
     </row>
-    <row r="98">
+    <row r="98" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="7"/>
@@ -3615,7 +3659,7 @@
       <c r="AA98" s="1"/>
       <c r="AB98" s="1"/>
     </row>
-    <row r="99">
+    <row r="99" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="7"/>
@@ -3645,7 +3689,7 @@
       <c r="AA99" s="1"/>
       <c r="AB99" s="1"/>
     </row>
-    <row r="100">
+    <row r="100" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="7"/>
@@ -3675,7 +3719,7 @@
       <c r="AA100" s="1"/>
       <c r="AB100" s="1"/>
     </row>
-    <row r="101">
+    <row r="101" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="7"/>
@@ -3705,7 +3749,7 @@
       <c r="AA101" s="1"/>
       <c r="AB101" s="1"/>
     </row>
-    <row r="102">
+    <row r="102" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="7"/>
@@ -3735,7 +3779,7 @@
       <c r="AA102" s="1"/>
       <c r="AB102" s="1"/>
     </row>
-    <row r="103">
+    <row r="103" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="7"/>
@@ -3765,7 +3809,7 @@
       <c r="AA103" s="1"/>
       <c r="AB103" s="1"/>
     </row>
-    <row r="104">
+    <row r="104" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="7"/>
@@ -3795,7 +3839,7 @@
       <c r="AA104" s="1"/>
       <c r="AB104" s="1"/>
     </row>
-    <row r="105">
+    <row r="105" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="7"/>
@@ -3825,7 +3869,7 @@
       <c r="AA105" s="1"/>
       <c r="AB105" s="1"/>
     </row>
-    <row r="106">
+    <row r="106" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="7"/>
@@ -3855,7 +3899,7 @@
       <c r="AA106" s="1"/>
       <c r="AB106" s="1"/>
     </row>
-    <row r="107">
+    <row r="107" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="7"/>
@@ -3885,7 +3929,7 @@
       <c r="AA107" s="1"/>
       <c r="AB107" s="1"/>
     </row>
-    <row r="108">
+    <row r="108" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="7"/>
@@ -3915,7 +3959,7 @@
       <c r="AA108" s="1"/>
       <c r="AB108" s="1"/>
     </row>
-    <row r="109">
+    <row r="109" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="7"/>
@@ -3945,7 +3989,7 @@
       <c r="AA109" s="1"/>
       <c r="AB109" s="1"/>
     </row>
-    <row r="110">
+    <row r="110" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="7"/>
@@ -3975,7 +4019,7 @@
       <c r="AA110" s="1"/>
       <c r="AB110" s="1"/>
     </row>
-    <row r="111">
+    <row r="111" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="7"/>
@@ -4005,7 +4049,7 @@
       <c r="AA111" s="1"/>
       <c r="AB111" s="1"/>
     </row>
-    <row r="112">
+    <row r="112" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="7"/>
@@ -4035,7 +4079,7 @@
       <c r="AA112" s="1"/>
       <c r="AB112" s="1"/>
     </row>
-    <row r="113">
+    <row r="113" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="7"/>
@@ -4065,7 +4109,7 @@
       <c r="AA113" s="1"/>
       <c r="AB113" s="1"/>
     </row>
-    <row r="114">
+    <row r="114" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="7"/>
@@ -4095,7 +4139,7 @@
       <c r="AA114" s="1"/>
       <c r="AB114" s="1"/>
     </row>
-    <row r="115">
+    <row r="115" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="7"/>
@@ -4125,7 +4169,7 @@
       <c r="AA115" s="1"/>
       <c r="AB115" s="1"/>
     </row>
-    <row r="116">
+    <row r="116" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="7"/>
@@ -4155,7 +4199,7 @@
       <c r="AA116" s="1"/>
       <c r="AB116" s="1"/>
     </row>
-    <row r="117">
+    <row r="117" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="7"/>
@@ -4185,7 +4229,7 @@
       <c r="AA117" s="1"/>
       <c r="AB117" s="1"/>
     </row>
-    <row r="118">
+    <row r="118" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="7"/>
@@ -4215,7 +4259,7 @@
       <c r="AA118" s="1"/>
       <c r="AB118" s="1"/>
     </row>
-    <row r="119">
+    <row r="119" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="7"/>
@@ -4245,7 +4289,7 @@
       <c r="AA119" s="1"/>
       <c r="AB119" s="1"/>
     </row>
-    <row r="120">
+    <row r="120" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="7"/>
@@ -4275,7 +4319,7 @@
       <c r="AA120" s="1"/>
       <c r="AB120" s="1"/>
     </row>
-    <row r="121">
+    <row r="121" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="7"/>
@@ -4305,7 +4349,7 @@
       <c r="AA121" s="1"/>
       <c r="AB121" s="1"/>
     </row>
-    <row r="122">
+    <row r="122" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="7"/>
@@ -4335,7 +4379,7 @@
       <c r="AA122" s="1"/>
       <c r="AB122" s="1"/>
     </row>
-    <row r="123">
+    <row r="123" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="7"/>
@@ -4365,7 +4409,7 @@
       <c r="AA123" s="1"/>
       <c r="AB123" s="1"/>
     </row>
-    <row r="124">
+    <row r="124" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="7"/>
@@ -4395,7 +4439,7 @@
       <c r="AA124" s="1"/>
       <c r="AB124" s="1"/>
     </row>
-    <row r="125">
+    <row r="125" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="7"/>
@@ -4425,7 +4469,7 @@
       <c r="AA125" s="1"/>
       <c r="AB125" s="1"/>
     </row>
-    <row r="126">
+    <row r="126" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="7"/>
@@ -4455,7 +4499,7 @@
       <c r="AA126" s="1"/>
       <c r="AB126" s="1"/>
     </row>
-    <row r="127">
+    <row r="127" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="7"/>
@@ -4485,7 +4529,7 @@
       <c r="AA127" s="1"/>
       <c r="AB127" s="1"/>
     </row>
-    <row r="128">
+    <row r="128" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="7"/>
@@ -4515,7 +4559,7 @@
       <c r="AA128" s="1"/>
       <c r="AB128" s="1"/>
     </row>
-    <row r="129">
+    <row r="129" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="7"/>
@@ -4545,7 +4589,7 @@
       <c r="AA129" s="1"/>
       <c r="AB129" s="1"/>
     </row>
-    <row r="130">
+    <row r="130" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="7"/>
@@ -4575,7 +4619,7 @@
       <c r="AA130" s="1"/>
       <c r="AB130" s="1"/>
     </row>
-    <row r="131">
+    <row r="131" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="7"/>
@@ -4605,7 +4649,7 @@
       <c r="AA131" s="1"/>
       <c r="AB131" s="1"/>
     </row>
-    <row r="132">
+    <row r="132" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="7"/>
@@ -4635,7 +4679,7 @@
       <c r="AA132" s="1"/>
       <c r="AB132" s="1"/>
     </row>
-    <row r="133">
+    <row r="133" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="7"/>
@@ -4665,7 +4709,7 @@
       <c r="AA133" s="1"/>
       <c r="AB133" s="1"/>
     </row>
-    <row r="134">
+    <row r="134" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="7"/>
@@ -4695,7 +4739,7 @@
       <c r="AA134" s="1"/>
       <c r="AB134" s="1"/>
     </row>
-    <row r="135">
+    <row r="135" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="7"/>
@@ -4725,7 +4769,7 @@
       <c r="AA135" s="1"/>
       <c r="AB135" s="1"/>
     </row>
-    <row r="136">
+    <row r="136" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="7"/>
@@ -4755,7 +4799,7 @@
       <c r="AA136" s="1"/>
       <c r="AB136" s="1"/>
     </row>
-    <row r="137">
+    <row r="137" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="7"/>
@@ -4785,7 +4829,7 @@
       <c r="AA137" s="1"/>
       <c r="AB137" s="1"/>
     </row>
-    <row r="138">
+    <row r="138" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="7"/>
@@ -4815,7 +4859,7 @@
       <c r="AA138" s="1"/>
       <c r="AB138" s="1"/>
     </row>
-    <row r="139">
+    <row r="139" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="7"/>
@@ -4845,7 +4889,7 @@
       <c r="AA139" s="1"/>
       <c r="AB139" s="1"/>
     </row>
-    <row r="140">
+    <row r="140" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="7"/>
@@ -4875,7 +4919,7 @@
       <c r="AA140" s="1"/>
       <c r="AB140" s="1"/>
     </row>
-    <row r="141">
+    <row r="141" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="7"/>
@@ -4905,7 +4949,7 @@
       <c r="AA141" s="1"/>
       <c r="AB141" s="1"/>
     </row>
-    <row r="142">
+    <row r="142" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="7"/>
@@ -4935,7 +4979,7 @@
       <c r="AA142" s="1"/>
       <c r="AB142" s="1"/>
     </row>
-    <row r="143">
+    <row r="143" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="7"/>
@@ -4965,7 +5009,7 @@
       <c r="AA143" s="1"/>
       <c r="AB143" s="1"/>
     </row>
-    <row r="144">
+    <row r="144" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="7"/>
@@ -4995,7 +5039,7 @@
       <c r="AA144" s="1"/>
       <c r="AB144" s="1"/>
     </row>
-    <row r="145">
+    <row r="145" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="7"/>
@@ -5025,7 +5069,7 @@
       <c r="AA145" s="1"/>
       <c r="AB145" s="1"/>
     </row>
-    <row r="146">
+    <row r="146" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="7"/>
@@ -5055,7 +5099,7 @@
       <c r="AA146" s="1"/>
       <c r="AB146" s="1"/>
     </row>
-    <row r="147">
+    <row r="147" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="7"/>
@@ -5085,7 +5129,7 @@
       <c r="AA147" s="1"/>
       <c r="AB147" s="1"/>
     </row>
-    <row r="148">
+    <row r="148" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="7"/>
@@ -5115,7 +5159,7 @@
       <c r="AA148" s="1"/>
       <c r="AB148" s="1"/>
     </row>
-    <row r="149">
+    <row r="149" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="7"/>
@@ -5145,7 +5189,7 @@
       <c r="AA149" s="1"/>
       <c r="AB149" s="1"/>
     </row>
-    <row r="150">
+    <row r="150" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="7"/>
@@ -5175,7 +5219,7 @@
       <c r="AA150" s="1"/>
       <c r="AB150" s="1"/>
     </row>
-    <row r="151">
+    <row r="151" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="7"/>
@@ -5205,7 +5249,7 @@
       <c r="AA151" s="1"/>
       <c r="AB151" s="1"/>
     </row>
-    <row r="152">
+    <row r="152" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="7"/>
@@ -5235,7 +5279,7 @@
       <c r="AA152" s="1"/>
       <c r="AB152" s="1"/>
     </row>
-    <row r="153">
+    <row r="153" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="7"/>
@@ -5265,7 +5309,7 @@
       <c r="AA153" s="1"/>
       <c r="AB153" s="1"/>
     </row>
-    <row r="154">
+    <row r="154" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="7"/>
@@ -5295,7 +5339,7 @@
       <c r="AA154" s="1"/>
       <c r="AB154" s="1"/>
     </row>
-    <row r="155">
+    <row r="155" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="7"/>
@@ -5325,7 +5369,7 @@
       <c r="AA155" s="1"/>
       <c r="AB155" s="1"/>
     </row>
-    <row r="156">
+    <row r="156" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="7"/>
@@ -5355,7 +5399,7 @@
       <c r="AA156" s="1"/>
       <c r="AB156" s="1"/>
     </row>
-    <row r="157">
+    <row r="157" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="7"/>
@@ -5385,7 +5429,7 @@
       <c r="AA157" s="1"/>
       <c r="AB157" s="1"/>
     </row>
-    <row r="158">
+    <row r="158" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="7"/>
@@ -5415,7 +5459,7 @@
       <c r="AA158" s="1"/>
       <c r="AB158" s="1"/>
     </row>
-    <row r="159">
+    <row r="159" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="7"/>
@@ -5445,7 +5489,7 @@
       <c r="AA159" s="1"/>
       <c r="AB159" s="1"/>
     </row>
-    <row r="160">
+    <row r="160" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="7"/>
@@ -5475,7 +5519,7 @@
       <c r="AA160" s="1"/>
       <c r="AB160" s="1"/>
     </row>
-    <row r="161">
+    <row r="161" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="7"/>
@@ -5505,7 +5549,7 @@
       <c r="AA161" s="1"/>
       <c r="AB161" s="1"/>
     </row>
-    <row r="162">
+    <row r="162" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="7"/>
@@ -5535,7 +5579,7 @@
       <c r="AA162" s="1"/>
       <c r="AB162" s="1"/>
     </row>
-    <row r="163">
+    <row r="163" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="7"/>
@@ -5565,7 +5609,7 @@
       <c r="AA163" s="1"/>
       <c r="AB163" s="1"/>
     </row>
-    <row r="164">
+    <row r="164" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="7"/>
@@ -5595,7 +5639,7 @@
       <c r="AA164" s="1"/>
       <c r="AB164" s="1"/>
     </row>
-    <row r="165">
+    <row r="165" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="7"/>
@@ -5625,7 +5669,7 @@
       <c r="AA165" s="1"/>
       <c r="AB165" s="1"/>
     </row>
-    <row r="166">
+    <row r="166" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="7"/>
@@ -5655,7 +5699,7 @@
       <c r="AA166" s="1"/>
       <c r="AB166" s="1"/>
     </row>
-    <row r="167">
+    <row r="167" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="7"/>
@@ -5685,7 +5729,7 @@
       <c r="AA167" s="1"/>
       <c r="AB167" s="1"/>
     </row>
-    <row r="168">
+    <row r="168" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="7"/>
@@ -5715,7 +5759,7 @@
       <c r="AA168" s="1"/>
       <c r="AB168" s="1"/>
     </row>
-    <row r="169">
+    <row r="169" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="7"/>
@@ -5745,7 +5789,7 @@
       <c r="AA169" s="1"/>
       <c r="AB169" s="1"/>
     </row>
-    <row r="170">
+    <row r="170" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="7"/>
@@ -5775,7 +5819,7 @@
       <c r="AA170" s="1"/>
       <c r="AB170" s="1"/>
     </row>
-    <row r="171">
+    <row r="171" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="7"/>
@@ -5805,7 +5849,7 @@
       <c r="AA171" s="1"/>
       <c r="AB171" s="1"/>
     </row>
-    <row r="172">
+    <row r="172" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="7"/>
@@ -5835,7 +5879,7 @@
       <c r="AA172" s="1"/>
       <c r="AB172" s="1"/>
     </row>
-    <row r="173">
+    <row r="173" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="7"/>
@@ -5865,7 +5909,7 @@
       <c r="AA173" s="1"/>
       <c r="AB173" s="1"/>
     </row>
-    <row r="174">
+    <row r="174" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="7"/>
@@ -5895,7 +5939,7 @@
       <c r="AA174" s="1"/>
       <c r="AB174" s="1"/>
     </row>
-    <row r="175">
+    <row r="175" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="7"/>
@@ -5925,7 +5969,7 @@
       <c r="AA175" s="1"/>
       <c r="AB175" s="1"/>
     </row>
-    <row r="176">
+    <row r="176" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="7"/>
@@ -5955,7 +5999,7 @@
       <c r="AA176" s="1"/>
       <c r="AB176" s="1"/>
     </row>
-    <row r="177">
+    <row r="177" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="7"/>
@@ -5985,7 +6029,7 @@
       <c r="AA177" s="1"/>
       <c r="AB177" s="1"/>
     </row>
-    <row r="178">
+    <row r="178" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="7"/>
@@ -6015,7 +6059,7 @@
       <c r="AA178" s="1"/>
       <c r="AB178" s="1"/>
     </row>
-    <row r="179">
+    <row r="179" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="7"/>
@@ -6045,7 +6089,7 @@
       <c r="AA179" s="1"/>
       <c r="AB179" s="1"/>
     </row>
-    <row r="180">
+    <row r="180" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="7"/>
@@ -6075,7 +6119,7 @@
       <c r="AA180" s="1"/>
       <c r="AB180" s="1"/>
     </row>
-    <row r="181">
+    <row r="181" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="7"/>
@@ -6105,7 +6149,7 @@
       <c r="AA181" s="1"/>
       <c r="AB181" s="1"/>
     </row>
-    <row r="182">
+    <row r="182" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="7"/>
@@ -6135,7 +6179,7 @@
       <c r="AA182" s="1"/>
       <c r="AB182" s="1"/>
     </row>
-    <row r="183">
+    <row r="183" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="7"/>
@@ -6165,7 +6209,7 @@
       <c r="AA183" s="1"/>
       <c r="AB183" s="1"/>
     </row>
-    <row r="184">
+    <row r="184" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="7"/>
@@ -6195,7 +6239,7 @@
       <c r="AA184" s="1"/>
       <c r="AB184" s="1"/>
     </row>
-    <row r="185">
+    <row r="185" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="7"/>
@@ -6225,7 +6269,7 @@
       <c r="AA185" s="1"/>
       <c r="AB185" s="1"/>
     </row>
-    <row r="186">
+    <row r="186" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="7"/>
@@ -6255,7 +6299,7 @@
       <c r="AA186" s="1"/>
       <c r="AB186" s="1"/>
     </row>
-    <row r="187">
+    <row r="187" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="7"/>
@@ -6285,7 +6329,7 @@
       <c r="AA187" s="1"/>
       <c r="AB187" s="1"/>
     </row>
-    <row r="188">
+    <row r="188" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="7"/>
@@ -6315,7 +6359,7 @@
       <c r="AA188" s="1"/>
       <c r="AB188" s="1"/>
     </row>
-    <row r="189">
+    <row r="189" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="7"/>
@@ -6345,7 +6389,7 @@
       <c r="AA189" s="1"/>
       <c r="AB189" s="1"/>
     </row>
-    <row r="190">
+    <row r="190" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="7"/>
@@ -6375,7 +6419,7 @@
       <c r="AA190" s="1"/>
       <c r="AB190" s="1"/>
     </row>
-    <row r="191">
+    <row r="191" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="7"/>
@@ -6405,7 +6449,7 @@
       <c r="AA191" s="1"/>
       <c r="AB191" s="1"/>
     </row>
-    <row r="192">
+    <row r="192" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="7"/>
@@ -6435,7 +6479,7 @@
       <c r="AA192" s="1"/>
       <c r="AB192" s="1"/>
     </row>
-    <row r="193">
+    <row r="193" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="7"/>
@@ -6465,7 +6509,7 @@
       <c r="AA193" s="1"/>
       <c r="AB193" s="1"/>
     </row>
-    <row r="194">
+    <row r="194" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="7"/>
@@ -6495,7 +6539,7 @@
       <c r="AA194" s="1"/>
       <c r="AB194" s="1"/>
     </row>
-    <row r="195">
+    <row r="195" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="7"/>
@@ -6525,7 +6569,7 @@
       <c r="AA195" s="1"/>
       <c r="AB195" s="1"/>
     </row>
-    <row r="196">
+    <row r="196" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="7"/>
@@ -6555,7 +6599,7 @@
       <c r="AA196" s="1"/>
       <c r="AB196" s="1"/>
     </row>
-    <row r="197">
+    <row r="197" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="7"/>
@@ -6585,7 +6629,7 @@
       <c r="AA197" s="1"/>
       <c r="AB197" s="1"/>
     </row>
-    <row r="198">
+    <row r="198" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="7"/>
@@ -6615,7 +6659,7 @@
       <c r="AA198" s="1"/>
       <c r="AB198" s="1"/>
     </row>
-    <row r="199">
+    <row r="199" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="7"/>
@@ -6645,7 +6689,7 @@
       <c r="AA199" s="1"/>
       <c r="AB199" s="1"/>
     </row>
-    <row r="200">
+    <row r="200" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="7"/>
@@ -6675,7 +6719,7 @@
       <c r="AA200" s="1"/>
       <c r="AB200" s="1"/>
     </row>
-    <row r="201">
+    <row r="201" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="7"/>
@@ -6705,7 +6749,7 @@
       <c r="AA201" s="1"/>
       <c r="AB201" s="1"/>
     </row>
-    <row r="202">
+    <row r="202" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="7"/>
@@ -6735,7 +6779,7 @@
       <c r="AA202" s="1"/>
       <c r="AB202" s="1"/>
     </row>
-    <row r="203">
+    <row r="203" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="7"/>
@@ -6765,7 +6809,7 @@
       <c r="AA203" s="1"/>
       <c r="AB203" s="1"/>
     </row>
-    <row r="204">
+    <row r="204" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="7"/>
@@ -6795,7 +6839,7 @@
       <c r="AA204" s="1"/>
       <c r="AB204" s="1"/>
     </row>
-    <row r="205">
+    <row r="205" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="7"/>
@@ -6825,7 +6869,7 @@
       <c r="AA205" s="1"/>
       <c r="AB205" s="1"/>
     </row>
-    <row r="206">
+    <row r="206" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="7"/>
@@ -6855,7 +6899,7 @@
       <c r="AA206" s="1"/>
       <c r="AB206" s="1"/>
     </row>
-    <row r="207">
+    <row r="207" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="7"/>
@@ -6885,7 +6929,7 @@
       <c r="AA207" s="1"/>
       <c r="AB207" s="1"/>
     </row>
-    <row r="208">
+    <row r="208" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="7"/>
@@ -6915,7 +6959,7 @@
       <c r="AA208" s="1"/>
       <c r="AB208" s="1"/>
     </row>
-    <row r="209">
+    <row r="209" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="7"/>
@@ -6945,7 +6989,7 @@
       <c r="AA209" s="1"/>
       <c r="AB209" s="1"/>
     </row>
-    <row r="210">
+    <row r="210" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="7"/>
@@ -6975,7 +7019,7 @@
       <c r="AA210" s="1"/>
       <c r="AB210" s="1"/>
     </row>
-    <row r="211">
+    <row r="211" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="7"/>
@@ -7005,7 +7049,7 @@
       <c r="AA211" s="1"/>
       <c r="AB211" s="1"/>
     </row>
-    <row r="212">
+    <row r="212" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="7"/>
@@ -7035,7 +7079,7 @@
       <c r="AA212" s="1"/>
       <c r="AB212" s="1"/>
     </row>
-    <row r="213">
+    <row r="213" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="7"/>
@@ -7065,7 +7109,7 @@
       <c r="AA213" s="1"/>
       <c r="AB213" s="1"/>
     </row>
-    <row r="214">
+    <row r="214" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="7"/>
@@ -7095,7 +7139,7 @@
       <c r="AA214" s="1"/>
       <c r="AB214" s="1"/>
     </row>
-    <row r="215">
+    <row r="215" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="7"/>
@@ -7125,7 +7169,7 @@
       <c r="AA215" s="1"/>
       <c r="AB215" s="1"/>
     </row>
-    <row r="216">
+    <row r="216" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="7"/>
@@ -7155,7 +7199,7 @@
       <c r="AA216" s="1"/>
       <c r="AB216" s="1"/>
     </row>
-    <row r="217">
+    <row r="217" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="7"/>
@@ -7185,7 +7229,7 @@
       <c r="AA217" s="1"/>
       <c r="AB217" s="1"/>
     </row>
-    <row r="218">
+    <row r="218" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="7"/>
@@ -7215,7 +7259,7 @@
       <c r="AA218" s="1"/>
       <c r="AB218" s="1"/>
     </row>
-    <row r="219">
+    <row r="219" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="7"/>
@@ -7245,7 +7289,7 @@
       <c r="AA219" s="1"/>
       <c r="AB219" s="1"/>
     </row>
-    <row r="220">
+    <row r="220" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="7"/>
@@ -7275,7 +7319,7 @@
       <c r="AA220" s="1"/>
       <c r="AB220" s="1"/>
     </row>
-    <row r="221">
+    <row r="221" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="7"/>
@@ -7305,7 +7349,7 @@
       <c r="AA221" s="1"/>
       <c r="AB221" s="1"/>
     </row>
-    <row r="222">
+    <row r="222" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="7"/>
@@ -7335,7 +7379,7 @@
       <c r="AA222" s="1"/>
       <c r="AB222" s="1"/>
     </row>
-    <row r="223">
+    <row r="223" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="7"/>
@@ -7365,7 +7409,7 @@
       <c r="AA223" s="1"/>
       <c r="AB223" s="1"/>
     </row>
-    <row r="224">
+    <row r="224" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="7"/>
@@ -7395,7 +7439,7 @@
       <c r="AA224" s="1"/>
       <c r="AB224" s="1"/>
     </row>
-    <row r="225">
+    <row r="225" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="7"/>
@@ -7425,7 +7469,7 @@
       <c r="AA225" s="1"/>
       <c r="AB225" s="1"/>
     </row>
-    <row r="226">
+    <row r="226" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="7"/>
@@ -7455,7 +7499,7 @@
       <c r="AA226" s="1"/>
       <c r="AB226" s="1"/>
     </row>
-    <row r="227">
+    <row r="227" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="7"/>
@@ -7485,7 +7529,7 @@
       <c r="AA227" s="1"/>
       <c r="AB227" s="1"/>
     </row>
-    <row r="228">
+    <row r="228" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="7"/>
@@ -7515,7 +7559,7 @@
       <c r="AA228" s="1"/>
       <c r="AB228" s="1"/>
     </row>
-    <row r="229">
+    <row r="229" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="7"/>
@@ -7545,7 +7589,7 @@
       <c r="AA229" s="1"/>
       <c r="AB229" s="1"/>
     </row>
-    <row r="230">
+    <row r="230" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="7"/>
@@ -7575,7 +7619,7 @@
       <c r="AA230" s="1"/>
       <c r="AB230" s="1"/>
     </row>
-    <row r="231">
+    <row r="231" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="7"/>
@@ -7605,7 +7649,7 @@
       <c r="AA231" s="1"/>
       <c r="AB231" s="1"/>
     </row>
-    <row r="232">
+    <row r="232" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="7"/>
@@ -7635,7 +7679,7 @@
       <c r="AA232" s="1"/>
       <c r="AB232" s="1"/>
     </row>
-    <row r="233">
+    <row r="233" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="7"/>
@@ -7665,7 +7709,7 @@
       <c r="AA233" s="1"/>
       <c r="AB233" s="1"/>
     </row>
-    <row r="234">
+    <row r="234" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="7"/>
@@ -7695,7 +7739,7 @@
       <c r="AA234" s="1"/>
       <c r="AB234" s="1"/>
     </row>
-    <row r="235">
+    <row r="235" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="7"/>
@@ -7725,7 +7769,7 @@
       <c r="AA235" s="1"/>
       <c r="AB235" s="1"/>
     </row>
-    <row r="236">
+    <row r="236" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="7"/>
@@ -7755,7 +7799,7 @@
       <c r="AA236" s="1"/>
       <c r="AB236" s="1"/>
     </row>
-    <row r="237">
+    <row r="237" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="7"/>
@@ -7785,7 +7829,7 @@
       <c r="AA237" s="1"/>
       <c r="AB237" s="1"/>
     </row>
-    <row r="238">
+    <row r="238" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="7"/>
@@ -7815,7 +7859,7 @@
       <c r="AA238" s="1"/>
       <c r="AB238" s="1"/>
     </row>
-    <row r="239">
+    <row r="239" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="7"/>
@@ -7845,7 +7889,7 @@
       <c r="AA239" s="1"/>
       <c r="AB239" s="1"/>
     </row>
-    <row r="240">
+    <row r="240" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="7"/>
@@ -7875,7 +7919,7 @@
       <c r="AA240" s="1"/>
       <c r="AB240" s="1"/>
     </row>
-    <row r="241">
+    <row r="241" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="7"/>
@@ -7905,7 +7949,7 @@
       <c r="AA241" s="1"/>
       <c r="AB241" s="1"/>
     </row>
-    <row r="242">
+    <row r="242" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="7"/>
@@ -7935,7 +7979,7 @@
       <c r="AA242" s="1"/>
       <c r="AB242" s="1"/>
     </row>
-    <row r="243">
+    <row r="243" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="7"/>
@@ -7965,7 +8009,7 @@
       <c r="AA243" s="1"/>
       <c r="AB243" s="1"/>
     </row>
-    <row r="244">
+    <row r="244" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="7"/>
@@ -7995,7 +8039,7 @@
       <c r="AA244" s="1"/>
       <c r="AB244" s="1"/>
     </row>
-    <row r="245">
+    <row r="245" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="7"/>
@@ -8025,7 +8069,7 @@
       <c r="AA245" s="1"/>
       <c r="AB245" s="1"/>
     </row>
-    <row r="246">
+    <row r="246" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="7"/>
@@ -8055,7 +8099,7 @@
       <c r="AA246" s="1"/>
       <c r="AB246" s="1"/>
     </row>
-    <row r="247">
+    <row r="247" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="7"/>
@@ -8085,7 +8129,7 @@
       <c r="AA247" s="1"/>
       <c r="AB247" s="1"/>
     </row>
-    <row r="248">
+    <row r="248" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="7"/>
@@ -8115,7 +8159,7 @@
       <c r="AA248" s="1"/>
       <c r="AB248" s="1"/>
     </row>
-    <row r="249">
+    <row r="249" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="7"/>
@@ -8145,7 +8189,7 @@
       <c r="AA249" s="1"/>
       <c r="AB249" s="1"/>
     </row>
-    <row r="250">
+    <row r="250" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="7"/>
@@ -8175,7 +8219,7 @@
       <c r="AA250" s="1"/>
       <c r="AB250" s="1"/>
     </row>
-    <row r="251">
+    <row r="251" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="7"/>
@@ -8205,7 +8249,7 @@
       <c r="AA251" s="1"/>
       <c r="AB251" s="1"/>
     </row>
-    <row r="252">
+    <row r="252" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="7"/>
@@ -8235,7 +8279,7 @@
       <c r="AA252" s="1"/>
       <c r="AB252" s="1"/>
     </row>
-    <row r="253">
+    <row r="253" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="7"/>
@@ -8265,7 +8309,7 @@
       <c r="AA253" s="1"/>
       <c r="AB253" s="1"/>
     </row>
-    <row r="254">
+    <row r="254" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="7"/>
@@ -8295,7 +8339,7 @@
       <c r="AA254" s="1"/>
       <c r="AB254" s="1"/>
     </row>
-    <row r="255">
+    <row r="255" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="7"/>
@@ -8325,7 +8369,7 @@
       <c r="AA255" s="1"/>
       <c r="AB255" s="1"/>
     </row>
-    <row r="256">
+    <row r="256" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="7"/>
@@ -8355,7 +8399,7 @@
       <c r="AA256" s="1"/>
       <c r="AB256" s="1"/>
     </row>
-    <row r="257">
+    <row r="257" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="7"/>
@@ -8385,7 +8429,7 @@
       <c r="AA257" s="1"/>
       <c r="AB257" s="1"/>
     </row>
-    <row r="258">
+    <row r="258" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="7"/>
@@ -8415,7 +8459,7 @@
       <c r="AA258" s="1"/>
       <c r="AB258" s="1"/>
     </row>
-    <row r="259">
+    <row r="259" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="7"/>
@@ -8445,7 +8489,7 @@
       <c r="AA259" s="1"/>
       <c r="AB259" s="1"/>
     </row>
-    <row r="260">
+    <row r="260" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="7"/>
@@ -8475,7 +8519,7 @@
       <c r="AA260" s="1"/>
       <c r="AB260" s="1"/>
     </row>
-    <row r="261">
+    <row r="261" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="7"/>
@@ -8505,7 +8549,7 @@
       <c r="AA261" s="1"/>
       <c r="AB261" s="1"/>
     </row>
-    <row r="262">
+    <row r="262" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="7"/>
@@ -8535,7 +8579,7 @@
       <c r="AA262" s="1"/>
       <c r="AB262" s="1"/>
     </row>
-    <row r="263">
+    <row r="263" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="7"/>
@@ -8565,7 +8609,7 @@
       <c r="AA263" s="1"/>
       <c r="AB263" s="1"/>
     </row>
-    <row r="264">
+    <row r="264" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="7"/>
@@ -8595,7 +8639,7 @@
       <c r="AA264" s="1"/>
       <c r="AB264" s="1"/>
     </row>
-    <row r="265">
+    <row r="265" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="7"/>
@@ -8625,7 +8669,7 @@
       <c r="AA265" s="1"/>
       <c r="AB265" s="1"/>
     </row>
-    <row r="266">
+    <row r="266" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="7"/>
@@ -8655,7 +8699,7 @@
       <c r="AA266" s="1"/>
       <c r="AB266" s="1"/>
     </row>
-    <row r="267">
+    <row r="267" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="7"/>
@@ -8685,7 +8729,7 @@
       <c r="AA267" s="1"/>
       <c r="AB267" s="1"/>
     </row>
-    <row r="268">
+    <row r="268" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="7"/>
@@ -8715,7 +8759,7 @@
       <c r="AA268" s="1"/>
       <c r="AB268" s="1"/>
     </row>
-    <row r="269">
+    <row r="269" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="7"/>
@@ -8745,7 +8789,7 @@
       <c r="AA269" s="1"/>
       <c r="AB269" s="1"/>
     </row>
-    <row r="270">
+    <row r="270" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="7"/>
@@ -8775,7 +8819,7 @@
       <c r="AA270" s="1"/>
       <c r="AB270" s="1"/>
     </row>
-    <row r="271">
+    <row r="271" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="7"/>
@@ -8805,7 +8849,7 @@
       <c r="AA271" s="1"/>
       <c r="AB271" s="1"/>
     </row>
-    <row r="272">
+    <row r="272" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="7"/>
@@ -8835,7 +8879,7 @@
       <c r="AA272" s="1"/>
       <c r="AB272" s="1"/>
     </row>
-    <row r="273">
+    <row r="273" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="7"/>
@@ -8865,7 +8909,7 @@
       <c r="AA273" s="1"/>
       <c r="AB273" s="1"/>
     </row>
-    <row r="274">
+    <row r="274" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="7"/>
@@ -8895,7 +8939,7 @@
       <c r="AA274" s="1"/>
       <c r="AB274" s="1"/>
     </row>
-    <row r="275">
+    <row r="275" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="7"/>
@@ -8925,7 +8969,7 @@
       <c r="AA275" s="1"/>
       <c r="AB275" s="1"/>
     </row>
-    <row r="276">
+    <row r="276" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="7"/>
@@ -8955,7 +8999,7 @@
       <c r="AA276" s="1"/>
       <c r="AB276" s="1"/>
     </row>
-    <row r="277">
+    <row r="277" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="C277" s="7"/>
@@ -8985,7 +9029,7 @@
       <c r="AA277" s="1"/>
       <c r="AB277" s="1"/>
     </row>
-    <row r="278">
+    <row r="278" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="7"/>
@@ -9015,7 +9059,7 @@
       <c r="AA278" s="1"/>
       <c r="AB278" s="1"/>
     </row>
-    <row r="279">
+    <row r="279" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="7"/>
@@ -9045,7 +9089,7 @@
       <c r="AA279" s="1"/>
       <c r="AB279" s="1"/>
     </row>
-    <row r="280">
+    <row r="280" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="7"/>
@@ -9075,7 +9119,7 @@
       <c r="AA280" s="1"/>
       <c r="AB280" s="1"/>
     </row>
-    <row r="281">
+    <row r="281" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="7"/>
@@ -9105,7 +9149,7 @@
       <c r="AA281" s="1"/>
       <c r="AB281" s="1"/>
     </row>
-    <row r="282">
+    <row r="282" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="C282" s="7"/>
@@ -9135,7 +9179,7 @@
       <c r="AA282" s="1"/>
       <c r="AB282" s="1"/>
     </row>
-    <row r="283">
+    <row r="283" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="7"/>
@@ -9165,7 +9209,7 @@
       <c r="AA283" s="1"/>
       <c r="AB283" s="1"/>
     </row>
-    <row r="284">
+    <row r="284" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="C284" s="7"/>
@@ -9195,7 +9239,7 @@
       <c r="AA284" s="1"/>
       <c r="AB284" s="1"/>
     </row>
-    <row r="285">
+    <row r="285" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="7"/>
@@ -9225,7 +9269,7 @@
       <c r="AA285" s="1"/>
       <c r="AB285" s="1"/>
     </row>
-    <row r="286">
+    <row r="286" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="7"/>
@@ -9255,7 +9299,7 @@
       <c r="AA286" s="1"/>
       <c r="AB286" s="1"/>
     </row>
-    <row r="287">
+    <row r="287" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="7"/>
@@ -9285,7 +9329,7 @@
       <c r="AA287" s="1"/>
       <c r="AB287" s="1"/>
     </row>
-    <row r="288">
+    <row r="288" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="C288" s="7"/>
@@ -9315,7 +9359,7 @@
       <c r="AA288" s="1"/>
       <c r="AB288" s="1"/>
     </row>
-    <row r="289">
+    <row r="289" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
       <c r="C289" s="7"/>
@@ -9345,7 +9389,7 @@
       <c r="AA289" s="1"/>
       <c r="AB289" s="1"/>
     </row>
-    <row r="290">
+    <row r="290" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
       <c r="C290" s="7"/>
@@ -9375,7 +9419,7 @@
       <c r="AA290" s="1"/>
       <c r="AB290" s="1"/>
     </row>
-    <row r="291">
+    <row r="291" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
       <c r="C291" s="7"/>
@@ -9405,7 +9449,7 @@
       <c r="AA291" s="1"/>
       <c r="AB291" s="1"/>
     </row>
-    <row r="292">
+    <row r="292" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A292" s="1"/>
       <c r="B292" s="1"/>
       <c r="C292" s="7"/>
@@ -9435,7 +9479,7 @@
       <c r="AA292" s="1"/>
       <c r="AB292" s="1"/>
     </row>
-    <row r="293">
+    <row r="293" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A293" s="1"/>
       <c r="B293" s="1"/>
       <c r="C293" s="7"/>
@@ -9465,7 +9509,7 @@
       <c r="AA293" s="1"/>
       <c r="AB293" s="1"/>
     </row>
-    <row r="294">
+    <row r="294" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
       <c r="C294" s="7"/>
@@ -9495,7 +9539,7 @@
       <c r="AA294" s="1"/>
       <c r="AB294" s="1"/>
     </row>
-    <row r="295">
+    <row r="295" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A295" s="1"/>
       <c r="B295" s="1"/>
       <c r="C295" s="7"/>
@@ -9525,7 +9569,7 @@
       <c r="AA295" s="1"/>
       <c r="AB295" s="1"/>
     </row>
-    <row r="296">
+    <row r="296" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A296" s="1"/>
       <c r="B296" s="1"/>
       <c r="C296" s="7"/>
@@ -9555,7 +9599,7 @@
       <c r="AA296" s="1"/>
       <c r="AB296" s="1"/>
     </row>
-    <row r="297">
+    <row r="297" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="C297" s="7"/>
@@ -9585,7 +9629,7 @@
       <c r="AA297" s="1"/>
       <c r="AB297" s="1"/>
     </row>
-    <row r="298">
+    <row r="298" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="7"/>
@@ -9615,7 +9659,7 @@
       <c r="AA298" s="1"/>
       <c r="AB298" s="1"/>
     </row>
-    <row r="299">
+    <row r="299" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="7"/>
@@ -9645,7 +9689,7 @@
       <c r="AA299" s="1"/>
       <c r="AB299" s="1"/>
     </row>
-    <row r="300">
+    <row r="300" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="7"/>
@@ -9675,7 +9719,7 @@
       <c r="AA300" s="1"/>
       <c r="AB300" s="1"/>
     </row>
-    <row r="301">
+    <row r="301" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="C301" s="7"/>
@@ -9705,7 +9749,7 @@
       <c r="AA301" s="1"/>
       <c r="AB301" s="1"/>
     </row>
-    <row r="302">
+    <row r="302" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A302" s="1"/>
       <c r="B302" s="1"/>
       <c r="C302" s="7"/>
@@ -9735,7 +9779,7 @@
       <c r="AA302" s="1"/>
       <c r="AB302" s="1"/>
     </row>
-    <row r="303">
+    <row r="303" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A303" s="1"/>
       <c r="B303" s="1"/>
       <c r="C303" s="7"/>
@@ -9765,7 +9809,7 @@
       <c r="AA303" s="1"/>
       <c r="AB303" s="1"/>
     </row>
-    <row r="304">
+    <row r="304" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A304" s="1"/>
       <c r="B304" s="1"/>
       <c r="C304" s="7"/>
@@ -9795,7 +9839,7 @@
       <c r="AA304" s="1"/>
       <c r="AB304" s="1"/>
     </row>
-    <row r="305">
+    <row r="305" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A305" s="1"/>
       <c r="B305" s="1"/>
       <c r="C305" s="7"/>
@@ -9825,7 +9869,7 @@
       <c r="AA305" s="1"/>
       <c r="AB305" s="1"/>
     </row>
-    <row r="306">
+    <row r="306" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="7"/>
@@ -9855,7 +9899,7 @@
       <c r="AA306" s="1"/>
       <c r="AB306" s="1"/>
     </row>
-    <row r="307">
+    <row r="307" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A307" s="1"/>
       <c r="B307" s="1"/>
       <c r="C307" s="7"/>
@@ -9885,7 +9929,7 @@
       <c r="AA307" s="1"/>
       <c r="AB307" s="1"/>
     </row>
-    <row r="308">
+    <row r="308" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A308" s="1"/>
       <c r="B308" s="1"/>
       <c r="C308" s="7"/>
@@ -9915,7 +9959,7 @@
       <c r="AA308" s="1"/>
       <c r="AB308" s="1"/>
     </row>
-    <row r="309">
+    <row r="309" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A309" s="1"/>
       <c r="B309" s="1"/>
       <c r="C309" s="7"/>
@@ -9945,7 +9989,7 @@
       <c r="AA309" s="1"/>
       <c r="AB309" s="1"/>
     </row>
-    <row r="310">
+    <row r="310" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="7"/>
@@ -9975,7 +10019,7 @@
       <c r="AA310" s="1"/>
       <c r="AB310" s="1"/>
     </row>
-    <row r="311">
+    <row r="311" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A311" s="1"/>
       <c r="B311" s="1"/>
       <c r="C311" s="7"/>
@@ -10005,7 +10049,7 @@
       <c r="AA311" s="1"/>
       <c r="AB311" s="1"/>
     </row>
-    <row r="312">
+    <row r="312" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A312" s="1"/>
       <c r="B312" s="1"/>
       <c r="C312" s="7"/>
@@ -10035,7 +10079,7 @@
       <c r="AA312" s="1"/>
       <c r="AB312" s="1"/>
     </row>
-    <row r="313">
+    <row r="313" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="7"/>
@@ -10065,7 +10109,7 @@
       <c r="AA313" s="1"/>
       <c r="AB313" s="1"/>
     </row>
-    <row r="314">
+    <row r="314" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A314" s="1"/>
       <c r="B314" s="1"/>
       <c r="C314" s="7"/>
@@ -10095,7 +10139,7 @@
       <c r="AA314" s="1"/>
       <c r="AB314" s="1"/>
     </row>
-    <row r="315">
+    <row r="315" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A315" s="1"/>
       <c r="B315" s="1"/>
       <c r="C315" s="7"/>
@@ -10125,7 +10169,7 @@
       <c r="AA315" s="1"/>
       <c r="AB315" s="1"/>
     </row>
-    <row r="316">
+    <row r="316" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A316" s="1"/>
       <c r="B316" s="1"/>
       <c r="C316" s="7"/>
@@ -10155,7 +10199,7 @@
       <c r="AA316" s="1"/>
       <c r="AB316" s="1"/>
     </row>
-    <row r="317">
+    <row r="317" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A317" s="1"/>
       <c r="B317" s="1"/>
       <c r="C317" s="7"/>
@@ -10185,7 +10229,7 @@
       <c r="AA317" s="1"/>
       <c r="AB317" s="1"/>
     </row>
-    <row r="318">
+    <row r="318" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A318" s="1"/>
       <c r="B318" s="1"/>
       <c r="C318" s="7"/>
@@ -10215,7 +10259,7 @@
       <c r="AA318" s="1"/>
       <c r="AB318" s="1"/>
     </row>
-    <row r="319">
+    <row r="319" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A319" s="1"/>
       <c r="B319" s="1"/>
       <c r="C319" s="7"/>
@@ -10245,7 +10289,7 @@
       <c r="AA319" s="1"/>
       <c r="AB319" s="1"/>
     </row>
-    <row r="320">
+    <row r="320" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
       <c r="C320" s="7"/>
@@ -10275,7 +10319,7 @@
       <c r="AA320" s="1"/>
       <c r="AB320" s="1"/>
     </row>
-    <row r="321">
+    <row r="321" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A321" s="1"/>
       <c r="B321" s="1"/>
       <c r="C321" s="7"/>
@@ -10305,7 +10349,7 @@
       <c r="AA321" s="1"/>
       <c r="AB321" s="1"/>
     </row>
-    <row r="322">
+    <row r="322" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A322" s="1"/>
       <c r="B322" s="1"/>
       <c r="C322" s="7"/>
@@ -10335,7 +10379,7 @@
       <c r="AA322" s="1"/>
       <c r="AB322" s="1"/>
     </row>
-    <row r="323">
+    <row r="323" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A323" s="1"/>
       <c r="B323" s="1"/>
       <c r="C323" s="7"/>
@@ -10365,7 +10409,7 @@
       <c r="AA323" s="1"/>
       <c r="AB323" s="1"/>
     </row>
-    <row r="324">
+    <row r="324" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="C324" s="7"/>
@@ -10395,7 +10439,7 @@
       <c r="AA324" s="1"/>
       <c r="AB324" s="1"/>
     </row>
-    <row r="325">
+    <row r="325" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="C325" s="7"/>
@@ -10425,7 +10469,7 @@
       <c r="AA325" s="1"/>
       <c r="AB325" s="1"/>
     </row>
-    <row r="326">
+    <row r="326" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="7"/>
@@ -10455,7 +10499,7 @@
       <c r="AA326" s="1"/>
       <c r="AB326" s="1"/>
     </row>
-    <row r="327">
+    <row r="327" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A327" s="1"/>
       <c r="B327" s="1"/>
       <c r="C327" s="7"/>
@@ -10485,7 +10529,7 @@
       <c r="AA327" s="1"/>
       <c r="AB327" s="1"/>
     </row>
-    <row r="328">
+    <row r="328" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A328" s="1"/>
       <c r="B328" s="1"/>
       <c r="C328" s="7"/>
@@ -10515,7 +10559,7 @@
       <c r="AA328" s="1"/>
       <c r="AB328" s="1"/>
     </row>
-    <row r="329">
+    <row r="329" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A329" s="1"/>
       <c r="B329" s="1"/>
       <c r="C329" s="7"/>
@@ -10545,7 +10589,7 @@
       <c r="AA329" s="1"/>
       <c r="AB329" s="1"/>
     </row>
-    <row r="330">
+    <row r="330" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A330" s="1"/>
       <c r="B330" s="1"/>
       <c r="C330" s="7"/>
@@ -10575,7 +10619,7 @@
       <c r="AA330" s="1"/>
       <c r="AB330" s="1"/>
     </row>
-    <row r="331">
+    <row r="331" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A331" s="1"/>
       <c r="B331" s="1"/>
       <c r="C331" s="7"/>
@@ -10605,7 +10649,7 @@
       <c r="AA331" s="1"/>
       <c r="AB331" s="1"/>
     </row>
-    <row r="332">
+    <row r="332" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="7"/>
@@ -10635,7 +10679,7 @@
       <c r="AA332" s="1"/>
       <c r="AB332" s="1"/>
     </row>
-    <row r="333">
+    <row r="333" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A333" s="1"/>
       <c r="B333" s="1"/>
       <c r="C333" s="7"/>
@@ -10665,7 +10709,7 @@
       <c r="AA333" s="1"/>
       <c r="AB333" s="1"/>
     </row>
-    <row r="334">
+    <row r="334" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A334" s="1"/>
       <c r="B334" s="1"/>
       <c r="C334" s="7"/>
@@ -10695,7 +10739,7 @@
       <c r="AA334" s="1"/>
       <c r="AB334" s="1"/>
     </row>
-    <row r="335">
+    <row r="335" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="7"/>
@@ -10725,7 +10769,7 @@
       <c r="AA335" s="1"/>
       <c r="AB335" s="1"/>
     </row>
-    <row r="336">
+    <row r="336" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="7"/>
@@ -10755,7 +10799,7 @@
       <c r="AA336" s="1"/>
       <c r="AB336" s="1"/>
     </row>
-    <row r="337">
+    <row r="337" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="7"/>
@@ -10785,7 +10829,7 @@
       <c r="AA337" s="1"/>
       <c r="AB337" s="1"/>
     </row>
-    <row r="338">
+    <row r="338" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="7"/>
@@ -10815,7 +10859,7 @@
       <c r="AA338" s="1"/>
       <c r="AB338" s="1"/>
     </row>
-    <row r="339">
+    <row r="339" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A339" s="1"/>
       <c r="B339" s="1"/>
       <c r="C339" s="7"/>
@@ -10845,7 +10889,7 @@
       <c r="AA339" s="1"/>
       <c r="AB339" s="1"/>
     </row>
-    <row r="340">
+    <row r="340" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A340" s="1"/>
       <c r="B340" s="1"/>
       <c r="C340" s="7"/>
@@ -10875,7 +10919,7 @@
       <c r="AA340" s="1"/>
       <c r="AB340" s="1"/>
     </row>
-    <row r="341">
+    <row r="341" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A341" s="1"/>
       <c r="B341" s="1"/>
       <c r="C341" s="7"/>
@@ -10905,7 +10949,7 @@
       <c r="AA341" s="1"/>
       <c r="AB341" s="1"/>
     </row>
-    <row r="342">
+    <row r="342" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A342" s="1"/>
       <c r="B342" s="1"/>
       <c r="C342" s="7"/>
@@ -10935,7 +10979,7 @@
       <c r="AA342" s="1"/>
       <c r="AB342" s="1"/>
     </row>
-    <row r="343">
+    <row r="343" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A343" s="1"/>
       <c r="B343" s="1"/>
       <c r="C343" s="7"/>
@@ -10965,7 +11009,7 @@
       <c r="AA343" s="1"/>
       <c r="AB343" s="1"/>
     </row>
-    <row r="344">
+    <row r="344" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A344" s="1"/>
       <c r="B344" s="1"/>
       <c r="C344" s="7"/>
@@ -10995,7 +11039,7 @@
       <c r="AA344" s="1"/>
       <c r="AB344" s="1"/>
     </row>
-    <row r="345">
+    <row r="345" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A345" s="1"/>
       <c r="B345" s="1"/>
       <c r="C345" s="7"/>
@@ -11025,7 +11069,7 @@
       <c r="AA345" s="1"/>
       <c r="AB345" s="1"/>
     </row>
-    <row r="346">
+    <row r="346" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="7"/>
@@ -11055,7 +11099,7 @@
       <c r="AA346" s="1"/>
       <c r="AB346" s="1"/>
     </row>
-    <row r="347">
+    <row r="347" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A347" s="1"/>
       <c r="B347" s="1"/>
       <c r="C347" s="7"/>
@@ -11085,7 +11129,7 @@
       <c r="AA347" s="1"/>
       <c r="AB347" s="1"/>
     </row>
-    <row r="348">
+    <row r="348" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="7"/>
@@ -11115,7 +11159,7 @@
       <c r="AA348" s="1"/>
       <c r="AB348" s="1"/>
     </row>
-    <row r="349">
+    <row r="349" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A349" s="1"/>
       <c r="B349" s="1"/>
       <c r="C349" s="7"/>
@@ -11145,7 +11189,7 @@
       <c r="AA349" s="1"/>
       <c r="AB349" s="1"/>
     </row>
-    <row r="350">
+    <row r="350" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A350" s="1"/>
       <c r="B350" s="1"/>
       <c r="C350" s="7"/>
@@ -11175,7 +11219,7 @@
       <c r="AA350" s="1"/>
       <c r="AB350" s="1"/>
     </row>
-    <row r="351">
+    <row r="351" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="7"/>
@@ -11205,7 +11249,7 @@
       <c r="AA351" s="1"/>
       <c r="AB351" s="1"/>
     </row>
-    <row r="352">
+    <row r="352" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A352" s="1"/>
       <c r="B352" s="1"/>
       <c r="C352" s="7"/>
@@ -11235,7 +11279,7 @@
       <c r="AA352" s="1"/>
       <c r="AB352" s="1"/>
     </row>
-    <row r="353">
+    <row r="353" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A353" s="1"/>
       <c r="B353" s="1"/>
       <c r="C353" s="7"/>
@@ -11265,7 +11309,7 @@
       <c r="AA353" s="1"/>
       <c r="AB353" s="1"/>
     </row>
-    <row r="354">
+    <row r="354" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="7"/>
@@ -11295,7 +11339,7 @@
       <c r="AA354" s="1"/>
       <c r="AB354" s="1"/>
     </row>
-    <row r="355">
+    <row r="355" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="7"/>
@@ -11325,7 +11369,7 @@
       <c r="AA355" s="1"/>
       <c r="AB355" s="1"/>
     </row>
-    <row r="356">
+    <row r="356" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="C356" s="7"/>
@@ -11355,7 +11399,7 @@
       <c r="AA356" s="1"/>
       <c r="AB356" s="1"/>
     </row>
-    <row r="357">
+    <row r="357" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A357" s="1"/>
       <c r="B357" s="1"/>
       <c r="C357" s="7"/>
@@ -11385,7 +11429,7 @@
       <c r="AA357" s="1"/>
       <c r="AB357" s="1"/>
     </row>
-    <row r="358">
+    <row r="358" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A358" s="1"/>
       <c r="B358" s="1"/>
       <c r="C358" s="7"/>
@@ -11415,7 +11459,7 @@
       <c r="AA358" s="1"/>
       <c r="AB358" s="1"/>
     </row>
-    <row r="359">
+    <row r="359" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A359" s="1"/>
       <c r="B359" s="1"/>
       <c r="C359" s="7"/>
@@ -11445,7 +11489,7 @@
       <c r="AA359" s="1"/>
       <c r="AB359" s="1"/>
     </row>
-    <row r="360">
+    <row r="360" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="C360" s="7"/>
@@ -11475,7 +11519,7 @@
       <c r="AA360" s="1"/>
       <c r="AB360" s="1"/>
     </row>
-    <row r="361">
+    <row r="361" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A361" s="1"/>
       <c r="B361" s="1"/>
       <c r="C361" s="7"/>
@@ -11505,7 +11549,7 @@
       <c r="AA361" s="1"/>
       <c r="AB361" s="1"/>
     </row>
-    <row r="362">
+    <row r="362" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A362" s="1"/>
       <c r="B362" s="1"/>
       <c r="C362" s="7"/>
@@ -11535,7 +11579,7 @@
       <c r="AA362" s="1"/>
       <c r="AB362" s="1"/>
     </row>
-    <row r="363">
+    <row r="363" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A363" s="1"/>
       <c r="B363" s="1"/>
       <c r="C363" s="7"/>
@@ -11565,7 +11609,7 @@
       <c r="AA363" s="1"/>
       <c r="AB363" s="1"/>
     </row>
-    <row r="364">
+    <row r="364" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A364" s="1"/>
       <c r="B364" s="1"/>
       <c r="C364" s="7"/>
@@ -11595,7 +11639,7 @@
       <c r="AA364" s="1"/>
       <c r="AB364" s="1"/>
     </row>
-    <row r="365">
+    <row r="365" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A365" s="1"/>
       <c r="B365" s="1"/>
       <c r="C365" s="7"/>
@@ -11625,7 +11669,7 @@
       <c r="AA365" s="1"/>
       <c r="AB365" s="1"/>
     </row>
-    <row r="366">
+    <row r="366" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="7"/>
@@ -11655,7 +11699,7 @@
       <c r="AA366" s="1"/>
       <c r="AB366" s="1"/>
     </row>
-    <row r="367">
+    <row r="367" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A367" s="1"/>
       <c r="B367" s="1"/>
       <c r="C367" s="7"/>
@@ -11685,7 +11729,7 @@
       <c r="AA367" s="1"/>
       <c r="AB367" s="1"/>
     </row>
-    <row r="368">
+    <row r="368" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A368" s="1"/>
       <c r="B368" s="1"/>
       <c r="C368" s="7"/>
@@ -11715,7 +11759,7 @@
       <c r="AA368" s="1"/>
       <c r="AB368" s="1"/>
     </row>
-    <row r="369">
+    <row r="369" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A369" s="1"/>
       <c r="B369" s="1"/>
       <c r="C369" s="7"/>
@@ -11745,7 +11789,7 @@
       <c r="AA369" s="1"/>
       <c r="AB369" s="1"/>
     </row>
-    <row r="370">
+    <row r="370" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A370" s="1"/>
       <c r="B370" s="1"/>
       <c r="C370" s="7"/>
@@ -11775,7 +11819,7 @@
       <c r="AA370" s="1"/>
       <c r="AB370" s="1"/>
     </row>
-    <row r="371">
+    <row r="371" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="C371" s="7"/>
@@ -11805,7 +11849,7 @@
       <c r="AA371" s="1"/>
       <c r="AB371" s="1"/>
     </row>
-    <row r="372">
+    <row r="372" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A372" s="1"/>
       <c r="B372" s="1"/>
       <c r="C372" s="7"/>
@@ -11835,7 +11879,7 @@
       <c r="AA372" s="1"/>
       <c r="AB372" s="1"/>
     </row>
-    <row r="373">
+    <row r="373" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A373" s="1"/>
       <c r="B373" s="1"/>
       <c r="C373" s="7"/>
@@ -11865,7 +11909,7 @@
       <c r="AA373" s="1"/>
       <c r="AB373" s="1"/>
     </row>
-    <row r="374">
+    <row r="374" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A374" s="1"/>
       <c r="B374" s="1"/>
       <c r="C374" s="7"/>
@@ -11895,7 +11939,7 @@
       <c r="AA374" s="1"/>
       <c r="AB374" s="1"/>
     </row>
-    <row r="375">
+    <row r="375" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A375" s="1"/>
       <c r="B375" s="1"/>
       <c r="C375" s="7"/>
@@ -11925,7 +11969,7 @@
       <c r="AA375" s="1"/>
       <c r="AB375" s="1"/>
     </row>
-    <row r="376">
+    <row r="376" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A376" s="1"/>
       <c r="B376" s="1"/>
       <c r="C376" s="7"/>
@@ -11955,7 +11999,7 @@
       <c r="AA376" s="1"/>
       <c r="AB376" s="1"/>
     </row>
-    <row r="377">
+    <row r="377" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A377" s="1"/>
       <c r="B377" s="1"/>
       <c r="C377" s="7"/>
@@ -11985,7 +12029,7 @@
       <c r="AA377" s="1"/>
       <c r="AB377" s="1"/>
     </row>
-    <row r="378">
+    <row r="378" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A378" s="1"/>
       <c r="B378" s="1"/>
       <c r="C378" s="7"/>
@@ -12015,7 +12059,7 @@
       <c r="AA378" s="1"/>
       <c r="AB378" s="1"/>
     </row>
-    <row r="379">
+    <row r="379" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A379" s="1"/>
       <c r="B379" s="1"/>
       <c r="C379" s="7"/>
@@ -12045,7 +12089,7 @@
       <c r="AA379" s="1"/>
       <c r="AB379" s="1"/>
     </row>
-    <row r="380">
+    <row r="380" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A380" s="1"/>
       <c r="B380" s="1"/>
       <c r="C380" s="7"/>
@@ -12075,7 +12119,7 @@
       <c r="AA380" s="1"/>
       <c r="AB380" s="1"/>
     </row>
-    <row r="381">
+    <row r="381" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="C381" s="7"/>
@@ -12105,7 +12149,7 @@
       <c r="AA381" s="1"/>
       <c r="AB381" s="1"/>
     </row>
-    <row r="382">
+    <row r="382" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A382" s="1"/>
       <c r="B382" s="1"/>
       <c r="C382" s="7"/>
@@ -12135,7 +12179,7 @@
       <c r="AA382" s="1"/>
       <c r="AB382" s="1"/>
     </row>
-    <row r="383">
+    <row r="383" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A383" s="1"/>
       <c r="B383" s="1"/>
       <c r="C383" s="7"/>
@@ -12165,7 +12209,7 @@
       <c r="AA383" s="1"/>
       <c r="AB383" s="1"/>
     </row>
-    <row r="384">
+    <row r="384" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A384" s="1"/>
       <c r="B384" s="1"/>
       <c r="C384" s="7"/>
@@ -12195,7 +12239,7 @@
       <c r="AA384" s="1"/>
       <c r="AB384" s="1"/>
     </row>
-    <row r="385">
+    <row r="385" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A385" s="1"/>
       <c r="B385" s="1"/>
       <c r="C385" s="7"/>
@@ -12225,7 +12269,7 @@
       <c r="AA385" s="1"/>
       <c r="AB385" s="1"/>
     </row>
-    <row r="386">
+    <row r="386" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A386" s="1"/>
       <c r="B386" s="1"/>
       <c r="C386" s="7"/>
@@ -12255,7 +12299,7 @@
       <c r="AA386" s="1"/>
       <c r="AB386" s="1"/>
     </row>
-    <row r="387">
+    <row r="387" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A387" s="1"/>
       <c r="B387" s="1"/>
       <c r="C387" s="7"/>
@@ -12285,7 +12329,7 @@
       <c r="AA387" s="1"/>
       <c r="AB387" s="1"/>
     </row>
-    <row r="388">
+    <row r="388" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A388" s="1"/>
       <c r="B388" s="1"/>
       <c r="C388" s="7"/>
@@ -12315,7 +12359,7 @@
       <c r="AA388" s="1"/>
       <c r="AB388" s="1"/>
     </row>
-    <row r="389">
+    <row r="389" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A389" s="1"/>
       <c r="B389" s="1"/>
       <c r="C389" s="7"/>
@@ -12345,7 +12389,7 @@
       <c r="AA389" s="1"/>
       <c r="AB389" s="1"/>
     </row>
-    <row r="390">
+    <row r="390" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A390" s="1"/>
       <c r="B390" s="1"/>
       <c r="C390" s="7"/>
@@ -12375,7 +12419,7 @@
       <c r="AA390" s="1"/>
       <c r="AB390" s="1"/>
     </row>
-    <row r="391">
+    <row r="391" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="C391" s="7"/>
@@ -12405,7 +12449,7 @@
       <c r="AA391" s="1"/>
       <c r="AB391" s="1"/>
     </row>
-    <row r="392">
+    <row r="392" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A392" s="1"/>
       <c r="B392" s="1"/>
       <c r="C392" s="7"/>
@@ -12435,7 +12479,7 @@
       <c r="AA392" s="1"/>
       <c r="AB392" s="1"/>
     </row>
-    <row r="393">
+    <row r="393" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A393" s="1"/>
       <c r="B393" s="1"/>
       <c r="C393" s="7"/>
@@ -12465,7 +12509,7 @@
       <c r="AA393" s="1"/>
       <c r="AB393" s="1"/>
     </row>
-    <row r="394">
+    <row r="394" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A394" s="1"/>
       <c r="B394" s="1"/>
       <c r="C394" s="7"/>
@@ -12495,7 +12539,7 @@
       <c r="AA394" s="1"/>
       <c r="AB394" s="1"/>
     </row>
-    <row r="395">
+    <row r="395" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A395" s="1"/>
       <c r="B395" s="1"/>
       <c r="C395" s="7"/>
@@ -12525,7 +12569,7 @@
       <c r="AA395" s="1"/>
       <c r="AB395" s="1"/>
     </row>
-    <row r="396">
+    <row r="396" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A396" s="1"/>
       <c r="B396" s="1"/>
       <c r="C396" s="7"/>
@@ -12555,7 +12599,7 @@
       <c r="AA396" s="1"/>
       <c r="AB396" s="1"/>
     </row>
-    <row r="397">
+    <row r="397" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A397" s="1"/>
       <c r="B397" s="1"/>
       <c r="C397" s="7"/>
@@ -12585,7 +12629,7 @@
       <c r="AA397" s="1"/>
       <c r="AB397" s="1"/>
     </row>
-    <row r="398">
+    <row r="398" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="C398" s="7"/>
@@ -12615,7 +12659,7 @@
       <c r="AA398" s="1"/>
       <c r="AB398" s="1"/>
     </row>
-    <row r="399">
+    <row r="399" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A399" s="1"/>
       <c r="B399" s="1"/>
       <c r="C399" s="7"/>
@@ -12645,7 +12689,7 @@
       <c r="AA399" s="1"/>
       <c r="AB399" s="1"/>
     </row>
-    <row r="400">
+    <row r="400" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A400" s="1"/>
       <c r="B400" s="1"/>
       <c r="C400" s="7"/>
@@ -12675,7 +12719,7 @@
       <c r="AA400" s="1"/>
       <c r="AB400" s="1"/>
     </row>
-    <row r="401">
+    <row r="401" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A401" s="1"/>
       <c r="B401" s="1"/>
       <c r="C401" s="7"/>
@@ -12705,7 +12749,7 @@
       <c r="AA401" s="1"/>
       <c r="AB401" s="1"/>
     </row>
-    <row r="402">
+    <row r="402" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A402" s="1"/>
       <c r="B402" s="1"/>
       <c r="C402" s="7"/>
@@ -12735,7 +12779,7 @@
       <c r="AA402" s="1"/>
       <c r="AB402" s="1"/>
     </row>
-    <row r="403">
+    <row r="403" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A403" s="1"/>
       <c r="B403" s="1"/>
       <c r="C403" s="7"/>
@@ -12765,7 +12809,7 @@
       <c r="AA403" s="1"/>
       <c r="AB403" s="1"/>
     </row>
-    <row r="404">
+    <row r="404" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A404" s="1"/>
       <c r="B404" s="1"/>
       <c r="C404" s="7"/>
@@ -12795,7 +12839,7 @@
       <c r="AA404" s="1"/>
       <c r="AB404" s="1"/>
     </row>
-    <row r="405">
+    <row r="405" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A405" s="1"/>
       <c r="B405" s="1"/>
       <c r="C405" s="7"/>
@@ -12825,7 +12869,7 @@
       <c r="AA405" s="1"/>
       <c r="AB405" s="1"/>
     </row>
-    <row r="406">
+    <row r="406" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A406" s="1"/>
       <c r="B406" s="1"/>
       <c r="C406" s="7"/>
@@ -12855,7 +12899,7 @@
       <c r="AA406" s="1"/>
       <c r="AB406" s="1"/>
     </row>
-    <row r="407">
+    <row r="407" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A407" s="1"/>
       <c r="B407" s="1"/>
       <c r="C407" s="7"/>
@@ -12885,7 +12929,7 @@
       <c r="AA407" s="1"/>
       <c r="AB407" s="1"/>
     </row>
-    <row r="408">
+    <row r="408" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A408" s="1"/>
       <c r="B408" s="1"/>
       <c r="C408" s="7"/>
@@ -12915,7 +12959,7 @@
       <c r="AA408" s="1"/>
       <c r="AB408" s="1"/>
     </row>
-    <row r="409">
+    <row r="409" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A409" s="1"/>
       <c r="B409" s="1"/>
       <c r="C409" s="7"/>
@@ -12945,7 +12989,7 @@
       <c r="AA409" s="1"/>
       <c r="AB409" s="1"/>
     </row>
-    <row r="410">
+    <row r="410" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A410" s="1"/>
       <c r="B410" s="1"/>
       <c r="C410" s="7"/>
@@ -12975,7 +13019,7 @@
       <c r="AA410" s="1"/>
       <c r="AB410" s="1"/>
     </row>
-    <row r="411">
+    <row r="411" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="7"/>
@@ -13005,7 +13049,7 @@
       <c r="AA411" s="1"/>
       <c r="AB411" s="1"/>
     </row>
-    <row r="412">
+    <row r="412" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A412" s="1"/>
       <c r="B412" s="1"/>
       <c r="C412" s="7"/>
@@ -13035,7 +13079,7 @@
       <c r="AA412" s="1"/>
       <c r="AB412" s="1"/>
     </row>
-    <row r="413">
+    <row r="413" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A413" s="1"/>
       <c r="B413" s="1"/>
       <c r="C413" s="7"/>
@@ -13065,7 +13109,7 @@
       <c r="AA413" s="1"/>
       <c r="AB413" s="1"/>
     </row>
-    <row r="414">
+    <row r="414" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A414" s="1"/>
       <c r="B414" s="1"/>
       <c r="C414" s="7"/>
@@ -13095,7 +13139,7 @@
       <c r="AA414" s="1"/>
       <c r="AB414" s="1"/>
     </row>
-    <row r="415">
+    <row r="415" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="C415" s="7"/>
@@ -13125,7 +13169,7 @@
       <c r="AA415" s="1"/>
       <c r="AB415" s="1"/>
     </row>
-    <row r="416">
+    <row r="416" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="7"/>
@@ -13155,7 +13199,7 @@
       <c r="AA416" s="1"/>
       <c r="AB416" s="1"/>
     </row>
-    <row r="417">
+    <row r="417" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A417" s="1"/>
       <c r="B417" s="1"/>
       <c r="C417" s="7"/>
@@ -13185,7 +13229,7 @@
       <c r="AA417" s="1"/>
       <c r="AB417" s="1"/>
     </row>
-    <row r="418">
+    <row r="418" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A418" s="1"/>
       <c r="B418" s="1"/>
       <c r="C418" s="7"/>
@@ -13215,7 +13259,7 @@
       <c r="AA418" s="1"/>
       <c r="AB418" s="1"/>
     </row>
-    <row r="419">
+    <row r="419" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A419" s="1"/>
       <c r="B419" s="1"/>
       <c r="C419" s="7"/>
@@ -13245,7 +13289,7 @@
       <c r="AA419" s="1"/>
       <c r="AB419" s="1"/>
     </row>
-    <row r="420">
+    <row r="420" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A420" s="1"/>
       <c r="B420" s="1"/>
       <c r="C420" s="7"/>
@@ -13275,7 +13319,7 @@
       <c r="AA420" s="1"/>
       <c r="AB420" s="1"/>
     </row>
-    <row r="421">
+    <row r="421" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A421" s="1"/>
       <c r="B421" s="1"/>
       <c r="C421" s="7"/>
@@ -13305,7 +13349,7 @@
       <c r="AA421" s="1"/>
       <c r="AB421" s="1"/>
     </row>
-    <row r="422">
+    <row r="422" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A422" s="1"/>
       <c r="B422" s="1"/>
       <c r="C422" s="7"/>
@@ -13335,7 +13379,7 @@
       <c r="AA422" s="1"/>
       <c r="AB422" s="1"/>
     </row>
-    <row r="423">
+    <row r="423" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A423" s="1"/>
       <c r="B423" s="1"/>
       <c r="C423" s="7"/>
@@ -13365,7 +13409,7 @@
       <c r="AA423" s="1"/>
       <c r="AB423" s="1"/>
     </row>
-    <row r="424">
+    <row r="424" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A424" s="1"/>
       <c r="B424" s="1"/>
       <c r="C424" s="7"/>
@@ -13395,7 +13439,7 @@
       <c r="AA424" s="1"/>
       <c r="AB424" s="1"/>
     </row>
-    <row r="425">
+    <row r="425" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A425" s="1"/>
       <c r="B425" s="1"/>
       <c r="C425" s="7"/>
@@ -13425,7 +13469,7 @@
       <c r="AA425" s="1"/>
       <c r="AB425" s="1"/>
     </row>
-    <row r="426">
+    <row r="426" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A426" s="1"/>
       <c r="B426" s="1"/>
       <c r="C426" s="7"/>
@@ -13455,7 +13499,7 @@
       <c r="AA426" s="1"/>
       <c r="AB426" s="1"/>
     </row>
-    <row r="427">
+    <row r="427" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A427" s="1"/>
       <c r="B427" s="1"/>
       <c r="C427" s="7"/>
@@ -13485,7 +13529,7 @@
       <c r="AA427" s="1"/>
       <c r="AB427" s="1"/>
     </row>
-    <row r="428">
+    <row r="428" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A428" s="1"/>
       <c r="B428" s="1"/>
       <c r="C428" s="7"/>
@@ -13515,7 +13559,7 @@
       <c r="AA428" s="1"/>
       <c r="AB428" s="1"/>
     </row>
-    <row r="429">
+    <row r="429" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="7"/>
@@ -13545,7 +13589,7 @@
       <c r="AA429" s="1"/>
       <c r="AB429" s="1"/>
     </row>
-    <row r="430">
+    <row r="430" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="7"/>
@@ -13575,7 +13619,7 @@
       <c r="AA430" s="1"/>
       <c r="AB430" s="1"/>
     </row>
-    <row r="431">
+    <row r="431" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A431" s="1"/>
       <c r="B431" s="1"/>
       <c r="C431" s="7"/>
@@ -13605,7 +13649,7 @@
       <c r="AA431" s="1"/>
       <c r="AB431" s="1"/>
     </row>
-    <row r="432">
+    <row r="432" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A432" s="1"/>
       <c r="B432" s="1"/>
       <c r="C432" s="7"/>
@@ -13635,7 +13679,7 @@
       <c r="AA432" s="1"/>
       <c r="AB432" s="1"/>
     </row>
-    <row r="433">
+    <row r="433" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A433" s="1"/>
       <c r="B433" s="1"/>
       <c r="C433" s="7"/>
@@ -13665,7 +13709,7 @@
       <c r="AA433" s="1"/>
       <c r="AB433" s="1"/>
     </row>
-    <row r="434">
+    <row r="434" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A434" s="1"/>
       <c r="B434" s="1"/>
       <c r="C434" s="7"/>
@@ -13695,7 +13739,7 @@
       <c r="AA434" s="1"/>
       <c r="AB434" s="1"/>
     </row>
-    <row r="435">
+    <row r="435" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A435" s="1"/>
       <c r="B435" s="1"/>
       <c r="C435" s="7"/>
@@ -13725,7 +13769,7 @@
       <c r="AA435" s="1"/>
       <c r="AB435" s="1"/>
     </row>
-    <row r="436">
+    <row r="436" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A436" s="1"/>
       <c r="B436" s="1"/>
       <c r="C436" s="7"/>
@@ -13755,7 +13799,7 @@
       <c r="AA436" s="1"/>
       <c r="AB436" s="1"/>
     </row>
-    <row r="437">
+    <row r="437" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A437" s="1"/>
       <c r="B437" s="1"/>
       <c r="C437" s="7"/>
@@ -13785,7 +13829,7 @@
       <c r="AA437" s="1"/>
       <c r="AB437" s="1"/>
     </row>
-    <row r="438">
+    <row r="438" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A438" s="1"/>
       <c r="B438" s="1"/>
       <c r="C438" s="7"/>
@@ -13815,7 +13859,7 @@
       <c r="AA438" s="1"/>
       <c r="AB438" s="1"/>
     </row>
-    <row r="439">
+    <row r="439" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="C439" s="7"/>
@@ -13845,7 +13889,7 @@
       <c r="AA439" s="1"/>
       <c r="AB439" s="1"/>
     </row>
-    <row r="440">
+    <row r="440" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A440" s="1"/>
       <c r="B440" s="1"/>
       <c r="C440" s="7"/>
@@ -13875,7 +13919,7 @@
       <c r="AA440" s="1"/>
       <c r="AB440" s="1"/>
     </row>
-    <row r="441">
+    <row r="441" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A441" s="1"/>
       <c r="B441" s="1"/>
       <c r="C441" s="7"/>
@@ -13905,7 +13949,7 @@
       <c r="AA441" s="1"/>
       <c r="AB441" s="1"/>
     </row>
-    <row r="442">
+    <row r="442" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A442" s="1"/>
       <c r="B442" s="1"/>
       <c r="C442" s="7"/>
@@ -13935,7 +13979,7 @@
       <c r="AA442" s="1"/>
       <c r="AB442" s="1"/>
     </row>
-    <row r="443">
+    <row r="443" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A443" s="1"/>
       <c r="B443" s="1"/>
       <c r="C443" s="7"/>
@@ -13965,7 +14009,7 @@
       <c r="AA443" s="1"/>
       <c r="AB443" s="1"/>
     </row>
-    <row r="444">
+    <row r="444" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A444" s="1"/>
       <c r="B444" s="1"/>
       <c r="C444" s="7"/>
@@ -13995,7 +14039,7 @@
       <c r="AA444" s="1"/>
       <c r="AB444" s="1"/>
     </row>
-    <row r="445">
+    <row r="445" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A445" s="1"/>
       <c r="B445" s="1"/>
       <c r="C445" s="7"/>
@@ -14025,7 +14069,7 @@
       <c r="AA445" s="1"/>
       <c r="AB445" s="1"/>
     </row>
-    <row r="446">
+    <row r="446" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A446" s="1"/>
       <c r="B446" s="1"/>
       <c r="C446" s="7"/>
@@ -14055,7 +14099,7 @@
       <c r="AA446" s="1"/>
       <c r="AB446" s="1"/>
     </row>
-    <row r="447">
+    <row r="447" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A447" s="1"/>
       <c r="B447" s="1"/>
       <c r="C447" s="7"/>
@@ -14085,7 +14129,7 @@
       <c r="AA447" s="1"/>
       <c r="AB447" s="1"/>
     </row>
-    <row r="448">
+    <row r="448" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A448" s="1"/>
       <c r="B448" s="1"/>
       <c r="C448" s="7"/>
@@ -14115,7 +14159,7 @@
       <c r="AA448" s="1"/>
       <c r="AB448" s="1"/>
     </row>
-    <row r="449">
+    <row r="449" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A449" s="1"/>
       <c r="B449" s="1"/>
       <c r="C449" s="7"/>
@@ -14145,7 +14189,7 @@
       <c r="AA449" s="1"/>
       <c r="AB449" s="1"/>
     </row>
-    <row r="450">
+    <row r="450" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="7"/>
@@ -14175,7 +14219,7 @@
       <c r="AA450" s="1"/>
       <c r="AB450" s="1"/>
     </row>
-    <row r="451">
+    <row r="451" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A451" s="1"/>
       <c r="B451" s="1"/>
       <c r="C451" s="7"/>
@@ -14205,7 +14249,7 @@
       <c r="AA451" s="1"/>
       <c r="AB451" s="1"/>
     </row>
-    <row r="452">
+    <row r="452" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A452" s="1"/>
       <c r="B452" s="1"/>
       <c r="C452" s="7"/>
@@ -14235,7 +14279,7 @@
       <c r="AA452" s="1"/>
       <c r="AB452" s="1"/>
     </row>
-    <row r="453">
+    <row r="453" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A453" s="1"/>
       <c r="B453" s="1"/>
       <c r="C453" s="7"/>
@@ -14265,7 +14309,7 @@
       <c r="AA453" s="1"/>
       <c r="AB453" s="1"/>
     </row>
-    <row r="454">
+    <row r="454" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A454" s="1"/>
       <c r="B454" s="1"/>
       <c r="C454" s="7"/>
@@ -14295,7 +14339,7 @@
       <c r="AA454" s="1"/>
       <c r="AB454" s="1"/>
     </row>
-    <row r="455">
+    <row r="455" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A455" s="1"/>
       <c r="B455" s="1"/>
       <c r="C455" s="7"/>
@@ -14325,7 +14369,7 @@
       <c r="AA455" s="1"/>
       <c r="AB455" s="1"/>
     </row>
-    <row r="456">
+    <row r="456" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A456" s="1"/>
       <c r="B456" s="1"/>
       <c r="C456" s="7"/>
@@ -14355,7 +14399,7 @@
       <c r="AA456" s="1"/>
       <c r="AB456" s="1"/>
     </row>
-    <row r="457">
+    <row r="457" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A457" s="1"/>
       <c r="B457" s="1"/>
       <c r="C457" s="7"/>
@@ -14385,7 +14429,7 @@
       <c r="AA457" s="1"/>
       <c r="AB457" s="1"/>
     </row>
-    <row r="458">
+    <row r="458" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A458" s="1"/>
       <c r="B458" s="1"/>
       <c r="C458" s="7"/>
@@ -14415,7 +14459,7 @@
       <c r="AA458" s="1"/>
       <c r="AB458" s="1"/>
     </row>
-    <row r="459">
+    <row r="459" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A459" s="1"/>
       <c r="B459" s="1"/>
       <c r="C459" s="7"/>
@@ -14445,7 +14489,7 @@
       <c r="AA459" s="1"/>
       <c r="AB459" s="1"/>
     </row>
-    <row r="460">
+    <row r="460" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A460" s="1"/>
       <c r="B460" s="1"/>
       <c r="C460" s="7"/>
@@ -14475,7 +14519,7 @@
       <c r="AA460" s="1"/>
       <c r="AB460" s="1"/>
     </row>
-    <row r="461">
+    <row r="461" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A461" s="1"/>
       <c r="B461" s="1"/>
       <c r="C461" s="7"/>
@@ -14505,7 +14549,7 @@
       <c r="AA461" s="1"/>
       <c r="AB461" s="1"/>
     </row>
-    <row r="462">
+    <row r="462" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A462" s="1"/>
       <c r="B462" s="1"/>
       <c r="C462" s="7"/>
@@ -14535,7 +14579,7 @@
       <c r="AA462" s="1"/>
       <c r="AB462" s="1"/>
     </row>
-    <row r="463">
+    <row r="463" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A463" s="1"/>
       <c r="B463" s="1"/>
       <c r="C463" s="7"/>
@@ -14565,7 +14609,7 @@
       <c r="AA463" s="1"/>
       <c r="AB463" s="1"/>
     </row>
-    <row r="464">
+    <row r="464" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A464" s="1"/>
       <c r="B464" s="1"/>
       <c r="C464" s="7"/>
@@ -14595,7 +14639,7 @@
       <c r="AA464" s="1"/>
       <c r="AB464" s="1"/>
     </row>
-    <row r="465">
+    <row r="465" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A465" s="1"/>
       <c r="B465" s="1"/>
       <c r="C465" s="7"/>
@@ -14625,7 +14669,7 @@
       <c r="AA465" s="1"/>
       <c r="AB465" s="1"/>
     </row>
-    <row r="466">
+    <row r="466" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A466" s="1"/>
       <c r="B466" s="1"/>
       <c r="C466" s="7"/>
@@ -14655,7 +14699,7 @@
       <c r="AA466" s="1"/>
       <c r="AB466" s="1"/>
     </row>
-    <row r="467">
+    <row r="467" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A467" s="1"/>
       <c r="B467" s="1"/>
       <c r="C467" s="7"/>
@@ -14685,7 +14729,7 @@
       <c r="AA467" s="1"/>
       <c r="AB467" s="1"/>
     </row>
-    <row r="468">
+    <row r="468" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A468" s="1"/>
       <c r="B468" s="1"/>
       <c r="C468" s="7"/>
@@ -14715,7 +14759,7 @@
       <c r="AA468" s="1"/>
       <c r="AB468" s="1"/>
     </row>
-    <row r="469">
+    <row r="469" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A469" s="1"/>
       <c r="B469" s="1"/>
       <c r="C469" s="7"/>
@@ -14745,7 +14789,7 @@
       <c r="AA469" s="1"/>
       <c r="AB469" s="1"/>
     </row>
-    <row r="470">
+    <row r="470" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A470" s="1"/>
       <c r="B470" s="1"/>
       <c r="C470" s="7"/>
@@ -14775,7 +14819,7 @@
       <c r="AA470" s="1"/>
       <c r="AB470" s="1"/>
     </row>
-    <row r="471">
+    <row r="471" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A471" s="1"/>
       <c r="B471" s="1"/>
       <c r="C471" s="7"/>
@@ -14805,7 +14849,7 @@
       <c r="AA471" s="1"/>
       <c r="AB471" s="1"/>
     </row>
-    <row r="472">
+    <row r="472" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A472" s="1"/>
       <c r="B472" s="1"/>
       <c r="C472" s="7"/>
@@ -14835,7 +14879,7 @@
       <c r="AA472" s="1"/>
       <c r="AB472" s="1"/>
     </row>
-    <row r="473">
+    <row r="473" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A473" s="1"/>
       <c r="B473" s="1"/>
       <c r="C473" s="7"/>
@@ -14865,7 +14909,7 @@
       <c r="AA473" s="1"/>
       <c r="AB473" s="1"/>
     </row>
-    <row r="474">
+    <row r="474" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A474" s="1"/>
       <c r="B474" s="1"/>
       <c r="C474" s="7"/>
@@ -14895,7 +14939,7 @@
       <c r="AA474" s="1"/>
       <c r="AB474" s="1"/>
     </row>
-    <row r="475">
+    <row r="475" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A475" s="1"/>
       <c r="B475" s="1"/>
       <c r="C475" s="7"/>
@@ -14925,7 +14969,7 @@
       <c r="AA475" s="1"/>
       <c r="AB475" s="1"/>
     </row>
-    <row r="476">
+    <row r="476" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="C476" s="7"/>
@@ -14955,7 +14999,7 @@
       <c r="AA476" s="1"/>
       <c r="AB476" s="1"/>
     </row>
-    <row r="477">
+    <row r="477" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A477" s="1"/>
       <c r="B477" s="1"/>
       <c r="C477" s="7"/>
@@ -14985,7 +15029,7 @@
       <c r="AA477" s="1"/>
       <c r="AB477" s="1"/>
     </row>
-    <row r="478">
+    <row r="478" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A478" s="1"/>
       <c r="B478" s="1"/>
       <c r="C478" s="7"/>
@@ -15015,7 +15059,7 @@
       <c r="AA478" s="1"/>
       <c r="AB478" s="1"/>
     </row>
-    <row r="479">
+    <row r="479" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A479" s="1"/>
       <c r="B479" s="1"/>
       <c r="C479" s="7"/>
@@ -15045,7 +15089,7 @@
       <c r="AA479" s="1"/>
       <c r="AB479" s="1"/>
     </row>
-    <row r="480">
+    <row r="480" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A480" s="1"/>
       <c r="B480" s="1"/>
       <c r="C480" s="7"/>
@@ -15075,7 +15119,7 @@
       <c r="AA480" s="1"/>
       <c r="AB480" s="1"/>
     </row>
-    <row r="481">
+    <row r="481" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A481" s="1"/>
       <c r="B481" s="1"/>
       <c r="C481" s="7"/>
@@ -15105,7 +15149,7 @@
       <c r="AA481" s="1"/>
       <c r="AB481" s="1"/>
     </row>
-    <row r="482">
+    <row r="482" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A482" s="1"/>
       <c r="B482" s="1"/>
       <c r="C482" s="7"/>
@@ -15135,7 +15179,7 @@
       <c r="AA482" s="1"/>
       <c r="AB482" s="1"/>
     </row>
-    <row r="483">
+    <row r="483" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A483" s="1"/>
       <c r="B483" s="1"/>
       <c r="C483" s="7"/>
@@ -15165,7 +15209,7 @@
       <c r="AA483" s="1"/>
       <c r="AB483" s="1"/>
     </row>
-    <row r="484">
+    <row r="484" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A484" s="1"/>
       <c r="B484" s="1"/>
       <c r="C484" s="7"/>
@@ -15195,7 +15239,7 @@
       <c r="AA484" s="1"/>
       <c r="AB484" s="1"/>
     </row>
-    <row r="485">
+    <row r="485" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A485" s="1"/>
       <c r="B485" s="1"/>
       <c r="C485" s="7"/>
@@ -15225,7 +15269,7 @@
       <c r="AA485" s="1"/>
       <c r="AB485" s="1"/>
     </row>
-    <row r="486">
+    <row r="486" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A486" s="1"/>
       <c r="B486" s="1"/>
       <c r="C486" s="7"/>
@@ -15255,7 +15299,7 @@
       <c r="AA486" s="1"/>
       <c r="AB486" s="1"/>
     </row>
-    <row r="487">
+    <row r="487" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A487" s="1"/>
       <c r="B487" s="1"/>
       <c r="C487" s="7"/>
@@ -15285,7 +15329,7 @@
       <c r="AA487" s="1"/>
       <c r="AB487" s="1"/>
     </row>
-    <row r="488">
+    <row r="488" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A488" s="1"/>
       <c r="B488" s="1"/>
       <c r="C488" s="7"/>
@@ -15315,7 +15359,7 @@
       <c r="AA488" s="1"/>
       <c r="AB488" s="1"/>
     </row>
-    <row r="489">
+    <row r="489" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A489" s="1"/>
       <c r="B489" s="1"/>
       <c r="C489" s="7"/>
@@ -15345,7 +15389,7 @@
       <c r="AA489" s="1"/>
       <c r="AB489" s="1"/>
     </row>
-    <row r="490">
+    <row r="490" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A490" s="1"/>
       <c r="B490" s="1"/>
       <c r="C490" s="7"/>
@@ -15375,7 +15419,7 @@
       <c r="AA490" s="1"/>
       <c r="AB490" s="1"/>
     </row>
-    <row r="491">
+    <row r="491" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A491" s="1"/>
       <c r="B491" s="1"/>
       <c r="C491" s="7"/>
@@ -15405,7 +15449,7 @@
       <c r="AA491" s="1"/>
       <c r="AB491" s="1"/>
     </row>
-    <row r="492">
+    <row r="492" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A492" s="1"/>
       <c r="B492" s="1"/>
       <c r="C492" s="7"/>
@@ -15435,7 +15479,7 @@
       <c r="AA492" s="1"/>
       <c r="AB492" s="1"/>
     </row>
-    <row r="493">
+    <row r="493" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A493" s="1"/>
       <c r="B493" s="1"/>
       <c r="C493" s="7"/>
@@ -15465,7 +15509,7 @@
       <c r="AA493" s="1"/>
       <c r="AB493" s="1"/>
     </row>
-    <row r="494">
+    <row r="494" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A494" s="1"/>
       <c r="B494" s="1"/>
       <c r="C494" s="7"/>
@@ -15495,7 +15539,7 @@
       <c r="AA494" s="1"/>
       <c r="AB494" s="1"/>
     </row>
-    <row r="495">
+    <row r="495" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A495" s="1"/>
       <c r="B495" s="1"/>
       <c r="C495" s="7"/>
@@ -15525,7 +15569,7 @@
       <c r="AA495" s="1"/>
       <c r="AB495" s="1"/>
     </row>
-    <row r="496">
+    <row r="496" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A496" s="1"/>
       <c r="B496" s="1"/>
       <c r="C496" s="7"/>
@@ -15555,7 +15599,7 @@
       <c r="AA496" s="1"/>
       <c r="AB496" s="1"/>
     </row>
-    <row r="497">
+    <row r="497" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A497" s="1"/>
       <c r="B497" s="1"/>
       <c r="C497" s="7"/>
@@ -15585,7 +15629,7 @@
       <c r="AA497" s="1"/>
       <c r="AB497" s="1"/>
     </row>
-    <row r="498">
+    <row r="498" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A498" s="1"/>
       <c r="B498" s="1"/>
       <c r="C498" s="7"/>
@@ -15615,7 +15659,7 @@
       <c r="AA498" s="1"/>
       <c r="AB498" s="1"/>
     </row>
-    <row r="499">
+    <row r="499" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A499" s="1"/>
       <c r="B499" s="1"/>
       <c r="C499" s="7"/>
@@ -15645,7 +15689,7 @@
       <c r="AA499" s="1"/>
       <c r="AB499" s="1"/>
     </row>
-    <row r="500">
+    <row r="500" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A500" s="1"/>
       <c r="B500" s="1"/>
       <c r="C500" s="7"/>
@@ -15675,7 +15719,7 @@
       <c r="AA500" s="1"/>
       <c r="AB500" s="1"/>
     </row>
-    <row r="501">
+    <row r="501" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A501" s="1"/>
       <c r="B501" s="1"/>
       <c r="C501" s="7"/>
@@ -15705,7 +15749,7 @@
       <c r="AA501" s="1"/>
       <c r="AB501" s="1"/>
     </row>
-    <row r="502">
+    <row r="502" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A502" s="1"/>
       <c r="B502" s="1"/>
       <c r="C502" s="7"/>
@@ -15735,7 +15779,7 @@
       <c r="AA502" s="1"/>
       <c r="AB502" s="1"/>
     </row>
-    <row r="503">
+    <row r="503" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A503" s="1"/>
       <c r="B503" s="1"/>
       <c r="C503" s="7"/>
@@ -15765,7 +15809,7 @@
       <c r="AA503" s="1"/>
       <c r="AB503" s="1"/>
     </row>
-    <row r="504">
+    <row r="504" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A504" s="1"/>
       <c r="B504" s="1"/>
       <c r="C504" s="7"/>
@@ -15795,7 +15839,7 @@
       <c r="AA504" s="1"/>
       <c r="AB504" s="1"/>
     </row>
-    <row r="505">
+    <row r="505" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A505" s="1"/>
       <c r="B505" s="1"/>
       <c r="C505" s="7"/>
@@ -15825,7 +15869,7 @@
       <c r="AA505" s="1"/>
       <c r="AB505" s="1"/>
     </row>
-    <row r="506">
+    <row r="506" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A506" s="1"/>
       <c r="B506" s="1"/>
       <c r="C506" s="7"/>
@@ -15855,7 +15899,7 @@
       <c r="AA506" s="1"/>
       <c r="AB506" s="1"/>
     </row>
-    <row r="507">
+    <row r="507" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A507" s="1"/>
       <c r="B507" s="1"/>
       <c r="C507" s="7"/>
@@ -15885,7 +15929,7 @@
       <c r="AA507" s="1"/>
       <c r="AB507" s="1"/>
     </row>
-    <row r="508">
+    <row r="508" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A508" s="1"/>
       <c r="B508" s="1"/>
       <c r="C508" s="7"/>
@@ -15915,7 +15959,7 @@
       <c r="AA508" s="1"/>
       <c r="AB508" s="1"/>
     </row>
-    <row r="509">
+    <row r="509" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A509" s="1"/>
       <c r="B509" s="1"/>
       <c r="C509" s="7"/>
@@ -15945,7 +15989,7 @@
       <c r="AA509" s="1"/>
       <c r="AB509" s="1"/>
     </row>
-    <row r="510">
+    <row r="510" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A510" s="1"/>
       <c r="B510" s="1"/>
       <c r="C510" s="7"/>
@@ -15975,7 +16019,7 @@
       <c r="AA510" s="1"/>
       <c r="AB510" s="1"/>
     </row>
-    <row r="511">
+    <row r="511" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A511" s="1"/>
       <c r="B511" s="1"/>
       <c r="C511" s="7"/>
@@ -16005,7 +16049,7 @@
       <c r="AA511" s="1"/>
       <c r="AB511" s="1"/>
     </row>
-    <row r="512">
+    <row r="512" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A512" s="1"/>
       <c r="B512" s="1"/>
       <c r="C512" s="7"/>
@@ -16035,7 +16079,7 @@
       <c r="AA512" s="1"/>
       <c r="AB512" s="1"/>
     </row>
-    <row r="513">
+    <row r="513" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A513" s="1"/>
       <c r="B513" s="1"/>
       <c r="C513" s="7"/>
@@ -16065,7 +16109,7 @@
       <c r="AA513" s="1"/>
       <c r="AB513" s="1"/>
     </row>
-    <row r="514">
+    <row r="514" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A514" s="1"/>
       <c r="B514" s="1"/>
       <c r="C514" s="7"/>
@@ -16095,7 +16139,7 @@
       <c r="AA514" s="1"/>
       <c r="AB514" s="1"/>
     </row>
-    <row r="515">
+    <row r="515" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A515" s="1"/>
       <c r="B515" s="1"/>
       <c r="C515" s="7"/>
@@ -16125,7 +16169,7 @@
       <c r="AA515" s="1"/>
       <c r="AB515" s="1"/>
     </row>
-    <row r="516">
+    <row r="516" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A516" s="1"/>
       <c r="B516" s="1"/>
       <c r="C516" s="7"/>
@@ -16155,7 +16199,7 @@
       <c r="AA516" s="1"/>
       <c r="AB516" s="1"/>
     </row>
-    <row r="517">
+    <row r="517" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A517" s="1"/>
       <c r="B517" s="1"/>
       <c r="C517" s="7"/>
@@ -16185,7 +16229,7 @@
       <c r="AA517" s="1"/>
       <c r="AB517" s="1"/>
     </row>
-    <row r="518">
+    <row r="518" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A518" s="1"/>
       <c r="B518" s="1"/>
       <c r="C518" s="7"/>
@@ -16215,7 +16259,7 @@
       <c r="AA518" s="1"/>
       <c r="AB518" s="1"/>
     </row>
-    <row r="519">
+    <row r="519" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A519" s="1"/>
       <c r="B519" s="1"/>
       <c r="C519" s="7"/>
@@ -16245,7 +16289,7 @@
       <c r="AA519" s="1"/>
       <c r="AB519" s="1"/>
     </row>
-    <row r="520">
+    <row r="520" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A520" s="1"/>
       <c r="B520" s="1"/>
       <c r="C520" s="7"/>
@@ -16275,7 +16319,7 @@
       <c r="AA520" s="1"/>
       <c r="AB520" s="1"/>
     </row>
-    <row r="521">
+    <row r="521" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A521" s="1"/>
       <c r="B521" s="1"/>
       <c r="C521" s="7"/>
@@ -16305,7 +16349,7 @@
       <c r="AA521" s="1"/>
       <c r="AB521" s="1"/>
     </row>
-    <row r="522">
+    <row r="522" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A522" s="1"/>
       <c r="B522" s="1"/>
       <c r="C522" s="7"/>
@@ -16335,7 +16379,7 @@
       <c r="AA522" s="1"/>
       <c r="AB522" s="1"/>
     </row>
-    <row r="523">
+    <row r="523" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A523" s="1"/>
       <c r="B523" s="1"/>
       <c r="C523" s="7"/>
@@ -16365,7 +16409,7 @@
       <c r="AA523" s="1"/>
       <c r="AB523" s="1"/>
     </row>
-    <row r="524">
+    <row r="524" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A524" s="1"/>
       <c r="B524" s="1"/>
       <c r="C524" s="7"/>
@@ -16395,7 +16439,7 @@
       <c r="AA524" s="1"/>
       <c r="AB524" s="1"/>
     </row>
-    <row r="525">
+    <row r="525" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A525" s="1"/>
       <c r="B525" s="1"/>
       <c r="C525" s="7"/>
@@ -16425,7 +16469,7 @@
       <c r="AA525" s="1"/>
       <c r="AB525" s="1"/>
     </row>
-    <row r="526">
+    <row r="526" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A526" s="1"/>
       <c r="B526" s="1"/>
       <c r="C526" s="7"/>
@@ -16455,7 +16499,7 @@
       <c r="AA526" s="1"/>
       <c r="AB526" s="1"/>
     </row>
-    <row r="527">
+    <row r="527" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A527" s="1"/>
       <c r="B527" s="1"/>
       <c r="C527" s="7"/>
@@ -16485,7 +16529,7 @@
       <c r="AA527" s="1"/>
       <c r="AB527" s="1"/>
     </row>
-    <row r="528">
+    <row r="528" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A528" s="1"/>
       <c r="B528" s="1"/>
       <c r="C528" s="7"/>
@@ -16515,7 +16559,7 @@
       <c r="AA528" s="1"/>
       <c r="AB528" s="1"/>
     </row>
-    <row r="529">
+    <row r="529" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A529" s="1"/>
       <c r="B529" s="1"/>
       <c r="C529" s="7"/>
@@ -16545,7 +16589,7 @@
       <c r="AA529" s="1"/>
       <c r="AB529" s="1"/>
     </row>
-    <row r="530">
+    <row r="530" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A530" s="1"/>
       <c r="B530" s="1"/>
       <c r="C530" s="7"/>
@@ -16575,7 +16619,7 @@
       <c r="AA530" s="1"/>
       <c r="AB530" s="1"/>
     </row>
-    <row r="531">
+    <row r="531" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A531" s="1"/>
       <c r="B531" s="1"/>
       <c r="C531" s="7"/>
@@ -16605,7 +16649,7 @@
       <c r="AA531" s="1"/>
       <c r="AB531" s="1"/>
     </row>
-    <row r="532">
+    <row r="532" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A532" s="1"/>
       <c r="B532" s="1"/>
       <c r="C532" s="7"/>
@@ -16635,7 +16679,7 @@
       <c r="AA532" s="1"/>
       <c r="AB532" s="1"/>
     </row>
-    <row r="533">
+    <row r="533" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A533" s="1"/>
       <c r="B533" s="1"/>
       <c r="C533" s="7"/>
@@ -16665,7 +16709,7 @@
       <c r="AA533" s="1"/>
       <c r="AB533" s="1"/>
     </row>
-    <row r="534">
+    <row r="534" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A534" s="1"/>
       <c r="B534" s="1"/>
       <c r="C534" s="7"/>
@@ -16695,7 +16739,7 @@
       <c r="AA534" s="1"/>
       <c r="AB534" s="1"/>
     </row>
-    <row r="535">
+    <row r="535" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A535" s="1"/>
       <c r="B535" s="1"/>
       <c r="C535" s="7"/>
@@ -16725,7 +16769,7 @@
       <c r="AA535" s="1"/>
       <c r="AB535" s="1"/>
     </row>
-    <row r="536">
+    <row r="536" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A536" s="1"/>
       <c r="B536" s="1"/>
       <c r="C536" s="7"/>
@@ -16755,7 +16799,7 @@
       <c r="AA536" s="1"/>
       <c r="AB536" s="1"/>
     </row>
-    <row r="537">
+    <row r="537" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A537" s="1"/>
       <c r="B537" s="1"/>
       <c r="C537" s="7"/>
@@ -16785,7 +16829,7 @@
       <c r="AA537" s="1"/>
       <c r="AB537" s="1"/>
     </row>
-    <row r="538">
+    <row r="538" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A538" s="1"/>
       <c r="B538" s="1"/>
       <c r="C538" s="7"/>
@@ -16815,7 +16859,7 @@
       <c r="AA538" s="1"/>
       <c r="AB538" s="1"/>
     </row>
-    <row r="539">
+    <row r="539" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A539" s="1"/>
       <c r="B539" s="1"/>
       <c r="C539" s="7"/>
@@ -16845,7 +16889,7 @@
       <c r="AA539" s="1"/>
       <c r="AB539" s="1"/>
     </row>
-    <row r="540">
+    <row r="540" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A540" s="1"/>
       <c r="B540" s="1"/>
       <c r="C540" s="7"/>
@@ -16875,7 +16919,7 @@
       <c r="AA540" s="1"/>
       <c r="AB540" s="1"/>
     </row>
-    <row r="541">
+    <row r="541" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A541" s="1"/>
       <c r="B541" s="1"/>
       <c r="C541" s="7"/>
@@ -16905,7 +16949,7 @@
       <c r="AA541" s="1"/>
       <c r="AB541" s="1"/>
     </row>
-    <row r="542">
+    <row r="542" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A542" s="1"/>
       <c r="B542" s="1"/>
       <c r="C542" s="7"/>
@@ -16935,7 +16979,7 @@
       <c r="AA542" s="1"/>
       <c r="AB542" s="1"/>
     </row>
-    <row r="543">
+    <row r="543" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A543" s="1"/>
       <c r="B543" s="1"/>
       <c r="C543" s="7"/>
@@ -16965,7 +17009,7 @@
       <c r="AA543" s="1"/>
       <c r="AB543" s="1"/>
     </row>
-    <row r="544">
+    <row r="544" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A544" s="1"/>
       <c r="B544" s="1"/>
       <c r="C544" s="7"/>
@@ -16995,7 +17039,7 @@
       <c r="AA544" s="1"/>
       <c r="AB544" s="1"/>
     </row>
-    <row r="545">
+    <row r="545" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A545" s="1"/>
       <c r="B545" s="1"/>
       <c r="C545" s="7"/>
@@ -17025,7 +17069,7 @@
       <c r="AA545" s="1"/>
       <c r="AB545" s="1"/>
     </row>
-    <row r="546">
+    <row r="546" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A546" s="1"/>
       <c r="B546" s="1"/>
       <c r="C546" s="7"/>
@@ -17055,7 +17099,7 @@
       <c r="AA546" s="1"/>
       <c r="AB546" s="1"/>
     </row>
-    <row r="547">
+    <row r="547" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A547" s="1"/>
       <c r="B547" s="1"/>
       <c r="C547" s="7"/>
@@ -17085,7 +17129,7 @@
       <c r="AA547" s="1"/>
       <c r="AB547" s="1"/>
     </row>
-    <row r="548">
+    <row r="548" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A548" s="1"/>
       <c r="B548" s="1"/>
       <c r="C548" s="7"/>
@@ -17115,7 +17159,7 @@
       <c r="AA548" s="1"/>
       <c r="AB548" s="1"/>
     </row>
-    <row r="549">
+    <row r="549" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A549" s="1"/>
       <c r="B549" s="1"/>
       <c r="C549" s="7"/>
@@ -17145,7 +17189,7 @@
       <c r="AA549" s="1"/>
       <c r="AB549" s="1"/>
     </row>
-    <row r="550">
+    <row r="550" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A550" s="1"/>
       <c r="B550" s="1"/>
       <c r="C550" s="7"/>
@@ -17175,7 +17219,7 @@
       <c r="AA550" s="1"/>
       <c r="AB550" s="1"/>
     </row>
-    <row r="551">
+    <row r="551" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A551" s="1"/>
       <c r="B551" s="1"/>
       <c r="C551" s="7"/>
@@ -17205,7 +17249,7 @@
       <c r="AA551" s="1"/>
       <c r="AB551" s="1"/>
     </row>
-    <row r="552">
+    <row r="552" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A552" s="1"/>
       <c r="B552" s="1"/>
       <c r="C552" s="7"/>
@@ -17235,7 +17279,7 @@
       <c r="AA552" s="1"/>
       <c r="AB552" s="1"/>
     </row>
-    <row r="553">
+    <row r="553" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A553" s="1"/>
       <c r="B553" s="1"/>
       <c r="C553" s="7"/>
@@ -17265,7 +17309,7 @@
       <c r="AA553" s="1"/>
       <c r="AB553" s="1"/>
     </row>
-    <row r="554">
+    <row r="554" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A554" s="1"/>
       <c r="B554" s="1"/>
       <c r="C554" s="7"/>
@@ -17295,7 +17339,7 @@
       <c r="AA554" s="1"/>
       <c r="AB554" s="1"/>
     </row>
-    <row r="555">
+    <row r="555" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A555" s="1"/>
       <c r="B555" s="1"/>
       <c r="C555" s="7"/>
@@ -17325,7 +17369,7 @@
       <c r="AA555" s="1"/>
       <c r="AB555" s="1"/>
     </row>
-    <row r="556">
+    <row r="556" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A556" s="1"/>
       <c r="B556" s="1"/>
       <c r="C556" s="7"/>
@@ -17355,7 +17399,7 @@
       <c r="AA556" s="1"/>
       <c r="AB556" s="1"/>
     </row>
-    <row r="557">
+    <row r="557" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A557" s="1"/>
       <c r="B557" s="1"/>
       <c r="C557" s="7"/>
@@ -17385,7 +17429,7 @@
       <c r="AA557" s="1"/>
       <c r="AB557" s="1"/>
     </row>
-    <row r="558">
+    <row r="558" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A558" s="1"/>
       <c r="B558" s="1"/>
       <c r="C558" s="7"/>
@@ -17415,7 +17459,7 @@
       <c r="AA558" s="1"/>
       <c r="AB558" s="1"/>
     </row>
-    <row r="559">
+    <row r="559" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A559" s="1"/>
       <c r="B559" s="1"/>
       <c r="C559" s="7"/>
@@ -17445,7 +17489,7 @@
       <c r="AA559" s="1"/>
       <c r="AB559" s="1"/>
     </row>
-    <row r="560">
+    <row r="560" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A560" s="1"/>
       <c r="B560" s="1"/>
       <c r="C560" s="7"/>
@@ -17475,7 +17519,7 @@
       <c r="AA560" s="1"/>
       <c r="AB560" s="1"/>
     </row>
-    <row r="561">
+    <row r="561" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A561" s="1"/>
       <c r="B561" s="1"/>
       <c r="C561" s="7"/>
@@ -17505,7 +17549,7 @@
       <c r="AA561" s="1"/>
       <c r="AB561" s="1"/>
     </row>
-    <row r="562">
+    <row r="562" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A562" s="1"/>
       <c r="B562" s="1"/>
       <c r="C562" s="7"/>
@@ -17535,7 +17579,7 @@
       <c r="AA562" s="1"/>
       <c r="AB562" s="1"/>
     </row>
-    <row r="563">
+    <row r="563" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A563" s="1"/>
       <c r="B563" s="1"/>
       <c r="C563" s="7"/>
@@ -17565,7 +17609,7 @@
       <c r="AA563" s="1"/>
       <c r="AB563" s="1"/>
     </row>
-    <row r="564">
+    <row r="564" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A564" s="1"/>
       <c r="B564" s="1"/>
       <c r="C564" s="7"/>
@@ -17595,7 +17639,7 @@
       <c r="AA564" s="1"/>
       <c r="AB564" s="1"/>
     </row>
-    <row r="565">
+    <row r="565" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A565" s="1"/>
       <c r="B565" s="1"/>
       <c r="C565" s="7"/>
@@ -17625,7 +17669,7 @@
       <c r="AA565" s="1"/>
       <c r="AB565" s="1"/>
     </row>
-    <row r="566">
+    <row r="566" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A566" s="1"/>
       <c r="B566" s="1"/>
       <c r="C566" s="7"/>
@@ -17655,7 +17699,7 @@
       <c r="AA566" s="1"/>
       <c r="AB566" s="1"/>
     </row>
-    <row r="567">
+    <row r="567" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A567" s="1"/>
       <c r="B567" s="1"/>
       <c r="C567" s="7"/>
@@ -17685,7 +17729,7 @@
       <c r="AA567" s="1"/>
       <c r="AB567" s="1"/>
     </row>
-    <row r="568">
+    <row r="568" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A568" s="1"/>
       <c r="B568" s="1"/>
       <c r="C568" s="7"/>
@@ -17715,7 +17759,7 @@
       <c r="AA568" s="1"/>
       <c r="AB568" s="1"/>
     </row>
-    <row r="569">
+    <row r="569" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A569" s="1"/>
       <c r="B569" s="1"/>
       <c r="C569" s="7"/>
@@ -17745,7 +17789,7 @@
       <c r="AA569" s="1"/>
       <c r="AB569" s="1"/>
     </row>
-    <row r="570">
+    <row r="570" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A570" s="1"/>
       <c r="B570" s="1"/>
       <c r="C570" s="7"/>
@@ -17775,7 +17819,7 @@
       <c r="AA570" s="1"/>
       <c r="AB570" s="1"/>
     </row>
-    <row r="571">
+    <row r="571" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A571" s="1"/>
       <c r="B571" s="1"/>
       <c r="C571" s="7"/>
@@ -17805,7 +17849,7 @@
       <c r="AA571" s="1"/>
       <c r="AB571" s="1"/>
     </row>
-    <row r="572">
+    <row r="572" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A572" s="1"/>
       <c r="B572" s="1"/>
       <c r="C572" s="7"/>
@@ -17835,7 +17879,7 @@
       <c r="AA572" s="1"/>
       <c r="AB572" s="1"/>
     </row>
-    <row r="573">
+    <row r="573" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A573" s="1"/>
       <c r="B573" s="1"/>
       <c r="C573" s="7"/>
@@ -17865,7 +17909,7 @@
       <c r="AA573" s="1"/>
       <c r="AB573" s="1"/>
     </row>
-    <row r="574">
+    <row r="574" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A574" s="1"/>
       <c r="B574" s="1"/>
       <c r="C574" s="7"/>
@@ -17895,7 +17939,7 @@
       <c r="AA574" s="1"/>
       <c r="AB574" s="1"/>
     </row>
-    <row r="575">
+    <row r="575" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A575" s="1"/>
       <c r="B575" s="1"/>
       <c r="C575" s="7"/>
@@ -17925,7 +17969,7 @@
       <c r="AA575" s="1"/>
       <c r="AB575" s="1"/>
     </row>
-    <row r="576">
+    <row r="576" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A576" s="1"/>
       <c r="B576" s="1"/>
       <c r="C576" s="7"/>
@@ -17955,7 +17999,7 @@
       <c r="AA576" s="1"/>
       <c r="AB576" s="1"/>
     </row>
-    <row r="577">
+    <row r="577" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A577" s="1"/>
       <c r="B577" s="1"/>
       <c r="C577" s="7"/>
@@ -17985,7 +18029,7 @@
       <c r="AA577" s="1"/>
       <c r="AB577" s="1"/>
     </row>
-    <row r="578">
+    <row r="578" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A578" s="1"/>
       <c r="B578" s="1"/>
       <c r="C578" s="7"/>
@@ -18015,7 +18059,7 @@
       <c r="AA578" s="1"/>
       <c r="AB578" s="1"/>
     </row>
-    <row r="579">
+    <row r="579" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A579" s="1"/>
       <c r="B579" s="1"/>
       <c r="C579" s="7"/>
@@ -18045,7 +18089,7 @@
       <c r="AA579" s="1"/>
       <c r="AB579" s="1"/>
     </row>
-    <row r="580">
+    <row r="580" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="7"/>
@@ -18075,7 +18119,7 @@
       <c r="AA580" s="1"/>
       <c r="AB580" s="1"/>
     </row>
-    <row r="581">
+    <row r="581" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A581" s="1"/>
       <c r="B581" s="1"/>
       <c r="C581" s="7"/>
@@ -18105,7 +18149,7 @@
       <c r="AA581" s="1"/>
       <c r="AB581" s="1"/>
     </row>
-    <row r="582">
+    <row r="582" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A582" s="1"/>
       <c r="B582" s="1"/>
       <c r="C582" s="7"/>
@@ -18135,7 +18179,7 @@
       <c r="AA582" s="1"/>
       <c r="AB582" s="1"/>
     </row>
-    <row r="583">
+    <row r="583" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A583" s="1"/>
       <c r="B583" s="1"/>
       <c r="C583" s="7"/>
@@ -18165,7 +18209,7 @@
       <c r="AA583" s="1"/>
       <c r="AB583" s="1"/>
     </row>
-    <row r="584">
+    <row r="584" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A584" s="1"/>
       <c r="B584" s="1"/>
       <c r="C584" s="7"/>
@@ -18195,7 +18239,7 @@
       <c r="AA584" s="1"/>
       <c r="AB584" s="1"/>
     </row>
-    <row r="585">
+    <row r="585" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A585" s="1"/>
       <c r="B585" s="1"/>
       <c r="C585" s="7"/>
@@ -18225,7 +18269,7 @@
       <c r="AA585" s="1"/>
       <c r="AB585" s="1"/>
     </row>
-    <row r="586">
+    <row r="586" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A586" s="1"/>
       <c r="B586" s="1"/>
       <c r="C586" s="7"/>
@@ -18255,7 +18299,7 @@
       <c r="AA586" s="1"/>
       <c r="AB586" s="1"/>
     </row>
-    <row r="587">
+    <row r="587" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A587" s="1"/>
       <c r="B587" s="1"/>
       <c r="C587" s="7"/>
@@ -18285,7 +18329,7 @@
       <c r="AA587" s="1"/>
       <c r="AB587" s="1"/>
     </row>
-    <row r="588">
+    <row r="588" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A588" s="1"/>
       <c r="B588" s="1"/>
       <c r="C588" s="7"/>
@@ -18315,7 +18359,7 @@
       <c r="AA588" s="1"/>
       <c r="AB588" s="1"/>
     </row>
-    <row r="589">
+    <row r="589" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A589" s="1"/>
       <c r="B589" s="1"/>
       <c r="C589" s="7"/>
@@ -18345,7 +18389,7 @@
       <c r="AA589" s="1"/>
       <c r="AB589" s="1"/>
     </row>
-    <row r="590">
+    <row r="590" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A590" s="1"/>
       <c r="B590" s="1"/>
       <c r="C590" s="7"/>
@@ -18375,7 +18419,7 @@
       <c r="AA590" s="1"/>
       <c r="AB590" s="1"/>
     </row>
-    <row r="591">
+    <row r="591" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A591" s="1"/>
       <c r="B591" s="1"/>
       <c r="C591" s="7"/>
@@ -18405,7 +18449,7 @@
       <c r="AA591" s="1"/>
       <c r="AB591" s="1"/>
     </row>
-    <row r="592">
+    <row r="592" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A592" s="1"/>
       <c r="B592" s="1"/>
       <c r="C592" s="7"/>
@@ -18435,7 +18479,7 @@
       <c r="AA592" s="1"/>
       <c r="AB592" s="1"/>
     </row>
-    <row r="593">
+    <row r="593" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A593" s="1"/>
       <c r="B593" s="1"/>
       <c r="C593" s="7"/>
@@ -18465,7 +18509,7 @@
       <c r="AA593" s="1"/>
       <c r="AB593" s="1"/>
     </row>
-    <row r="594">
+    <row r="594" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A594" s="1"/>
       <c r="B594" s="1"/>
       <c r="C594" s="7"/>
@@ -18495,7 +18539,7 @@
       <c r="AA594" s="1"/>
       <c r="AB594" s="1"/>
     </row>
-    <row r="595">
+    <row r="595" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A595" s="1"/>
       <c r="B595" s="1"/>
       <c r="C595" s="7"/>
@@ -18525,7 +18569,7 @@
       <c r="AA595" s="1"/>
       <c r="AB595" s="1"/>
     </row>
-    <row r="596">
+    <row r="596" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A596" s="1"/>
       <c r="B596" s="1"/>
       <c r="C596" s="7"/>
@@ -18555,7 +18599,7 @@
       <c r="AA596" s="1"/>
       <c r="AB596" s="1"/>
     </row>
-    <row r="597">
+    <row r="597" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A597" s="1"/>
       <c r="B597" s="1"/>
       <c r="C597" s="7"/>
@@ -18585,7 +18629,7 @@
       <c r="AA597" s="1"/>
       <c r="AB597" s="1"/>
     </row>
-    <row r="598">
+    <row r="598" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A598" s="1"/>
       <c r="B598" s="1"/>
       <c r="C598" s="7"/>
@@ -18615,7 +18659,7 @@
       <c r="AA598" s="1"/>
       <c r="AB598" s="1"/>
     </row>
-    <row r="599">
+    <row r="599" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A599" s="1"/>
       <c r="B599" s="1"/>
       <c r="C599" s="7"/>
@@ -18645,7 +18689,7 @@
       <c r="AA599" s="1"/>
       <c r="AB599" s="1"/>
     </row>
-    <row r="600">
+    <row r="600" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A600" s="1"/>
       <c r="B600" s="1"/>
       <c r="C600" s="7"/>
@@ -18675,7 +18719,7 @@
       <c r="AA600" s="1"/>
       <c r="AB600" s="1"/>
     </row>
-    <row r="601">
+    <row r="601" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A601" s="1"/>
       <c r="B601" s="1"/>
       <c r="C601" s="7"/>
@@ -18705,7 +18749,7 @@
       <c r="AA601" s="1"/>
       <c r="AB601" s="1"/>
     </row>
-    <row r="602">
+    <row r="602" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A602" s="1"/>
       <c r="B602" s="1"/>
       <c r="C602" s="7"/>
@@ -18735,7 +18779,7 @@
       <c r="AA602" s="1"/>
       <c r="AB602" s="1"/>
     </row>
-    <row r="603">
+    <row r="603" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A603" s="1"/>
       <c r="B603" s="1"/>
       <c r="C603" s="7"/>
@@ -18765,7 +18809,7 @@
       <c r="AA603" s="1"/>
       <c r="AB603" s="1"/>
     </row>
-    <row r="604">
+    <row r="604" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A604" s="1"/>
       <c r="B604" s="1"/>
       <c r="C604" s="7"/>
@@ -18795,7 +18839,7 @@
       <c r="AA604" s="1"/>
       <c r="AB604" s="1"/>
     </row>
-    <row r="605">
+    <row r="605" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A605" s="1"/>
       <c r="B605" s="1"/>
       <c r="C605" s="7"/>
@@ -18825,7 +18869,7 @@
       <c r="AA605" s="1"/>
       <c r="AB605" s="1"/>
     </row>
-    <row r="606">
+    <row r="606" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A606" s="1"/>
       <c r="B606" s="1"/>
       <c r="C606" s="7"/>
@@ -18855,7 +18899,7 @@
       <c r="AA606" s="1"/>
       <c r="AB606" s="1"/>
     </row>
-    <row r="607">
+    <row r="607" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A607" s="1"/>
       <c r="B607" s="1"/>
       <c r="C607" s="7"/>
@@ -18885,7 +18929,7 @@
       <c r="AA607" s="1"/>
       <c r="AB607" s="1"/>
     </row>
-    <row r="608">
+    <row r="608" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A608" s="1"/>
       <c r="B608" s="1"/>
       <c r="C608" s="7"/>
@@ -18915,7 +18959,7 @@
       <c r="AA608" s="1"/>
       <c r="AB608" s="1"/>
     </row>
-    <row r="609">
+    <row r="609" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A609" s="1"/>
       <c r="B609" s="1"/>
       <c r="C609" s="7"/>
@@ -18945,7 +18989,7 @@
       <c r="AA609" s="1"/>
       <c r="AB609" s="1"/>
     </row>
-    <row r="610">
+    <row r="610" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A610" s="1"/>
       <c r="B610" s="1"/>
       <c r="C610" s="7"/>
@@ -18975,7 +19019,7 @@
       <c r="AA610" s="1"/>
       <c r="AB610" s="1"/>
     </row>
-    <row r="611">
+    <row r="611" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A611" s="1"/>
       <c r="B611" s="1"/>
       <c r="C611" s="7"/>
@@ -19005,7 +19049,7 @@
       <c r="AA611" s="1"/>
       <c r="AB611" s="1"/>
     </row>
-    <row r="612">
+    <row r="612" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A612" s="1"/>
       <c r="B612" s="1"/>
       <c r="C612" s="7"/>
@@ -19035,7 +19079,7 @@
       <c r="AA612" s="1"/>
       <c r="AB612" s="1"/>
     </row>
-    <row r="613">
+    <row r="613" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A613" s="1"/>
       <c r="B613" s="1"/>
       <c r="C613" s="7"/>
@@ -19065,7 +19109,7 @@
       <c r="AA613" s="1"/>
       <c r="AB613" s="1"/>
     </row>
-    <row r="614">
+    <row r="614" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A614" s="1"/>
       <c r="B614" s="1"/>
       <c r="C614" s="7"/>
@@ -19095,7 +19139,7 @@
       <c r="AA614" s="1"/>
       <c r="AB614" s="1"/>
     </row>
-    <row r="615">
+    <row r="615" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A615" s="1"/>
       <c r="B615" s="1"/>
       <c r="C615" s="7"/>
@@ -19125,7 +19169,7 @@
       <c r="AA615" s="1"/>
       <c r="AB615" s="1"/>
     </row>
-    <row r="616">
+    <row r="616" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A616" s="1"/>
       <c r="B616" s="1"/>
       <c r="C616" s="7"/>
@@ -19155,7 +19199,7 @@
       <c r="AA616" s="1"/>
       <c r="AB616" s="1"/>
     </row>
-    <row r="617">
+    <row r="617" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A617" s="1"/>
       <c r="B617" s="1"/>
       <c r="C617" s="7"/>
@@ -19185,7 +19229,7 @@
       <c r="AA617" s="1"/>
       <c r="AB617" s="1"/>
     </row>
-    <row r="618">
+    <row r="618" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A618" s="1"/>
       <c r="B618" s="1"/>
       <c r="C618" s="7"/>
@@ -19215,7 +19259,7 @@
       <c r="AA618" s="1"/>
       <c r="AB618" s="1"/>
     </row>
-    <row r="619">
+    <row r="619" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A619" s="1"/>
       <c r="B619" s="1"/>
       <c r="C619" s="7"/>
@@ -19245,7 +19289,7 @@
       <c r="AA619" s="1"/>
       <c r="AB619" s="1"/>
     </row>
-    <row r="620">
+    <row r="620" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A620" s="1"/>
       <c r="B620" s="1"/>
       <c r="C620" s="7"/>
@@ -19275,7 +19319,7 @@
       <c r="AA620" s="1"/>
       <c r="AB620" s="1"/>
     </row>
-    <row r="621">
+    <row r="621" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A621" s="1"/>
       <c r="B621" s="1"/>
       <c r="C621" s="7"/>
@@ -19305,7 +19349,7 @@
       <c r="AA621" s="1"/>
       <c r="AB621" s="1"/>
     </row>
-    <row r="622">
+    <row r="622" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A622" s="1"/>
       <c r="B622" s="1"/>
       <c r="C622" s="7"/>
@@ -19335,7 +19379,7 @@
       <c r="AA622" s="1"/>
       <c r="AB622" s="1"/>
     </row>
-    <row r="623">
+    <row r="623" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A623" s="1"/>
       <c r="B623" s="1"/>
       <c r="C623" s="7"/>
@@ -19365,7 +19409,7 @@
       <c r="AA623" s="1"/>
       <c r="AB623" s="1"/>
     </row>
-    <row r="624">
+    <row r="624" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A624" s="1"/>
       <c r="B624" s="1"/>
       <c r="C624" s="7"/>
@@ -19395,7 +19439,7 @@
       <c r="AA624" s="1"/>
       <c r="AB624" s="1"/>
     </row>
-    <row r="625">
+    <row r="625" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A625" s="1"/>
       <c r="B625" s="1"/>
       <c r="C625" s="7"/>
@@ -19425,7 +19469,7 @@
       <c r="AA625" s="1"/>
       <c r="AB625" s="1"/>
     </row>
-    <row r="626">
+    <row r="626" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A626" s="1"/>
       <c r="B626" s="1"/>
       <c r="C626" s="7"/>
@@ -19455,7 +19499,7 @@
       <c r="AA626" s="1"/>
       <c r="AB626" s="1"/>
     </row>
-    <row r="627">
+    <row r="627" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A627" s="1"/>
       <c r="B627" s="1"/>
       <c r="C627" s="7"/>
@@ -19485,7 +19529,7 @@
       <c r="AA627" s="1"/>
       <c r="AB627" s="1"/>
     </row>
-    <row r="628">
+    <row r="628" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A628" s="1"/>
       <c r="B628" s="1"/>
       <c r="C628" s="7"/>
@@ -19515,7 +19559,7 @@
       <c r="AA628" s="1"/>
       <c r="AB628" s="1"/>
     </row>
-    <row r="629">
+    <row r="629" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A629" s="1"/>
       <c r="B629" s="1"/>
       <c r="C629" s="7"/>
@@ -19545,7 +19589,7 @@
       <c r="AA629" s="1"/>
       <c r="AB629" s="1"/>
     </row>
-    <row r="630">
+    <row r="630" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A630" s="1"/>
       <c r="B630" s="1"/>
       <c r="C630" s="7"/>
@@ -19575,7 +19619,7 @@
       <c r="AA630" s="1"/>
       <c r="AB630" s="1"/>
     </row>
-    <row r="631">
+    <row r="631" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A631" s="1"/>
       <c r="B631" s="1"/>
       <c r="C631" s="7"/>
@@ -19605,7 +19649,7 @@
       <c r="AA631" s="1"/>
       <c r="AB631" s="1"/>
     </row>
-    <row r="632">
+    <row r="632" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A632" s="1"/>
       <c r="B632" s="1"/>
       <c r="C632" s="7"/>
@@ -19635,7 +19679,7 @@
       <c r="AA632" s="1"/>
       <c r="AB632" s="1"/>
     </row>
-    <row r="633">
+    <row r="633" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A633" s="1"/>
       <c r="B633" s="1"/>
       <c r="C633" s="7"/>
@@ -19665,7 +19709,7 @@
       <c r="AA633" s="1"/>
       <c r="AB633" s="1"/>
     </row>
-    <row r="634">
+    <row r="634" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A634" s="1"/>
       <c r="B634" s="1"/>
       <c r="C634" s="7"/>
@@ -19695,7 +19739,7 @@
       <c r="AA634" s="1"/>
       <c r="AB634" s="1"/>
     </row>
-    <row r="635">
+    <row r="635" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A635" s="1"/>
       <c r="B635" s="1"/>
       <c r="C635" s="7"/>
@@ -19725,7 +19769,7 @@
       <c r="AA635" s="1"/>
       <c r="AB635" s="1"/>
     </row>
-    <row r="636">
+    <row r="636" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A636" s="1"/>
       <c r="B636" s="1"/>
       <c r="C636" s="7"/>
@@ -19755,7 +19799,7 @@
       <c r="AA636" s="1"/>
       <c r="AB636" s="1"/>
     </row>
-    <row r="637">
+    <row r="637" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A637" s="1"/>
       <c r="B637" s="1"/>
       <c r="C637" s="7"/>
@@ -19785,7 +19829,7 @@
       <c r="AA637" s="1"/>
       <c r="AB637" s="1"/>
     </row>
-    <row r="638">
+    <row r="638" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A638" s="1"/>
       <c r="B638" s="1"/>
       <c r="C638" s="7"/>
@@ -19815,7 +19859,7 @@
       <c r="AA638" s="1"/>
       <c r="AB638" s="1"/>
     </row>
-    <row r="639">
+    <row r="639" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A639" s="1"/>
       <c r="B639" s="1"/>
       <c r="C639" s="7"/>
@@ -19845,7 +19889,7 @@
       <c r="AA639" s="1"/>
       <c r="AB639" s="1"/>
     </row>
-    <row r="640">
+    <row r="640" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A640" s="1"/>
       <c r="B640" s="1"/>
       <c r="C640" s="7"/>
@@ -19875,7 +19919,7 @@
       <c r="AA640" s="1"/>
       <c r="AB640" s="1"/>
     </row>
-    <row r="641">
+    <row r="641" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A641" s="1"/>
       <c r="B641" s="1"/>
       <c r="C641" s="7"/>
@@ -19905,7 +19949,7 @@
       <c r="AA641" s="1"/>
       <c r="AB641" s="1"/>
     </row>
-    <row r="642">
+    <row r="642" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A642" s="1"/>
       <c r="B642" s="1"/>
       <c r="C642" s="7"/>
@@ -19935,7 +19979,7 @@
       <c r="AA642" s="1"/>
       <c r="AB642" s="1"/>
     </row>
-    <row r="643">
+    <row r="643" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A643" s="1"/>
       <c r="B643" s="1"/>
       <c r="C643" s="7"/>
@@ -19965,7 +20009,7 @@
       <c r="AA643" s="1"/>
       <c r="AB643" s="1"/>
     </row>
-    <row r="644">
+    <row r="644" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A644" s="1"/>
       <c r="B644" s="1"/>
       <c r="C644" s="7"/>
@@ -19995,7 +20039,7 @@
       <c r="AA644" s="1"/>
       <c r="AB644" s="1"/>
     </row>
-    <row r="645">
+    <row r="645" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A645" s="1"/>
       <c r="B645" s="1"/>
       <c r="C645" s="7"/>
@@ -20025,7 +20069,7 @@
       <c r="AA645" s="1"/>
       <c r="AB645" s="1"/>
     </row>
-    <row r="646">
+    <row r="646" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A646" s="1"/>
       <c r="B646" s="1"/>
       <c r="C646" s="7"/>
@@ -20055,7 +20099,7 @@
       <c r="AA646" s="1"/>
       <c r="AB646" s="1"/>
     </row>
-    <row r="647">
+    <row r="647" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A647" s="1"/>
       <c r="B647" s="1"/>
       <c r="C647" s="7"/>
@@ -20085,7 +20129,7 @@
       <c r="AA647" s="1"/>
       <c r="AB647" s="1"/>
     </row>
-    <row r="648">
+    <row r="648" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A648" s="1"/>
       <c r="B648" s="1"/>
       <c r="C648" s="7"/>
@@ -20115,7 +20159,7 @@
       <c r="AA648" s="1"/>
       <c r="AB648" s="1"/>
     </row>
-    <row r="649">
+    <row r="649" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A649" s="1"/>
       <c r="B649" s="1"/>
       <c r="C649" s="7"/>
@@ -20145,7 +20189,7 @@
       <c r="AA649" s="1"/>
       <c r="AB649" s="1"/>
     </row>
-    <row r="650">
+    <row r="650" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A650" s="1"/>
       <c r="B650" s="1"/>
       <c r="C650" s="7"/>
@@ -20175,7 +20219,7 @@
       <c r="AA650" s="1"/>
       <c r="AB650" s="1"/>
     </row>
-    <row r="651">
+    <row r="651" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A651" s="1"/>
       <c r="B651" s="1"/>
       <c r="C651" s="7"/>
@@ -20205,7 +20249,7 @@
       <c r="AA651" s="1"/>
       <c r="AB651" s="1"/>
     </row>
-    <row r="652">
+    <row r="652" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A652" s="1"/>
       <c r="B652" s="1"/>
       <c r="C652" s="7"/>
@@ -20235,7 +20279,7 @@
       <c r="AA652" s="1"/>
       <c r="AB652" s="1"/>
     </row>
-    <row r="653">
+    <row r="653" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A653" s="1"/>
       <c r="B653" s="1"/>
       <c r="C653" s="7"/>
@@ -20265,7 +20309,7 @@
       <c r="AA653" s="1"/>
       <c r="AB653" s="1"/>
     </row>
-    <row r="654">
+    <row r="654" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A654" s="1"/>
       <c r="B654" s="1"/>
       <c r="C654" s="7"/>
@@ -20295,7 +20339,7 @@
       <c r="AA654" s="1"/>
       <c r="AB654" s="1"/>
     </row>
-    <row r="655">
+    <row r="655" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A655" s="1"/>
       <c r="B655" s="1"/>
       <c r="C655" s="7"/>
@@ -20325,7 +20369,7 @@
       <c r="AA655" s="1"/>
       <c r="AB655" s="1"/>
     </row>
-    <row r="656">
+    <row r="656" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A656" s="1"/>
       <c r="B656" s="1"/>
       <c r="C656" s="7"/>
@@ -20355,7 +20399,7 @@
       <c r="AA656" s="1"/>
       <c r="AB656" s="1"/>
     </row>
-    <row r="657">
+    <row r="657" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A657" s="1"/>
       <c r="B657" s="1"/>
       <c r="C657" s="7"/>
@@ -20385,7 +20429,7 @@
       <c r="AA657" s="1"/>
       <c r="AB657" s="1"/>
     </row>
-    <row r="658">
+    <row r="658" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A658" s="1"/>
       <c r="B658" s="1"/>
       <c r="C658" s="7"/>
@@ -20415,7 +20459,7 @@
       <c r="AA658" s="1"/>
       <c r="AB658" s="1"/>
     </row>
-    <row r="659">
+    <row r="659" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A659" s="1"/>
       <c r="B659" s="1"/>
       <c r="C659" s="7"/>
@@ -20445,7 +20489,7 @@
       <c r="AA659" s="1"/>
       <c r="AB659" s="1"/>
     </row>
-    <row r="660">
+    <row r="660" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A660" s="1"/>
       <c r="B660" s="1"/>
       <c r="C660" s="7"/>
@@ -20475,7 +20519,7 @@
       <c r="AA660" s="1"/>
       <c r="AB660" s="1"/>
     </row>
-    <row r="661">
+    <row r="661" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A661" s="1"/>
       <c r="B661" s="1"/>
       <c r="C661" s="7"/>
@@ -20505,7 +20549,7 @@
       <c r="AA661" s="1"/>
       <c r="AB661" s="1"/>
     </row>
-    <row r="662">
+    <row r="662" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A662" s="1"/>
       <c r="B662" s="1"/>
       <c r="C662" s="7"/>
@@ -20535,7 +20579,7 @@
       <c r="AA662" s="1"/>
       <c r="AB662" s="1"/>
     </row>
-    <row r="663">
+    <row r="663" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A663" s="1"/>
       <c r="B663" s="1"/>
       <c r="C663" s="7"/>
@@ -20565,7 +20609,7 @@
       <c r="AA663" s="1"/>
       <c r="AB663" s="1"/>
     </row>
-    <row r="664">
+    <row r="664" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A664" s="1"/>
       <c r="B664" s="1"/>
       <c r="C664" s="7"/>
@@ -20595,7 +20639,7 @@
       <c r="AA664" s="1"/>
       <c r="AB664" s="1"/>
     </row>
-    <row r="665">
+    <row r="665" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A665" s="1"/>
       <c r="B665" s="1"/>
       <c r="C665" s="7"/>
@@ -20625,7 +20669,7 @@
       <c r="AA665" s="1"/>
       <c r="AB665" s="1"/>
     </row>
-    <row r="666">
+    <row r="666" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A666" s="1"/>
       <c r="B666" s="1"/>
       <c r="C666" s="7"/>
@@ -20655,7 +20699,7 @@
       <c r="AA666" s="1"/>
       <c r="AB666" s="1"/>
     </row>
-    <row r="667">
+    <row r="667" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A667" s="1"/>
       <c r="B667" s="1"/>
       <c r="C667" s="7"/>
@@ -20685,7 +20729,7 @@
       <c r="AA667" s="1"/>
       <c r="AB667" s="1"/>
     </row>
-    <row r="668">
+    <row r="668" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A668" s="1"/>
       <c r="B668" s="1"/>
       <c r="C668" s="7"/>
@@ -20715,7 +20759,7 @@
       <c r="AA668" s="1"/>
       <c r="AB668" s="1"/>
     </row>
-    <row r="669">
+    <row r="669" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A669" s="1"/>
       <c r="B669" s="1"/>
       <c r="C669" s="7"/>
@@ -20745,7 +20789,7 @@
       <c r="AA669" s="1"/>
       <c r="AB669" s="1"/>
     </row>
-    <row r="670">
+    <row r="670" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A670" s="1"/>
       <c r="B670" s="1"/>
       <c r="C670" s="7"/>
@@ -20775,7 +20819,7 @@
       <c r="AA670" s="1"/>
       <c r="AB670" s="1"/>
     </row>
-    <row r="671">
+    <row r="671" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A671" s="1"/>
       <c r="B671" s="1"/>
       <c r="C671" s="7"/>
@@ -20805,7 +20849,7 @@
       <c r="AA671" s="1"/>
       <c r="AB671" s="1"/>
     </row>
-    <row r="672">
+    <row r="672" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A672" s="1"/>
       <c r="B672" s="1"/>
       <c r="C672" s="7"/>
@@ -20835,7 +20879,7 @@
       <c r="AA672" s="1"/>
       <c r="AB672" s="1"/>
     </row>
-    <row r="673">
+    <row r="673" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A673" s="1"/>
       <c r="B673" s="1"/>
       <c r="C673" s="7"/>
@@ -20865,7 +20909,7 @@
       <c r="AA673" s="1"/>
       <c r="AB673" s="1"/>
     </row>
-    <row r="674">
+    <row r="674" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A674" s="1"/>
       <c r="B674" s="1"/>
       <c r="C674" s="7"/>
@@ -20895,7 +20939,7 @@
       <c r="AA674" s="1"/>
       <c r="AB674" s="1"/>
     </row>
-    <row r="675">
+    <row r="675" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A675" s="1"/>
       <c r="B675" s="1"/>
       <c r="C675" s="7"/>
@@ -20925,7 +20969,7 @@
       <c r="AA675" s="1"/>
       <c r="AB675" s="1"/>
     </row>
-    <row r="676">
+    <row r="676" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A676" s="1"/>
       <c r="B676" s="1"/>
       <c r="C676" s="7"/>
@@ -20955,7 +20999,7 @@
       <c r="AA676" s="1"/>
       <c r="AB676" s="1"/>
     </row>
-    <row r="677">
+    <row r="677" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A677" s="1"/>
       <c r="B677" s="1"/>
       <c r="C677" s="7"/>
@@ -20985,7 +21029,7 @@
       <c r="AA677" s="1"/>
       <c r="AB677" s="1"/>
     </row>
-    <row r="678">
+    <row r="678" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A678" s="1"/>
       <c r="B678" s="1"/>
       <c r="C678" s="7"/>
@@ -21015,7 +21059,7 @@
       <c r="AA678" s="1"/>
       <c r="AB678" s="1"/>
     </row>
-    <row r="679">
+    <row r="679" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A679" s="1"/>
       <c r="B679" s="1"/>
       <c r="C679" s="7"/>
@@ -21045,7 +21089,7 @@
       <c r="AA679" s="1"/>
       <c r="AB679" s="1"/>
     </row>
-    <row r="680">
+    <row r="680" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A680" s="1"/>
       <c r="B680" s="1"/>
       <c r="C680" s="7"/>
@@ -21075,7 +21119,7 @@
       <c r="AA680" s="1"/>
       <c r="AB680" s="1"/>
     </row>
-    <row r="681">
+    <row r="681" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A681" s="1"/>
       <c r="B681" s="1"/>
       <c r="C681" s="7"/>
@@ -21105,7 +21149,7 @@
       <c r="AA681" s="1"/>
       <c r="AB681" s="1"/>
     </row>
-    <row r="682">
+    <row r="682" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A682" s="1"/>
       <c r="B682" s="1"/>
       <c r="C682" s="7"/>
@@ -21135,7 +21179,7 @@
       <c r="AA682" s="1"/>
       <c r="AB682" s="1"/>
     </row>
-    <row r="683">
+    <row r="683" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A683" s="1"/>
       <c r="B683" s="1"/>
       <c r="C683" s="7"/>
@@ -21165,7 +21209,7 @@
       <c r="AA683" s="1"/>
       <c r="AB683" s="1"/>
     </row>
-    <row r="684">
+    <row r="684" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A684" s="1"/>
       <c r="B684" s="1"/>
       <c r="C684" s="7"/>
@@ -21195,7 +21239,7 @@
       <c r="AA684" s="1"/>
       <c r="AB684" s="1"/>
     </row>
-    <row r="685">
+    <row r="685" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A685" s="1"/>
       <c r="B685" s="1"/>
       <c r="C685" s="7"/>
@@ -21225,7 +21269,7 @@
       <c r="AA685" s="1"/>
       <c r="AB685" s="1"/>
     </row>
-    <row r="686">
+    <row r="686" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A686" s="1"/>
       <c r="B686" s="1"/>
       <c r="C686" s="7"/>
@@ -21255,7 +21299,7 @@
       <c r="AA686" s="1"/>
       <c r="AB686" s="1"/>
     </row>
-    <row r="687">
+    <row r="687" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A687" s="1"/>
       <c r="B687" s="1"/>
       <c r="C687" s="7"/>
@@ -21285,7 +21329,7 @@
       <c r="AA687" s="1"/>
       <c r="AB687" s="1"/>
     </row>
-    <row r="688">
+    <row r="688" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A688" s="1"/>
       <c r="B688" s="1"/>
       <c r="C688" s="7"/>
@@ -21315,7 +21359,7 @@
       <c r="AA688" s="1"/>
       <c r="AB688" s="1"/>
     </row>
-    <row r="689">
+    <row r="689" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A689" s="1"/>
       <c r="B689" s="1"/>
       <c r="C689" s="7"/>
@@ -21345,7 +21389,7 @@
       <c r="AA689" s="1"/>
       <c r="AB689" s="1"/>
     </row>
-    <row r="690">
+    <row r="690" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A690" s="1"/>
       <c r="B690" s="1"/>
       <c r="C690" s="7"/>
@@ -21375,7 +21419,7 @@
       <c r="AA690" s="1"/>
       <c r="AB690" s="1"/>
     </row>
-    <row r="691">
+    <row r="691" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A691" s="1"/>
       <c r="B691" s="1"/>
       <c r="C691" s="7"/>
@@ -21405,7 +21449,7 @@
       <c r="AA691" s="1"/>
       <c r="AB691" s="1"/>
     </row>
-    <row r="692">
+    <row r="692" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A692" s="1"/>
       <c r="B692" s="1"/>
       <c r="C692" s="7"/>
@@ -21435,7 +21479,7 @@
       <c r="AA692" s="1"/>
       <c r="AB692" s="1"/>
     </row>
-    <row r="693">
+    <row r="693" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A693" s="1"/>
       <c r="B693" s="1"/>
       <c r="C693" s="7"/>
@@ -21465,7 +21509,7 @@
       <c r="AA693" s="1"/>
       <c r="AB693" s="1"/>
     </row>
-    <row r="694">
+    <row r="694" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A694" s="1"/>
       <c r="B694" s="1"/>
       <c r="C694" s="7"/>
@@ -21495,7 +21539,7 @@
       <c r="AA694" s="1"/>
       <c r="AB694" s="1"/>
     </row>
-    <row r="695">
+    <row r="695" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A695" s="1"/>
       <c r="B695" s="1"/>
       <c r="C695" s="7"/>
@@ -21525,7 +21569,7 @@
       <c r="AA695" s="1"/>
       <c r="AB695" s="1"/>
     </row>
-    <row r="696">
+    <row r="696" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A696" s="1"/>
       <c r="B696" s="1"/>
       <c r="C696" s="7"/>
@@ -21555,7 +21599,7 @@
       <c r="AA696" s="1"/>
       <c r="AB696" s="1"/>
     </row>
-    <row r="697">
+    <row r="697" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A697" s="1"/>
       <c r="B697" s="1"/>
       <c r="C697" s="7"/>
@@ -21585,7 +21629,7 @@
       <c r="AA697" s="1"/>
       <c r="AB697" s="1"/>
     </row>
-    <row r="698">
+    <row r="698" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A698" s="1"/>
       <c r="B698" s="1"/>
       <c r="C698" s="7"/>
@@ -21615,7 +21659,7 @@
       <c r="AA698" s="1"/>
       <c r="AB698" s="1"/>
     </row>
-    <row r="699">
+    <row r="699" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A699" s="1"/>
       <c r="B699" s="1"/>
       <c r="C699" s="7"/>
@@ -21645,7 +21689,7 @@
       <c r="AA699" s="1"/>
       <c r="AB699" s="1"/>
     </row>
-    <row r="700">
+    <row r="700" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A700" s="1"/>
       <c r="B700" s="1"/>
       <c r="C700" s="7"/>
@@ -21675,7 +21719,7 @@
       <c r="AA700" s="1"/>
       <c r="AB700" s="1"/>
     </row>
-    <row r="701">
+    <row r="701" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A701" s="1"/>
       <c r="B701" s="1"/>
       <c r="C701" s="7"/>
@@ -21705,7 +21749,7 @@
       <c r="AA701" s="1"/>
       <c r="AB701" s="1"/>
     </row>
-    <row r="702">
+    <row r="702" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A702" s="1"/>
       <c r="B702" s="1"/>
       <c r="C702" s="7"/>
@@ -21735,7 +21779,7 @@
       <c r="AA702" s="1"/>
       <c r="AB702" s="1"/>
     </row>
-    <row r="703">
+    <row r="703" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A703" s="1"/>
       <c r="B703" s="1"/>
       <c r="C703" s="7"/>
@@ -21765,7 +21809,7 @@
       <c r="AA703" s="1"/>
       <c r="AB703" s="1"/>
     </row>
-    <row r="704">
+    <row r="704" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A704" s="1"/>
       <c r="B704" s="1"/>
       <c r="C704" s="7"/>
@@ -21795,7 +21839,7 @@
       <c r="AA704" s="1"/>
       <c r="AB704" s="1"/>
     </row>
-    <row r="705">
+    <row r="705" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A705" s="1"/>
       <c r="B705" s="1"/>
       <c r="C705" s="7"/>
@@ -21825,7 +21869,7 @@
       <c r="AA705" s="1"/>
       <c r="AB705" s="1"/>
     </row>
-    <row r="706">
+    <row r="706" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A706" s="1"/>
       <c r="B706" s="1"/>
       <c r="C706" s="7"/>
@@ -21855,7 +21899,7 @@
       <c r="AA706" s="1"/>
       <c r="AB706" s="1"/>
     </row>
-    <row r="707">
+    <row r="707" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A707" s="1"/>
       <c r="B707" s="1"/>
       <c r="C707" s="7"/>
@@ -21885,7 +21929,7 @@
       <c r="AA707" s="1"/>
       <c r="AB707" s="1"/>
     </row>
-    <row r="708">
+    <row r="708" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A708" s="1"/>
       <c r="B708" s="1"/>
       <c r="C708" s="7"/>
@@ -21915,7 +21959,7 @@
       <c r="AA708" s="1"/>
       <c r="AB708" s="1"/>
     </row>
-    <row r="709">
+    <row r="709" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A709" s="1"/>
       <c r="B709" s="1"/>
       <c r="C709" s="7"/>
@@ -21945,7 +21989,7 @@
       <c r="AA709" s="1"/>
       <c r="AB709" s="1"/>
     </row>
-    <row r="710">
+    <row r="710" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A710" s="1"/>
       <c r="B710" s="1"/>
       <c r="C710" s="7"/>
@@ -21975,7 +22019,7 @@
       <c r="AA710" s="1"/>
       <c r="AB710" s="1"/>
     </row>
-    <row r="711">
+    <row r="711" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A711" s="1"/>
       <c r="B711" s="1"/>
       <c r="C711" s="7"/>
@@ -22005,7 +22049,7 @@
       <c r="AA711" s="1"/>
       <c r="AB711" s="1"/>
     </row>
-    <row r="712">
+    <row r="712" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A712" s="1"/>
       <c r="B712" s="1"/>
       <c r="C712" s="7"/>
@@ -22035,7 +22079,7 @@
       <c r="AA712" s="1"/>
       <c r="AB712" s="1"/>
     </row>
-    <row r="713">
+    <row r="713" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A713" s="1"/>
       <c r="B713" s="1"/>
       <c r="C713" s="7"/>
@@ -22065,7 +22109,7 @@
       <c r="AA713" s="1"/>
       <c r="AB713" s="1"/>
     </row>
-    <row r="714">
+    <row r="714" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A714" s="1"/>
       <c r="B714" s="1"/>
       <c r="C714" s="7"/>
@@ -22095,7 +22139,7 @@
       <c r="AA714" s="1"/>
       <c r="AB714" s="1"/>
     </row>
-    <row r="715">
+    <row r="715" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A715" s="1"/>
       <c r="B715" s="1"/>
       <c r="C715" s="7"/>
@@ -22125,7 +22169,7 @@
       <c r="AA715" s="1"/>
       <c r="AB715" s="1"/>
     </row>
-    <row r="716">
+    <row r="716" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A716" s="1"/>
       <c r="B716" s="1"/>
       <c r="C716" s="7"/>
@@ -22155,7 +22199,7 @@
       <c r="AA716" s="1"/>
       <c r="AB716" s="1"/>
     </row>
-    <row r="717">
+    <row r="717" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A717" s="1"/>
       <c r="B717" s="1"/>
       <c r="C717" s="7"/>
@@ -22185,7 +22229,7 @@
       <c r="AA717" s="1"/>
       <c r="AB717" s="1"/>
     </row>
-    <row r="718">
+    <row r="718" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A718" s="1"/>
       <c r="B718" s="1"/>
       <c r="C718" s="7"/>
@@ -22215,7 +22259,7 @@
       <c r="AA718" s="1"/>
       <c r="AB718" s="1"/>
     </row>
-    <row r="719">
+    <row r="719" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A719" s="1"/>
       <c r="B719" s="1"/>
       <c r="C719" s="7"/>
@@ -22245,7 +22289,7 @@
       <c r="AA719" s="1"/>
       <c r="AB719" s="1"/>
     </row>
-    <row r="720">
+    <row r="720" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A720" s="1"/>
       <c r="B720" s="1"/>
       <c r="C720" s="7"/>
@@ -22275,7 +22319,7 @@
       <c r="AA720" s="1"/>
       <c r="AB720" s="1"/>
     </row>
-    <row r="721">
+    <row r="721" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A721" s="1"/>
       <c r="B721" s="1"/>
       <c r="C721" s="7"/>
@@ -22305,7 +22349,7 @@
       <c r="AA721" s="1"/>
       <c r="AB721" s="1"/>
     </row>
-    <row r="722">
+    <row r="722" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A722" s="1"/>
       <c r="B722" s="1"/>
       <c r="C722" s="7"/>
@@ -22335,7 +22379,7 @@
       <c r="AA722" s="1"/>
       <c r="AB722" s="1"/>
     </row>
-    <row r="723">
+    <row r="723" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A723" s="1"/>
       <c r="B723" s="1"/>
       <c r="C723" s="7"/>
@@ -22365,7 +22409,7 @@
       <c r="AA723" s="1"/>
       <c r="AB723" s="1"/>
     </row>
-    <row r="724">
+    <row r="724" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A724" s="1"/>
       <c r="B724" s="1"/>
       <c r="C724" s="7"/>
@@ -22395,7 +22439,7 @@
       <c r="AA724" s="1"/>
       <c r="AB724" s="1"/>
     </row>
-    <row r="725">
+    <row r="725" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A725" s="1"/>
       <c r="B725" s="1"/>
       <c r="C725" s="7"/>
@@ -22425,7 +22469,7 @@
       <c r="AA725" s="1"/>
       <c r="AB725" s="1"/>
     </row>
-    <row r="726">
+    <row r="726" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A726" s="1"/>
       <c r="B726" s="1"/>
       <c r="C726" s="7"/>
@@ -22455,7 +22499,7 @@
       <c r="AA726" s="1"/>
       <c r="AB726" s="1"/>
     </row>
-    <row r="727">
+    <row r="727" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A727" s="1"/>
       <c r="B727" s="1"/>
       <c r="C727" s="7"/>
@@ -22485,7 +22529,7 @@
       <c r="AA727" s="1"/>
       <c r="AB727" s="1"/>
     </row>
-    <row r="728">
+    <row r="728" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A728" s="1"/>
       <c r="B728" s="1"/>
       <c r="C728" s="7"/>
@@ -22515,7 +22559,7 @@
       <c r="AA728" s="1"/>
       <c r="AB728" s="1"/>
     </row>
-    <row r="729">
+    <row r="729" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A729" s="1"/>
       <c r="B729" s="1"/>
       <c r="C729" s="7"/>
@@ -22545,7 +22589,7 @@
       <c r="AA729" s="1"/>
       <c r="AB729" s="1"/>
     </row>
-    <row r="730">
+    <row r="730" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A730" s="1"/>
       <c r="B730" s="1"/>
       <c r="C730" s="7"/>
@@ -22575,7 +22619,7 @@
       <c r="AA730" s="1"/>
       <c r="AB730" s="1"/>
     </row>
-    <row r="731">
+    <row r="731" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A731" s="1"/>
       <c r="B731" s="1"/>
       <c r="C731" s="7"/>
@@ -22605,7 +22649,7 @@
       <c r="AA731" s="1"/>
       <c r="AB731" s="1"/>
     </row>
-    <row r="732">
+    <row r="732" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A732" s="1"/>
       <c r="B732" s="1"/>
       <c r="C732" s="7"/>
@@ -22635,7 +22679,7 @@
       <c r="AA732" s="1"/>
       <c r="AB732" s="1"/>
     </row>
-    <row r="733">
+    <row r="733" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A733" s="1"/>
       <c r="B733" s="1"/>
       <c r="C733" s="7"/>
@@ -22665,7 +22709,7 @@
       <c r="AA733" s="1"/>
       <c r="AB733" s="1"/>
     </row>
-    <row r="734">
+    <row r="734" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A734" s="1"/>
       <c r="B734" s="1"/>
       <c r="C734" s="7"/>
@@ -22695,7 +22739,7 @@
       <c r="AA734" s="1"/>
       <c r="AB734" s="1"/>
     </row>
-    <row r="735">
+    <row r="735" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A735" s="1"/>
       <c r="B735" s="1"/>
       <c r="C735" s="7"/>
@@ -22725,7 +22769,7 @@
       <c r="AA735" s="1"/>
       <c r="AB735" s="1"/>
     </row>
-    <row r="736">
+    <row r="736" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A736" s="1"/>
       <c r="B736" s="1"/>
       <c r="C736" s="7"/>
@@ -22755,7 +22799,7 @@
       <c r="AA736" s="1"/>
       <c r="AB736" s="1"/>
     </row>
-    <row r="737">
+    <row r="737" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A737" s="1"/>
       <c r="B737" s="1"/>
       <c r="C737" s="7"/>
@@ -22785,7 +22829,7 @@
       <c r="AA737" s="1"/>
       <c r="AB737" s="1"/>
     </row>
-    <row r="738">
+    <row r="738" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A738" s="1"/>
       <c r="B738" s="1"/>
       <c r="C738" s="7"/>
@@ -22815,7 +22859,7 @@
       <c r="AA738" s="1"/>
       <c r="AB738" s="1"/>
     </row>
-    <row r="739">
+    <row r="739" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A739" s="1"/>
       <c r="B739" s="1"/>
       <c r="C739" s="7"/>
@@ -22845,7 +22889,7 @@
       <c r="AA739" s="1"/>
       <c r="AB739" s="1"/>
     </row>
-    <row r="740">
+    <row r="740" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A740" s="1"/>
       <c r="B740" s="1"/>
       <c r="C740" s="7"/>
@@ -22875,7 +22919,7 @@
       <c r="AA740" s="1"/>
       <c r="AB740" s="1"/>
     </row>
-    <row r="741">
+    <row r="741" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A741" s="1"/>
       <c r="B741" s="1"/>
       <c r="C741" s="7"/>
@@ -22905,7 +22949,7 @@
       <c r="AA741" s="1"/>
       <c r="AB741" s="1"/>
     </row>
-    <row r="742">
+    <row r="742" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A742" s="1"/>
       <c r="B742" s="1"/>
       <c r="C742" s="7"/>
@@ -22935,7 +22979,7 @@
       <c r="AA742" s="1"/>
       <c r="AB742" s="1"/>
     </row>
-    <row r="743">
+    <row r="743" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A743" s="1"/>
       <c r="B743" s="1"/>
       <c r="C743" s="7"/>
@@ -22965,7 +23009,7 @@
       <c r="AA743" s="1"/>
       <c r="AB743" s="1"/>
     </row>
-    <row r="744">
+    <row r="744" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A744" s="1"/>
       <c r="B744" s="1"/>
       <c r="C744" s="7"/>
@@ -22995,7 +23039,7 @@
       <c r="AA744" s="1"/>
       <c r="AB744" s="1"/>
     </row>
-    <row r="745">
+    <row r="745" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A745" s="1"/>
       <c r="B745" s="1"/>
       <c r="C745" s="7"/>
@@ -23025,7 +23069,7 @@
       <c r="AA745" s="1"/>
       <c r="AB745" s="1"/>
     </row>
-    <row r="746">
+    <row r="746" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A746" s="1"/>
       <c r="B746" s="1"/>
       <c r="C746" s="7"/>
@@ -23055,7 +23099,7 @@
       <c r="AA746" s="1"/>
       <c r="AB746" s="1"/>
     </row>
-    <row r="747">
+    <row r="747" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A747" s="1"/>
       <c r="B747" s="1"/>
       <c r="C747" s="7"/>
@@ -23085,7 +23129,7 @@
       <c r="AA747" s="1"/>
       <c r="AB747" s="1"/>
     </row>
-    <row r="748">
+    <row r="748" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A748" s="1"/>
       <c r="B748" s="1"/>
       <c r="C748" s="7"/>
@@ -23115,7 +23159,7 @@
       <c r="AA748" s="1"/>
       <c r="AB748" s="1"/>
     </row>
-    <row r="749">
+    <row r="749" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A749" s="1"/>
       <c r="B749" s="1"/>
       <c r="C749" s="7"/>
@@ -23145,7 +23189,7 @@
       <c r="AA749" s="1"/>
       <c r="AB749" s="1"/>
     </row>
-    <row r="750">
+    <row r="750" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A750" s="1"/>
       <c r="B750" s="1"/>
       <c r="C750" s="7"/>
@@ -23175,7 +23219,7 @@
       <c r="AA750" s="1"/>
       <c r="AB750" s="1"/>
     </row>
-    <row r="751">
+    <row r="751" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A751" s="1"/>
       <c r="B751" s="1"/>
       <c r="C751" s="7"/>
@@ -23205,7 +23249,7 @@
       <c r="AA751" s="1"/>
       <c r="AB751" s="1"/>
     </row>
-    <row r="752">
+    <row r="752" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A752" s="1"/>
       <c r="B752" s="1"/>
       <c r="C752" s="7"/>
@@ -23235,7 +23279,7 @@
       <c r="AA752" s="1"/>
       <c r="AB752" s="1"/>
     </row>
-    <row r="753">
+    <row r="753" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A753" s="1"/>
       <c r="B753" s="1"/>
       <c r="C753" s="7"/>
@@ -23265,7 +23309,7 @@
       <c r="AA753" s="1"/>
       <c r="AB753" s="1"/>
     </row>
-    <row r="754">
+    <row r="754" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A754" s="1"/>
       <c r="B754" s="1"/>
       <c r="C754" s="7"/>
@@ -23295,7 +23339,7 @@
       <c r="AA754" s="1"/>
       <c r="AB754" s="1"/>
     </row>
-    <row r="755">
+    <row r="755" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A755" s="1"/>
       <c r="B755" s="1"/>
       <c r="C755" s="7"/>
@@ -23325,7 +23369,7 @@
       <c r="AA755" s="1"/>
       <c r="AB755" s="1"/>
     </row>
-    <row r="756">
+    <row r="756" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A756" s="1"/>
       <c r="B756" s="1"/>
       <c r="C756" s="7"/>
@@ -23355,7 +23399,7 @@
       <c r="AA756" s="1"/>
       <c r="AB756" s="1"/>
     </row>
-    <row r="757">
+    <row r="757" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A757" s="1"/>
       <c r="B757" s="1"/>
       <c r="C757" s="7"/>
@@ -23385,7 +23429,7 @@
       <c r="AA757" s="1"/>
       <c r="AB757" s="1"/>
     </row>
-    <row r="758">
+    <row r="758" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A758" s="1"/>
       <c r="B758" s="1"/>
       <c r="C758" s="7"/>
@@ -23415,7 +23459,7 @@
       <c r="AA758" s="1"/>
       <c r="AB758" s="1"/>
     </row>
-    <row r="759">
+    <row r="759" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A759" s="1"/>
       <c r="B759" s="1"/>
       <c r="C759" s="7"/>
@@ -23445,7 +23489,7 @@
       <c r="AA759" s="1"/>
       <c r="AB759" s="1"/>
     </row>
-    <row r="760">
+    <row r="760" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A760" s="1"/>
       <c r="B760" s="1"/>
       <c r="C760" s="7"/>
@@ -23475,7 +23519,7 @@
       <c r="AA760" s="1"/>
       <c r="AB760" s="1"/>
     </row>
-    <row r="761">
+    <row r="761" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A761" s="1"/>
       <c r="B761" s="1"/>
       <c r="C761" s="7"/>
@@ -23505,7 +23549,7 @@
       <c r="AA761" s="1"/>
       <c r="AB761" s="1"/>
     </row>
-    <row r="762">
+    <row r="762" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A762" s="1"/>
       <c r="B762" s="1"/>
       <c r="C762" s="7"/>
@@ -23535,7 +23579,7 @@
       <c r="AA762" s="1"/>
       <c r="AB762" s="1"/>
     </row>
-    <row r="763">
+    <row r="763" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A763" s="1"/>
       <c r="B763" s="1"/>
       <c r="C763" s="7"/>
@@ -23565,7 +23609,7 @@
       <c r="AA763" s="1"/>
       <c r="AB763" s="1"/>
     </row>
-    <row r="764">
+    <row r="764" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A764" s="1"/>
       <c r="B764" s="1"/>
       <c r="C764" s="7"/>
@@ -23595,7 +23639,7 @@
       <c r="AA764" s="1"/>
       <c r="AB764" s="1"/>
     </row>
-    <row r="765">
+    <row r="765" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A765" s="1"/>
       <c r="B765" s="1"/>
       <c r="C765" s="7"/>
@@ -23625,7 +23669,7 @@
       <c r="AA765" s="1"/>
       <c r="AB765" s="1"/>
     </row>
-    <row r="766">
+    <row r="766" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A766" s="1"/>
       <c r="B766" s="1"/>
       <c r="C766" s="7"/>
@@ -23655,7 +23699,7 @@
       <c r="AA766" s="1"/>
       <c r="AB766" s="1"/>
     </row>
-    <row r="767">
+    <row r="767" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A767" s="1"/>
       <c r="B767" s="1"/>
       <c r="C767" s="7"/>
@@ -23685,7 +23729,7 @@
       <c r="AA767" s="1"/>
       <c r="AB767" s="1"/>
     </row>
-    <row r="768">
+    <row r="768" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A768" s="1"/>
       <c r="B768" s="1"/>
       <c r="C768" s="7"/>
@@ -23715,7 +23759,7 @@
       <c r="AA768" s="1"/>
       <c r="AB768" s="1"/>
     </row>
-    <row r="769">
+    <row r="769" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A769" s="1"/>
       <c r="B769" s="1"/>
       <c r="C769" s="7"/>
@@ -23745,7 +23789,7 @@
       <c r="AA769" s="1"/>
       <c r="AB769" s="1"/>
     </row>
-    <row r="770">
+    <row r="770" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A770" s="1"/>
       <c r="B770" s="1"/>
       <c r="C770" s="7"/>
@@ -23775,7 +23819,7 @@
       <c r="AA770" s="1"/>
       <c r="AB770" s="1"/>
     </row>
-    <row r="771">
+    <row r="771" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A771" s="1"/>
       <c r="B771" s="1"/>
       <c r="C771" s="7"/>
@@ -23805,7 +23849,7 @@
       <c r="AA771" s="1"/>
       <c r="AB771" s="1"/>
     </row>
-    <row r="772">
+    <row r="772" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A772" s="1"/>
       <c r="B772" s="1"/>
       <c r="C772" s="7"/>
@@ -23835,7 +23879,7 @@
       <c r="AA772" s="1"/>
       <c r="AB772" s="1"/>
     </row>
-    <row r="773">
+    <row r="773" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A773" s="1"/>
       <c r="B773" s="1"/>
       <c r="C773" s="7"/>
@@ -23865,7 +23909,7 @@
       <c r="AA773" s="1"/>
       <c r="AB773" s="1"/>
     </row>
-    <row r="774">
+    <row r="774" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A774" s="1"/>
       <c r="B774" s="1"/>
       <c r="C774" s="7"/>
@@ -23895,7 +23939,7 @@
       <c r="AA774" s="1"/>
       <c r="AB774" s="1"/>
     </row>
-    <row r="775">
+    <row r="775" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A775" s="1"/>
       <c r="B775" s="1"/>
       <c r="C775" s="7"/>
@@ -23925,7 +23969,7 @@
       <c r="AA775" s="1"/>
       <c r="AB775" s="1"/>
     </row>
-    <row r="776">
+    <row r="776" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A776" s="1"/>
       <c r="B776" s="1"/>
       <c r="C776" s="7"/>
@@ -23955,7 +23999,7 @@
       <c r="AA776" s="1"/>
       <c r="AB776" s="1"/>
     </row>
-    <row r="777">
+    <row r="777" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A777" s="1"/>
       <c r="B777" s="1"/>
       <c r="C777" s="7"/>
@@ -23985,7 +24029,7 @@
       <c r="AA777" s="1"/>
       <c r="AB777" s="1"/>
     </row>
-    <row r="778">
+    <row r="778" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A778" s="1"/>
       <c r="B778" s="1"/>
       <c r="C778" s="7"/>
@@ -24015,7 +24059,7 @@
       <c r="AA778" s="1"/>
       <c r="AB778" s="1"/>
     </row>
-    <row r="779">
+    <row r="779" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A779" s="1"/>
       <c r="B779" s="1"/>
       <c r="C779" s="7"/>
@@ -24045,7 +24089,7 @@
       <c r="AA779" s="1"/>
       <c r="AB779" s="1"/>
     </row>
-    <row r="780">
+    <row r="780" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A780" s="1"/>
       <c r="B780" s="1"/>
       <c r="C780" s="7"/>
@@ -24075,7 +24119,7 @@
       <c r="AA780" s="1"/>
       <c r="AB780" s="1"/>
     </row>
-    <row r="781">
+    <row r="781" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A781" s="1"/>
       <c r="B781" s="1"/>
       <c r="C781" s="7"/>
@@ -24105,7 +24149,7 @@
       <c r="AA781" s="1"/>
       <c r="AB781" s="1"/>
     </row>
-    <row r="782">
+    <row r="782" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A782" s="1"/>
       <c r="B782" s="1"/>
       <c r="C782" s="7"/>
@@ -24135,7 +24179,7 @@
       <c r="AA782" s="1"/>
       <c r="AB782" s="1"/>
     </row>
-    <row r="783">
+    <row r="783" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A783" s="1"/>
       <c r="B783" s="1"/>
       <c r="C783" s="7"/>
@@ -24165,7 +24209,7 @@
       <c r="AA783" s="1"/>
       <c r="AB783" s="1"/>
     </row>
-    <row r="784">
+    <row r="784" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A784" s="1"/>
       <c r="B784" s="1"/>
       <c r="C784" s="7"/>
@@ -24195,7 +24239,7 @@
       <c r="AA784" s="1"/>
       <c r="AB784" s="1"/>
     </row>
-    <row r="785">
+    <row r="785" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A785" s="1"/>
       <c r="B785" s="1"/>
       <c r="C785" s="7"/>
@@ -24225,7 +24269,7 @@
       <c r="AA785" s="1"/>
       <c r="AB785" s="1"/>
     </row>
-    <row r="786">
+    <row r="786" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A786" s="1"/>
       <c r="B786" s="1"/>
       <c r="C786" s="7"/>
@@ -24255,7 +24299,7 @@
       <c r="AA786" s="1"/>
       <c r="AB786" s="1"/>
     </row>
-    <row r="787">
+    <row r="787" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A787" s="1"/>
       <c r="B787" s="1"/>
       <c r="C787" s="7"/>
@@ -24285,7 +24329,7 @@
       <c r="AA787" s="1"/>
       <c r="AB787" s="1"/>
     </row>
-    <row r="788">
+    <row r="788" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A788" s="1"/>
       <c r="B788" s="1"/>
       <c r="C788" s="7"/>
@@ -24315,7 +24359,7 @@
       <c r="AA788" s="1"/>
       <c r="AB788" s="1"/>
     </row>
-    <row r="789">
+    <row r="789" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A789" s="1"/>
       <c r="B789" s="1"/>
       <c r="C789" s="7"/>
@@ -24345,7 +24389,7 @@
       <c r="AA789" s="1"/>
       <c r="AB789" s="1"/>
     </row>
-    <row r="790">
+    <row r="790" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A790" s="1"/>
       <c r="B790" s="1"/>
       <c r="C790" s="7"/>
@@ -24375,7 +24419,7 @@
       <c r="AA790" s="1"/>
       <c r="AB790" s="1"/>
     </row>
-    <row r="791">
+    <row r="791" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A791" s="1"/>
       <c r="B791" s="1"/>
       <c r="C791" s="7"/>
@@ -24405,7 +24449,7 @@
       <c r="AA791" s="1"/>
       <c r="AB791" s="1"/>
     </row>
-    <row r="792">
+    <row r="792" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A792" s="1"/>
       <c r="B792" s="1"/>
       <c r="C792" s="7"/>
@@ -24435,7 +24479,7 @@
       <c r="AA792" s="1"/>
       <c r="AB792" s="1"/>
     </row>
-    <row r="793">
+    <row r="793" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A793" s="1"/>
       <c r="B793" s="1"/>
       <c r="C793" s="7"/>
@@ -24465,7 +24509,7 @@
       <c r="AA793" s="1"/>
       <c r="AB793" s="1"/>
     </row>
-    <row r="794">
+    <row r="794" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A794" s="1"/>
       <c r="B794" s="1"/>
       <c r="C794" s="7"/>
@@ -24495,7 +24539,7 @@
       <c r="AA794" s="1"/>
       <c r="AB794" s="1"/>
     </row>
-    <row r="795">
+    <row r="795" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A795" s="1"/>
       <c r="B795" s="1"/>
       <c r="C795" s="7"/>
@@ -24525,7 +24569,7 @@
       <c r="AA795" s="1"/>
       <c r="AB795" s="1"/>
     </row>
-    <row r="796">
+    <row r="796" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A796" s="1"/>
       <c r="B796" s="1"/>
       <c r="C796" s="7"/>
@@ -24555,7 +24599,7 @@
       <c r="AA796" s="1"/>
       <c r="AB796" s="1"/>
     </row>
-    <row r="797">
+    <row r="797" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A797" s="1"/>
       <c r="B797" s="1"/>
       <c r="C797" s="7"/>
@@ -24585,7 +24629,7 @@
       <c r="AA797" s="1"/>
       <c r="AB797" s="1"/>
     </row>
-    <row r="798">
+    <row r="798" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A798" s="1"/>
       <c r="B798" s="1"/>
       <c r="C798" s="7"/>
@@ -24615,7 +24659,7 @@
       <c r="AA798" s="1"/>
       <c r="AB798" s="1"/>
     </row>
-    <row r="799">
+    <row r="799" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A799" s="1"/>
       <c r="B799" s="1"/>
       <c r="C799" s="7"/>
@@ -24645,7 +24689,7 @@
       <c r="AA799" s="1"/>
       <c r="AB799" s="1"/>
     </row>
-    <row r="800">
+    <row r="800" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A800" s="1"/>
       <c r="B800" s="1"/>
       <c r="C800" s="7"/>
@@ -24675,7 +24719,7 @@
       <c r="AA800" s="1"/>
       <c r="AB800" s="1"/>
     </row>
-    <row r="801">
+    <row r="801" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A801" s="1"/>
       <c r="B801" s="1"/>
       <c r="C801" s="7"/>
@@ -24705,7 +24749,7 @@
       <c r="AA801" s="1"/>
       <c r="AB801" s="1"/>
     </row>
-    <row r="802">
+    <row r="802" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A802" s="1"/>
       <c r="B802" s="1"/>
       <c r="C802" s="7"/>
@@ -24735,7 +24779,7 @@
       <c r="AA802" s="1"/>
       <c r="AB802" s="1"/>
     </row>
-    <row r="803">
+    <row r="803" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A803" s="1"/>
       <c r="B803" s="1"/>
       <c r="C803" s="7"/>
@@ -24765,7 +24809,7 @@
       <c r="AA803" s="1"/>
       <c r="AB803" s="1"/>
     </row>
-    <row r="804">
+    <row r="804" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A804" s="1"/>
       <c r="B804" s="1"/>
       <c r="C804" s="7"/>
@@ -24795,7 +24839,7 @@
       <c r="AA804" s="1"/>
       <c r="AB804" s="1"/>
     </row>
-    <row r="805">
+    <row r="805" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A805" s="1"/>
       <c r="B805" s="1"/>
       <c r="C805" s="7"/>
@@ -24825,7 +24869,7 @@
       <c r="AA805" s="1"/>
       <c r="AB805" s="1"/>
     </row>
-    <row r="806">
+    <row r="806" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A806" s="1"/>
       <c r="B806" s="1"/>
       <c r="C806" s="7"/>
@@ -24855,7 +24899,7 @@
       <c r="AA806" s="1"/>
       <c r="AB806" s="1"/>
     </row>
-    <row r="807">
+    <row r="807" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A807" s="1"/>
       <c r="B807" s="1"/>
       <c r="C807" s="7"/>
@@ -24885,7 +24929,7 @@
       <c r="AA807" s="1"/>
       <c r="AB807" s="1"/>
     </row>
-    <row r="808">
+    <row r="808" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A808" s="1"/>
       <c r="B808" s="1"/>
       <c r="C808" s="7"/>
@@ -24915,7 +24959,7 @@
       <c r="AA808" s="1"/>
       <c r="AB808" s="1"/>
     </row>
-    <row r="809">
+    <row r="809" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A809" s="1"/>
       <c r="B809" s="1"/>
       <c r="C809" s="7"/>
@@ -24945,7 +24989,7 @@
       <c r="AA809" s="1"/>
       <c r="AB809" s="1"/>
     </row>
-    <row r="810">
+    <row r="810" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A810" s="1"/>
       <c r="B810" s="1"/>
       <c r="C810" s="7"/>
@@ -24975,7 +25019,7 @@
       <c r="AA810" s="1"/>
       <c r="AB810" s="1"/>
     </row>
-    <row r="811">
+    <row r="811" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A811" s="1"/>
       <c r="B811" s="1"/>
       <c r="C811" s="7"/>
@@ -25005,7 +25049,7 @@
       <c r="AA811" s="1"/>
       <c r="AB811" s="1"/>
     </row>
-    <row r="812">
+    <row r="812" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A812" s="1"/>
       <c r="B812" s="1"/>
       <c r="C812" s="7"/>
@@ -25035,7 +25079,7 @@
       <c r="AA812" s="1"/>
       <c r="AB812" s="1"/>
     </row>
-    <row r="813">
+    <row r="813" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A813" s="1"/>
       <c r="B813" s="1"/>
       <c r="C813" s="7"/>
@@ -25065,7 +25109,7 @@
       <c r="AA813" s="1"/>
       <c r="AB813" s="1"/>
     </row>
-    <row r="814">
+    <row r="814" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A814" s="1"/>
       <c r="B814" s="1"/>
       <c r="C814" s="7"/>
@@ -25095,7 +25139,7 @@
       <c r="AA814" s="1"/>
       <c r="AB814" s="1"/>
     </row>
-    <row r="815">
+    <row r="815" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A815" s="1"/>
       <c r="B815" s="1"/>
       <c r="C815" s="7"/>
@@ -25125,7 +25169,7 @@
       <c r="AA815" s="1"/>
       <c r="AB815" s="1"/>
     </row>
-    <row r="816">
+    <row r="816" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A816" s="1"/>
       <c r="B816" s="1"/>
       <c r="C816" s="7"/>
@@ -25155,7 +25199,7 @@
       <c r="AA816" s="1"/>
       <c r="AB816" s="1"/>
     </row>
-    <row r="817">
+    <row r="817" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A817" s="1"/>
       <c r="B817" s="1"/>
       <c r="C817" s="7"/>
@@ -25185,7 +25229,7 @@
       <c r="AA817" s="1"/>
       <c r="AB817" s="1"/>
     </row>
-    <row r="818">
+    <row r="818" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A818" s="1"/>
       <c r="B818" s="1"/>
       <c r="C818" s="7"/>
@@ -25215,7 +25259,7 @@
       <c r="AA818" s="1"/>
       <c r="AB818" s="1"/>
     </row>
-    <row r="819">
+    <row r="819" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A819" s="1"/>
       <c r="B819" s="1"/>
       <c r="C819" s="7"/>
@@ -25245,7 +25289,7 @@
       <c r="AA819" s="1"/>
       <c r="AB819" s="1"/>
     </row>
-    <row r="820">
+    <row r="820" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A820" s="1"/>
       <c r="B820" s="1"/>
       <c r="C820" s="7"/>
@@ -25275,7 +25319,7 @@
       <c r="AA820" s="1"/>
       <c r="AB820" s="1"/>
     </row>
-    <row r="821">
+    <row r="821" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A821" s="1"/>
       <c r="B821" s="1"/>
       <c r="C821" s="7"/>
@@ -25305,7 +25349,7 @@
       <c r="AA821" s="1"/>
       <c r="AB821" s="1"/>
     </row>
-    <row r="822">
+    <row r="822" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A822" s="1"/>
       <c r="B822" s="1"/>
       <c r="C822" s="7"/>
@@ -25335,7 +25379,7 @@
       <c r="AA822" s="1"/>
       <c r="AB822" s="1"/>
     </row>
-    <row r="823">
+    <row r="823" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A823" s="1"/>
       <c r="B823" s="1"/>
       <c r="C823" s="7"/>
@@ -25365,7 +25409,7 @@
       <c r="AA823" s="1"/>
       <c r="AB823" s="1"/>
     </row>
-    <row r="824">
+    <row r="824" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A824" s="1"/>
       <c r="B824" s="1"/>
       <c r="C824" s="7"/>
@@ -25395,7 +25439,7 @@
       <c r="AA824" s="1"/>
       <c r="AB824" s="1"/>
     </row>
-    <row r="825">
+    <row r="825" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A825" s="1"/>
       <c r="B825" s="1"/>
       <c r="C825" s="7"/>
@@ -25425,7 +25469,7 @@
       <c r="AA825" s="1"/>
       <c r="AB825" s="1"/>
     </row>
-    <row r="826">
+    <row r="826" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A826" s="1"/>
       <c r="B826" s="1"/>
       <c r="C826" s="7"/>
@@ -25455,7 +25499,7 @@
       <c r="AA826" s="1"/>
       <c r="AB826" s="1"/>
     </row>
-    <row r="827">
+    <row r="827" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A827" s="1"/>
       <c r="B827" s="1"/>
       <c r="C827" s="7"/>
@@ -25485,7 +25529,7 @@
       <c r="AA827" s="1"/>
       <c r="AB827" s="1"/>
     </row>
-    <row r="828">
+    <row r="828" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A828" s="1"/>
       <c r="B828" s="1"/>
       <c r="C828" s="7"/>
@@ -25515,7 +25559,7 @@
       <c r="AA828" s="1"/>
       <c r="AB828" s="1"/>
     </row>
-    <row r="829">
+    <row r="829" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A829" s="1"/>
       <c r="B829" s="1"/>
       <c r="C829" s="7"/>
@@ -25545,7 +25589,7 @@
       <c r="AA829" s="1"/>
       <c r="AB829" s="1"/>
     </row>
-    <row r="830">
+    <row r="830" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A830" s="1"/>
       <c r="B830" s="1"/>
       <c r="C830" s="7"/>
@@ -25575,7 +25619,7 @@
       <c r="AA830" s="1"/>
       <c r="AB830" s="1"/>
     </row>
-    <row r="831">
+    <row r="831" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A831" s="1"/>
       <c r="B831" s="1"/>
       <c r="C831" s="7"/>
@@ -25605,7 +25649,7 @@
       <c r="AA831" s="1"/>
       <c r="AB831" s="1"/>
     </row>
-    <row r="832">
+    <row r="832" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A832" s="1"/>
       <c r="B832" s="1"/>
       <c r="C832" s="7"/>
@@ -25635,7 +25679,7 @@
       <c r="AA832" s="1"/>
       <c r="AB832" s="1"/>
     </row>
-    <row r="833">
+    <row r="833" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A833" s="1"/>
       <c r="B833" s="1"/>
       <c r="C833" s="7"/>
@@ -25665,7 +25709,7 @@
       <c r="AA833" s="1"/>
       <c r="AB833" s="1"/>
     </row>
-    <row r="834">
+    <row r="834" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A834" s="1"/>
       <c r="B834" s="1"/>
       <c r="C834" s="7"/>
@@ -25695,7 +25739,7 @@
       <c r="AA834" s="1"/>
       <c r="AB834" s="1"/>
     </row>
-    <row r="835">
+    <row r="835" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A835" s="1"/>
       <c r="B835" s="1"/>
       <c r="C835" s="7"/>
@@ -25725,7 +25769,7 @@
       <c r="AA835" s="1"/>
       <c r="AB835" s="1"/>
     </row>
-    <row r="836">
+    <row r="836" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A836" s="1"/>
       <c r="B836" s="1"/>
       <c r="C836" s="7"/>
@@ -25755,7 +25799,7 @@
       <c r="AA836" s="1"/>
       <c r="AB836" s="1"/>
     </row>
-    <row r="837">
+    <row r="837" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A837" s="1"/>
       <c r="B837" s="1"/>
       <c r="C837" s="7"/>
@@ -25785,7 +25829,7 @@
       <c r="AA837" s="1"/>
       <c r="AB837" s="1"/>
     </row>
-    <row r="838">
+    <row r="838" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A838" s="1"/>
       <c r="B838" s="1"/>
       <c r="C838" s="7"/>
@@ -25815,7 +25859,7 @@
       <c r="AA838" s="1"/>
       <c r="AB838" s="1"/>
     </row>
-    <row r="839">
+    <row r="839" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A839" s="1"/>
       <c r="B839" s="1"/>
       <c r="C839" s="7"/>
@@ -25845,7 +25889,7 @@
       <c r="AA839" s="1"/>
       <c r="AB839" s="1"/>
     </row>
-    <row r="840">
+    <row r="840" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A840" s="1"/>
       <c r="B840" s="1"/>
       <c r="C840" s="7"/>
@@ -25875,7 +25919,7 @@
       <c r="AA840" s="1"/>
       <c r="AB840" s="1"/>
     </row>
-    <row r="841">
+    <row r="841" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A841" s="1"/>
       <c r="B841" s="1"/>
       <c r="C841" s="7"/>
@@ -25905,7 +25949,7 @@
       <c r="AA841" s="1"/>
       <c r="AB841" s="1"/>
     </row>
-    <row r="842">
+    <row r="842" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A842" s="1"/>
       <c r="B842" s="1"/>
       <c r="C842" s="7"/>
@@ -25935,7 +25979,7 @@
       <c r="AA842" s="1"/>
       <c r="AB842" s="1"/>
     </row>
-    <row r="843">
+    <row r="843" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A843" s="1"/>
       <c r="B843" s="1"/>
       <c r="C843" s="7"/>
@@ -25965,7 +26009,7 @@
       <c r="AA843" s="1"/>
       <c r="AB843" s="1"/>
     </row>
-    <row r="844">
+    <row r="844" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A844" s="1"/>
       <c r="B844" s="1"/>
       <c r="C844" s="7"/>
@@ -25995,7 +26039,7 @@
       <c r="AA844" s="1"/>
       <c r="AB844" s="1"/>
     </row>
-    <row r="845">
+    <row r="845" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A845" s="1"/>
       <c r="B845" s="1"/>
       <c r="C845" s="7"/>
@@ -26025,7 +26069,7 @@
       <c r="AA845" s="1"/>
       <c r="AB845" s="1"/>
     </row>
-    <row r="846">
+    <row r="846" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A846" s="1"/>
       <c r="B846" s="1"/>
       <c r="C846" s="7"/>
@@ -26055,7 +26099,7 @@
       <c r="AA846" s="1"/>
       <c r="AB846" s="1"/>
     </row>
-    <row r="847">
+    <row r="847" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A847" s="1"/>
       <c r="B847" s="1"/>
       <c r="C847" s="7"/>
@@ -26085,7 +26129,7 @@
       <c r="AA847" s="1"/>
       <c r="AB847" s="1"/>
     </row>
-    <row r="848">
+    <row r="848" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A848" s="1"/>
       <c r="B848" s="1"/>
       <c r="C848" s="7"/>
@@ -26115,7 +26159,7 @@
       <c r="AA848" s="1"/>
       <c r="AB848" s="1"/>
     </row>
-    <row r="849">
+    <row r="849" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A849" s="1"/>
       <c r="B849" s="1"/>
       <c r="C849" s="7"/>
@@ -26145,7 +26189,7 @@
       <c r="AA849" s="1"/>
       <c r="AB849" s="1"/>
     </row>
-    <row r="850">
+    <row r="850" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A850" s="1"/>
       <c r="B850" s="1"/>
       <c r="C850" s="7"/>
@@ -26175,7 +26219,7 @@
       <c r="AA850" s="1"/>
       <c r="AB850" s="1"/>
     </row>
-    <row r="851">
+    <row r="851" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A851" s="1"/>
       <c r="B851" s="1"/>
       <c r="C851" s="7"/>
@@ -26205,7 +26249,7 @@
       <c r="AA851" s="1"/>
       <c r="AB851" s="1"/>
     </row>
-    <row r="852">
+    <row r="852" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A852" s="1"/>
       <c r="B852" s="1"/>
       <c r="C852" s="7"/>
@@ -26235,7 +26279,7 @@
       <c r="AA852" s="1"/>
       <c r="AB852" s="1"/>
     </row>
-    <row r="853">
+    <row r="853" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A853" s="1"/>
       <c r="B853" s="1"/>
       <c r="C853" s="7"/>
@@ -26265,7 +26309,7 @@
       <c r="AA853" s="1"/>
       <c r="AB853" s="1"/>
     </row>
-    <row r="854">
+    <row r="854" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A854" s="1"/>
       <c r="B854" s="1"/>
       <c r="C854" s="7"/>
@@ -26295,7 +26339,7 @@
       <c r="AA854" s="1"/>
       <c r="AB854" s="1"/>
     </row>
-    <row r="855">
+    <row r="855" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A855" s="1"/>
       <c r="B855" s="1"/>
       <c r="C855" s="7"/>
@@ -26325,7 +26369,7 @@
       <c r="AA855" s="1"/>
       <c r="AB855" s="1"/>
     </row>
-    <row r="856">
+    <row r="856" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A856" s="1"/>
       <c r="B856" s="1"/>
       <c r="C856" s="7"/>
@@ -26355,7 +26399,7 @@
       <c r="AA856" s="1"/>
       <c r="AB856" s="1"/>
     </row>
-    <row r="857">
+    <row r="857" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A857" s="1"/>
       <c r="B857" s="1"/>
       <c r="C857" s="7"/>
@@ -26385,7 +26429,7 @@
       <c r="AA857" s="1"/>
       <c r="AB857" s="1"/>
     </row>
-    <row r="858">
+    <row r="858" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A858" s="1"/>
       <c r="B858" s="1"/>
       <c r="C858" s="7"/>
@@ -26415,7 +26459,7 @@
       <c r="AA858" s="1"/>
       <c r="AB858" s="1"/>
     </row>
-    <row r="859">
+    <row r="859" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A859" s="1"/>
       <c r="B859" s="1"/>
       <c r="C859" s="7"/>
@@ -26445,7 +26489,7 @@
       <c r="AA859" s="1"/>
       <c r="AB859" s="1"/>
     </row>
-    <row r="860">
+    <row r="860" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A860" s="1"/>
       <c r="B860" s="1"/>
       <c r="C860" s="7"/>
@@ -26475,7 +26519,7 @@
       <c r="AA860" s="1"/>
       <c r="AB860" s="1"/>
     </row>
-    <row r="861">
+    <row r="861" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A861" s="1"/>
       <c r="B861" s="1"/>
       <c r="C861" s="7"/>
@@ -26505,7 +26549,7 @@
       <c r="AA861" s="1"/>
       <c r="AB861" s="1"/>
     </row>
-    <row r="862">
+    <row r="862" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A862" s="1"/>
       <c r="B862" s="1"/>
       <c r="C862" s="7"/>
@@ -26535,7 +26579,7 @@
       <c r="AA862" s="1"/>
       <c r="AB862" s="1"/>
     </row>
-    <row r="863">
+    <row r="863" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A863" s="1"/>
       <c r="B863" s="1"/>
       <c r="C863" s="7"/>
@@ -26565,7 +26609,7 @@
       <c r="AA863" s="1"/>
       <c r="AB863" s="1"/>
     </row>
-    <row r="864">
+    <row r="864" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A864" s="1"/>
       <c r="B864" s="1"/>
       <c r="C864" s="7"/>
@@ -26595,7 +26639,7 @@
       <c r="AA864" s="1"/>
       <c r="AB864" s="1"/>
     </row>
-    <row r="865">
+    <row r="865" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A865" s="1"/>
       <c r="B865" s="1"/>
       <c r="C865" s="7"/>
@@ -26625,7 +26669,7 @@
       <c r="AA865" s="1"/>
       <c r="AB865" s="1"/>
     </row>
-    <row r="866">
+    <row r="866" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A866" s="1"/>
       <c r="B866" s="1"/>
       <c r="C866" s="7"/>
@@ -26655,7 +26699,7 @@
       <c r="AA866" s="1"/>
       <c r="AB866" s="1"/>
     </row>
-    <row r="867">
+    <row r="867" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A867" s="1"/>
       <c r="B867" s="1"/>
       <c r="C867" s="7"/>
@@ -26685,7 +26729,7 @@
       <c r="AA867" s="1"/>
       <c r="AB867" s="1"/>
     </row>
-    <row r="868">
+    <row r="868" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A868" s="1"/>
       <c r="B868" s="1"/>
       <c r="C868" s="7"/>
@@ -26715,7 +26759,7 @@
       <c r="AA868" s="1"/>
       <c r="AB868" s="1"/>
     </row>
-    <row r="869">
+    <row r="869" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A869" s="1"/>
       <c r="B869" s="1"/>
       <c r="C869" s="7"/>
@@ -26745,7 +26789,7 @@
       <c r="AA869" s="1"/>
       <c r="AB869" s="1"/>
     </row>
-    <row r="870">
+    <row r="870" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A870" s="1"/>
       <c r="B870" s="1"/>
       <c r="C870" s="7"/>
@@ -26775,7 +26819,7 @@
       <c r="AA870" s="1"/>
       <c r="AB870" s="1"/>
     </row>
-    <row r="871">
+    <row r="871" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A871" s="1"/>
       <c r="B871" s="1"/>
       <c r="C871" s="7"/>
@@ -26805,7 +26849,7 @@
       <c r="AA871" s="1"/>
       <c r="AB871" s="1"/>
     </row>
-    <row r="872">
+    <row r="872" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A872" s="1"/>
       <c r="B872" s="1"/>
       <c r="C872" s="7"/>
@@ -26835,7 +26879,7 @@
       <c r="AA872" s="1"/>
       <c r="AB872" s="1"/>
     </row>
-    <row r="873">
+    <row r="873" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A873" s="1"/>
       <c r="B873" s="1"/>
       <c r="C873" s="7"/>
@@ -26865,7 +26909,7 @@
       <c r="AA873" s="1"/>
       <c r="AB873" s="1"/>
     </row>
-    <row r="874">
+    <row r="874" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A874" s="1"/>
       <c r="B874" s="1"/>
       <c r="C874" s="7"/>
@@ -26895,7 +26939,7 @@
       <c r="AA874" s="1"/>
       <c r="AB874" s="1"/>
     </row>
-    <row r="875">
+    <row r="875" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A875" s="1"/>
       <c r="B875" s="1"/>
       <c r="C875" s="7"/>
@@ -26925,7 +26969,7 @@
       <c r="AA875" s="1"/>
       <c r="AB875" s="1"/>
     </row>
-    <row r="876">
+    <row r="876" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A876" s="1"/>
       <c r="B876" s="1"/>
       <c r="C876" s="7"/>
@@ -26955,7 +26999,7 @@
       <c r="AA876" s="1"/>
       <c r="AB876" s="1"/>
     </row>
-    <row r="877">
+    <row r="877" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A877" s="1"/>
       <c r="B877" s="1"/>
       <c r="C877" s="7"/>
@@ -26985,7 +27029,7 @@
       <c r="AA877" s="1"/>
       <c r="AB877" s="1"/>
     </row>
-    <row r="878">
+    <row r="878" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A878" s="1"/>
       <c r="B878" s="1"/>
       <c r="C878" s="7"/>
@@ -27015,7 +27059,7 @@
       <c r="AA878" s="1"/>
       <c r="AB878" s="1"/>
     </row>
-    <row r="879">
+    <row r="879" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A879" s="1"/>
       <c r="B879" s="1"/>
       <c r="C879" s="7"/>
@@ -27045,7 +27089,7 @@
       <c r="AA879" s="1"/>
       <c r="AB879" s="1"/>
     </row>
-    <row r="880">
+    <row r="880" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A880" s="1"/>
       <c r="B880" s="1"/>
       <c r="C880" s="7"/>
@@ -27075,7 +27119,7 @@
       <c r="AA880" s="1"/>
       <c r="AB880" s="1"/>
     </row>
-    <row r="881">
+    <row r="881" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A881" s="1"/>
       <c r="B881" s="1"/>
       <c r="C881" s="7"/>
@@ -27105,7 +27149,7 @@
       <c r="AA881" s="1"/>
       <c r="AB881" s="1"/>
     </row>
-    <row r="882">
+    <row r="882" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A882" s="1"/>
       <c r="B882" s="1"/>
       <c r="C882" s="7"/>
@@ -27135,7 +27179,7 @@
       <c r="AA882" s="1"/>
       <c r="AB882" s="1"/>
     </row>
-    <row r="883">
+    <row r="883" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A883" s="1"/>
       <c r="B883" s="1"/>
       <c r="C883" s="7"/>
@@ -27165,7 +27209,7 @@
       <c r="AA883" s="1"/>
       <c r="AB883" s="1"/>
     </row>
-    <row r="884">
+    <row r="884" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A884" s="1"/>
       <c r="B884" s="1"/>
       <c r="C884" s="7"/>
@@ -27195,7 +27239,7 @@
       <c r="AA884" s="1"/>
       <c r="AB884" s="1"/>
     </row>
-    <row r="885">
+    <row r="885" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A885" s="1"/>
       <c r="B885" s="1"/>
       <c r="C885" s="7"/>
@@ -27225,7 +27269,7 @@
       <c r="AA885" s="1"/>
       <c r="AB885" s="1"/>
     </row>
-    <row r="886">
+    <row r="886" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A886" s="1"/>
       <c r="B886" s="1"/>
       <c r="C886" s="7"/>
@@ -27255,7 +27299,7 @@
       <c r="AA886" s="1"/>
       <c r="AB886" s="1"/>
     </row>
-    <row r="887">
+    <row r="887" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A887" s="1"/>
       <c r="B887" s="1"/>
       <c r="C887" s="7"/>
@@ -27285,7 +27329,7 @@
       <c r="AA887" s="1"/>
       <c r="AB887" s="1"/>
     </row>
-    <row r="888">
+    <row r="888" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A888" s="1"/>
       <c r="B888" s="1"/>
       <c r="C888" s="7"/>
@@ -27315,7 +27359,7 @@
       <c r="AA888" s="1"/>
       <c r="AB888" s="1"/>
     </row>
-    <row r="889">
+    <row r="889" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A889" s="1"/>
       <c r="B889" s="1"/>
       <c r="C889" s="7"/>
@@ -27345,7 +27389,7 @@
       <c r="AA889" s="1"/>
       <c r="AB889" s="1"/>
     </row>
-    <row r="890">
+    <row r="890" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A890" s="1"/>
       <c r="B890" s="1"/>
       <c r="C890" s="7"/>
@@ -27375,7 +27419,7 @@
       <c r="AA890" s="1"/>
       <c r="AB890" s="1"/>
     </row>
-    <row r="891">
+    <row r="891" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A891" s="1"/>
       <c r="B891" s="1"/>
       <c r="C891" s="7"/>
@@ -27405,7 +27449,7 @@
       <c r="AA891" s="1"/>
       <c r="AB891" s="1"/>
     </row>
-    <row r="892">
+    <row r="892" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A892" s="1"/>
       <c r="B892" s="1"/>
       <c r="C892" s="7"/>
@@ -27435,7 +27479,7 @@
       <c r="AA892" s="1"/>
       <c r="AB892" s="1"/>
     </row>
-    <row r="893">
+    <row r="893" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A893" s="1"/>
       <c r="B893" s="1"/>
       <c r="C893" s="7"/>
@@ -27465,7 +27509,7 @@
       <c r="AA893" s="1"/>
       <c r="AB893" s="1"/>
     </row>
-    <row r="894">
+    <row r="894" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A894" s="1"/>
       <c r="B894" s="1"/>
       <c r="C894" s="7"/>
@@ -27495,7 +27539,7 @@
       <c r="AA894" s="1"/>
       <c r="AB894" s="1"/>
     </row>
-    <row r="895">
+    <row r="895" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A895" s="1"/>
       <c r="B895" s="1"/>
       <c r="C895" s="7"/>
@@ -27525,7 +27569,7 @@
       <c r="AA895" s="1"/>
       <c r="AB895" s="1"/>
     </row>
-    <row r="896">
+    <row r="896" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A896" s="1"/>
       <c r="B896" s="1"/>
       <c r="C896" s="7"/>
@@ -27555,7 +27599,7 @@
       <c r="AA896" s="1"/>
       <c r="AB896" s="1"/>
     </row>
-    <row r="897">
+    <row r="897" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A897" s="1"/>
       <c r="B897" s="1"/>
       <c r="C897" s="7"/>
@@ -27585,7 +27629,7 @@
       <c r="AA897" s="1"/>
       <c r="AB897" s="1"/>
     </row>
-    <row r="898">
+    <row r="898" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A898" s="1"/>
       <c r="B898" s="1"/>
       <c r="C898" s="7"/>
@@ -27615,7 +27659,7 @@
       <c r="AA898" s="1"/>
       <c r="AB898" s="1"/>
     </row>
-    <row r="899">
+    <row r="899" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A899" s="1"/>
       <c r="B899" s="1"/>
       <c r="C899" s="7"/>
@@ -27645,7 +27689,7 @@
       <c r="AA899" s="1"/>
       <c r="AB899" s="1"/>
     </row>
-    <row r="900">
+    <row r="900" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A900" s="1"/>
       <c r="B900" s="1"/>
       <c r="C900" s="7"/>
@@ -27675,7 +27719,7 @@
       <c r="AA900" s="1"/>
       <c r="AB900" s="1"/>
     </row>
-    <row r="901">
+    <row r="901" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A901" s="1"/>
       <c r="B901" s="1"/>
       <c r="C901" s="7"/>
@@ -27705,7 +27749,7 @@
       <c r="AA901" s="1"/>
       <c r="AB901" s="1"/>
     </row>
-    <row r="902">
+    <row r="902" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A902" s="1"/>
       <c r="B902" s="1"/>
       <c r="C902" s="7"/>
@@ -27735,7 +27779,7 @@
       <c r="AA902" s="1"/>
       <c r="AB902" s="1"/>
     </row>
-    <row r="903">
+    <row r="903" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A903" s="1"/>
       <c r="B903" s="1"/>
       <c r="C903" s="7"/>
@@ -27765,7 +27809,7 @@
       <c r="AA903" s="1"/>
       <c r="AB903" s="1"/>
     </row>
-    <row r="904">
+    <row r="904" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A904" s="1"/>
       <c r="B904" s="1"/>
       <c r="C904" s="7"/>
@@ -27795,7 +27839,7 @@
       <c r="AA904" s="1"/>
       <c r="AB904" s="1"/>
     </row>
-    <row r="905">
+    <row r="905" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A905" s="1"/>
       <c r="B905" s="1"/>
       <c r="C905" s="7"/>
@@ -27825,7 +27869,7 @@
       <c r="AA905" s="1"/>
       <c r="AB905" s="1"/>
     </row>
-    <row r="906">
+    <row r="906" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A906" s="1"/>
       <c r="B906" s="1"/>
       <c r="C906" s="7"/>
@@ -27855,7 +27899,7 @@
       <c r="AA906" s="1"/>
       <c r="AB906" s="1"/>
     </row>
-    <row r="907">
+    <row r="907" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A907" s="1"/>
       <c r="B907" s="1"/>
       <c r="C907" s="7"/>
@@ -27885,7 +27929,7 @@
       <c r="AA907" s="1"/>
       <c r="AB907" s="1"/>
     </row>
-    <row r="908">
+    <row r="908" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A908" s="1"/>
       <c r="B908" s="1"/>
       <c r="C908" s="7"/>
@@ -27915,7 +27959,7 @@
       <c r="AA908" s="1"/>
       <c r="AB908" s="1"/>
     </row>
-    <row r="909">
+    <row r="909" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A909" s="1"/>
       <c r="B909" s="1"/>
       <c r="C909" s="7"/>
@@ -27945,7 +27989,7 @@
       <c r="AA909" s="1"/>
       <c r="AB909" s="1"/>
     </row>
-    <row r="910">
+    <row r="910" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A910" s="1"/>
       <c r="B910" s="1"/>
       <c r="C910" s="7"/>
@@ -27975,7 +28019,7 @@
       <c r="AA910" s="1"/>
       <c r="AB910" s="1"/>
     </row>
-    <row r="911">
+    <row r="911" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A911" s="1"/>
       <c r="B911" s="1"/>
       <c r="C911" s="7"/>
@@ -28005,7 +28049,7 @@
       <c r="AA911" s="1"/>
       <c r="AB911" s="1"/>
     </row>
-    <row r="912">
+    <row r="912" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A912" s="1"/>
       <c r="B912" s="1"/>
       <c r="C912" s="7"/>
@@ -28035,7 +28079,7 @@
       <c r="AA912" s="1"/>
       <c r="AB912" s="1"/>
     </row>
-    <row r="913">
+    <row r="913" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A913" s="1"/>
       <c r="B913" s="1"/>
       <c r="C913" s="7"/>
@@ -28065,7 +28109,7 @@
       <c r="AA913" s="1"/>
       <c r="AB913" s="1"/>
     </row>
-    <row r="914">
+    <row r="914" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A914" s="1"/>
       <c r="B914" s="1"/>
       <c r="C914" s="7"/>
@@ -28095,7 +28139,7 @@
       <c r="AA914" s="1"/>
       <c r="AB914" s="1"/>
     </row>
-    <row r="915">
+    <row r="915" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A915" s="1"/>
       <c r="B915" s="1"/>
       <c r="C915" s="7"/>
@@ -28125,7 +28169,7 @@
       <c r="AA915" s="1"/>
       <c r="AB915" s="1"/>
     </row>
-    <row r="916">
+    <row r="916" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A916" s="1"/>
       <c r="B916" s="1"/>
       <c r="C916" s="7"/>
@@ -28155,7 +28199,7 @@
       <c r="AA916" s="1"/>
       <c r="AB916" s="1"/>
     </row>
-    <row r="917">
+    <row r="917" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A917" s="1"/>
       <c r="B917" s="1"/>
       <c r="C917" s="7"/>
@@ -28185,7 +28229,7 @@
       <c r="AA917" s="1"/>
       <c r="AB917" s="1"/>
     </row>
-    <row r="918">
+    <row r="918" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A918" s="1"/>
       <c r="B918" s="1"/>
       <c r="C918" s="7"/>
@@ -28215,7 +28259,7 @@
       <c r="AA918" s="1"/>
       <c r="AB918" s="1"/>
     </row>
-    <row r="919">
+    <row r="919" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A919" s="1"/>
       <c r="B919" s="1"/>
       <c r="C919" s="7"/>
@@ -28245,7 +28289,7 @@
       <c r="AA919" s="1"/>
       <c r="AB919" s="1"/>
     </row>
-    <row r="920">
+    <row r="920" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A920" s="1"/>
       <c r="B920" s="1"/>
       <c r="C920" s="7"/>
@@ -28275,7 +28319,7 @@
       <c r="AA920" s="1"/>
       <c r="AB920" s="1"/>
     </row>
-    <row r="921">
+    <row r="921" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A921" s="1"/>
       <c r="B921" s="1"/>
       <c r="C921" s="7"/>
@@ -28305,7 +28349,7 @@
       <c r="AA921" s="1"/>
       <c r="AB921" s="1"/>
     </row>
-    <row r="922">
+    <row r="922" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A922" s="1"/>
       <c r="B922" s="1"/>
       <c r="C922" s="7"/>
@@ -28335,7 +28379,7 @@
       <c r="AA922" s="1"/>
       <c r="AB922" s="1"/>
     </row>
-    <row r="923">
+    <row r="923" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A923" s="1"/>
       <c r="B923" s="1"/>
       <c r="C923" s="7"/>
@@ -28365,7 +28409,7 @@
       <c r="AA923" s="1"/>
       <c r="AB923" s="1"/>
     </row>
-    <row r="924">
+    <row r="924" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A924" s="1"/>
       <c r="B924" s="1"/>
       <c r="C924" s="7"/>
@@ -28395,7 +28439,7 @@
       <c r="AA924" s="1"/>
       <c r="AB924" s="1"/>
     </row>
-    <row r="925">
+    <row r="925" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A925" s="1"/>
       <c r="B925" s="1"/>
       <c r="C925" s="7"/>
@@ -28425,7 +28469,7 @@
       <c r="AA925" s="1"/>
       <c r="AB925" s="1"/>
     </row>
-    <row r="926">
+    <row r="926" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A926" s="1"/>
       <c r="B926" s="1"/>
       <c r="C926" s="7"/>
@@ -28455,7 +28499,7 @@
       <c r="AA926" s="1"/>
       <c r="AB926" s="1"/>
     </row>
-    <row r="927">
+    <row r="927" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A927" s="1"/>
       <c r="B927" s="1"/>
       <c r="C927" s="7"/>
@@ -28485,7 +28529,7 @@
       <c r="AA927" s="1"/>
       <c r="AB927" s="1"/>
     </row>
-    <row r="928">
+    <row r="928" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A928" s="1"/>
       <c r="B928" s="1"/>
       <c r="C928" s="7"/>
@@ -28515,7 +28559,7 @@
       <c r="AA928" s="1"/>
       <c r="AB928" s="1"/>
     </row>
-    <row r="929">
+    <row r="929" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A929" s="1"/>
       <c r="B929" s="1"/>
       <c r="C929" s="7"/>
@@ -28545,7 +28589,7 @@
       <c r="AA929" s="1"/>
       <c r="AB929" s="1"/>
     </row>
-    <row r="930">
+    <row r="930" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A930" s="1"/>
       <c r="B930" s="1"/>
       <c r="C930" s="7"/>
@@ -28575,7 +28619,7 @@
       <c r="AA930" s="1"/>
       <c r="AB930" s="1"/>
     </row>
-    <row r="931">
+    <row r="931" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A931" s="1"/>
       <c r="B931" s="1"/>
       <c r="C931" s="7"/>
@@ -28605,7 +28649,7 @@
       <c r="AA931" s="1"/>
       <c r="AB931" s="1"/>
     </row>
-    <row r="932">
+    <row r="932" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A932" s="1"/>
       <c r="B932" s="1"/>
       <c r="C932" s="7"/>
@@ -28635,7 +28679,7 @@
       <c r="AA932" s="1"/>
       <c r="AB932" s="1"/>
     </row>
-    <row r="933">
+    <row r="933" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A933" s="1"/>
       <c r="B933" s="1"/>
       <c r="C933" s="7"/>
@@ -28665,7 +28709,7 @@
       <c r="AA933" s="1"/>
       <c r="AB933" s="1"/>
     </row>
-    <row r="934">
+    <row r="934" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A934" s="1"/>
       <c r="B934" s="1"/>
       <c r="C934" s="7"/>
@@ -28695,7 +28739,7 @@
       <c r="AA934" s="1"/>
       <c r="AB934" s="1"/>
     </row>
-    <row r="935">
+    <row r="935" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A935" s="1"/>
       <c r="B935" s="1"/>
       <c r="C935" s="7"/>
@@ -28725,7 +28769,7 @@
       <c r="AA935" s="1"/>
       <c r="AB935" s="1"/>
     </row>
-    <row r="936">
+    <row r="936" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A936" s="1"/>
       <c r="B936" s="1"/>
       <c r="C936" s="7"/>
@@ -28755,7 +28799,7 @@
       <c r="AA936" s="1"/>
       <c r="AB936" s="1"/>
     </row>
-    <row r="937">
+    <row r="937" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A937" s="1"/>
       <c r="B937" s="1"/>
       <c r="C937" s="7"/>
@@ -28785,7 +28829,7 @@
       <c r="AA937" s="1"/>
       <c r="AB937" s="1"/>
     </row>
-    <row r="938">
+    <row r="938" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A938" s="1"/>
       <c r="B938" s="1"/>
       <c r="C938" s="7"/>
@@ -28815,7 +28859,7 @@
       <c r="AA938" s="1"/>
       <c r="AB938" s="1"/>
     </row>
-    <row r="939">
+    <row r="939" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A939" s="1"/>
       <c r="B939" s="1"/>
       <c r="C939" s="7"/>
@@ -28845,7 +28889,7 @@
       <c r="AA939" s="1"/>
       <c r="AB939" s="1"/>
     </row>
-    <row r="940">
+    <row r="940" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A940" s="1"/>
       <c r="B940" s="1"/>
       <c r="C940" s="7"/>
@@ -28875,7 +28919,7 @@
       <c r="AA940" s="1"/>
       <c r="AB940" s="1"/>
     </row>
-    <row r="941">
+    <row r="941" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A941" s="1"/>
       <c r="B941" s="1"/>
       <c r="C941" s="7"/>
@@ -28905,7 +28949,7 @@
       <c r="AA941" s="1"/>
       <c r="AB941" s="1"/>
     </row>
-    <row r="942">
+    <row r="942" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A942" s="1"/>
       <c r="B942" s="1"/>
       <c r="C942" s="7"/>
@@ -28935,7 +28979,7 @@
       <c r="AA942" s="1"/>
       <c r="AB942" s="1"/>
     </row>
-    <row r="943">
+    <row r="943" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A943" s="1"/>
       <c r="B943" s="1"/>
       <c r="C943" s="7"/>
@@ -28965,7 +29009,7 @@
       <c r="AA943" s="1"/>
       <c r="AB943" s="1"/>
     </row>
-    <row r="944">
+    <row r="944" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A944" s="1"/>
       <c r="B944" s="1"/>
       <c r="C944" s="7"/>
@@ -28995,7 +29039,7 @@
       <c r="AA944" s="1"/>
       <c r="AB944" s="1"/>
     </row>
-    <row r="945">
+    <row r="945" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A945" s="1"/>
       <c r="B945" s="1"/>
       <c r="C945" s="7"/>
@@ -29025,7 +29069,7 @@
       <c r="AA945" s="1"/>
       <c r="AB945" s="1"/>
     </row>
-    <row r="946">
+    <row r="946" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A946" s="1"/>
       <c r="B946" s="1"/>
       <c r="C946" s="7"/>
@@ -29055,7 +29099,7 @@
       <c r="AA946" s="1"/>
       <c r="AB946" s="1"/>
     </row>
-    <row r="947">
+    <row r="947" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A947" s="1"/>
       <c r="B947" s="1"/>
       <c r="C947" s="7"/>
@@ -29085,7 +29129,7 @@
       <c r="AA947" s="1"/>
       <c r="AB947" s="1"/>
     </row>
-    <row r="948">
+    <row r="948" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A948" s="1"/>
       <c r="B948" s="1"/>
       <c r="C948" s="7"/>
@@ -29115,7 +29159,7 @@
       <c r="AA948" s="1"/>
       <c r="AB948" s="1"/>
     </row>
-    <row r="949">
+    <row r="949" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A949" s="1"/>
       <c r="B949" s="1"/>
       <c r="C949" s="7"/>
@@ -29145,7 +29189,7 @@
       <c r="AA949" s="1"/>
       <c r="AB949" s="1"/>
     </row>
-    <row r="950">
+    <row r="950" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A950" s="1"/>
       <c r="B950" s="1"/>
       <c r="C950" s="7"/>
@@ -29175,7 +29219,7 @@
       <c r="AA950" s="1"/>
       <c r="AB950" s="1"/>
     </row>
-    <row r="951">
+    <row r="951" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A951" s="1"/>
       <c r="B951" s="1"/>
       <c r="C951" s="7"/>
@@ -29205,7 +29249,7 @@
       <c r="AA951" s="1"/>
       <c r="AB951" s="1"/>
     </row>
-    <row r="952">
+    <row r="952" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A952" s="1"/>
       <c r="B952" s="1"/>
       <c r="C952" s="7"/>
@@ -29235,7 +29279,7 @@
       <c r="AA952" s="1"/>
       <c r="AB952" s="1"/>
     </row>
-    <row r="953">
+    <row r="953" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A953" s="1"/>
       <c r="B953" s="1"/>
       <c r="C953" s="7"/>
@@ -29265,7 +29309,7 @@
       <c r="AA953" s="1"/>
       <c r="AB953" s="1"/>
     </row>
-    <row r="954">
+    <row r="954" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A954" s="1"/>
       <c r="B954" s="1"/>
       <c r="C954" s="7"/>
@@ -29295,7 +29339,7 @@
       <c r="AA954" s="1"/>
       <c r="AB954" s="1"/>
     </row>
-    <row r="955">
+    <row r="955" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A955" s="1"/>
       <c r="B955" s="1"/>
       <c r="C955" s="7"/>
@@ -29325,7 +29369,7 @@
       <c r="AA955" s="1"/>
       <c r="AB955" s="1"/>
     </row>
-    <row r="956">
+    <row r="956" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A956" s="1"/>
       <c r="B956" s="1"/>
       <c r="C956" s="7"/>
@@ -29355,7 +29399,7 @@
       <c r="AA956" s="1"/>
       <c r="AB956" s="1"/>
     </row>
-    <row r="957">
+    <row r="957" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A957" s="1"/>
       <c r="B957" s="1"/>
       <c r="C957" s="7"/>
@@ -29385,7 +29429,7 @@
       <c r="AA957" s="1"/>
       <c r="AB957" s="1"/>
     </row>
-    <row r="958">
+    <row r="958" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A958" s="1"/>
       <c r="B958" s="1"/>
       <c r="C958" s="7"/>
@@ -29415,7 +29459,7 @@
       <c r="AA958" s="1"/>
       <c r="AB958" s="1"/>
     </row>
-    <row r="959">
+    <row r="959" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A959" s="1"/>
       <c r="B959" s="1"/>
       <c r="C959" s="7"/>
@@ -29445,7 +29489,7 @@
       <c r="AA959" s="1"/>
       <c r="AB959" s="1"/>
     </row>
-    <row r="960">
+    <row r="960" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A960" s="1"/>
       <c r="B960" s="1"/>
       <c r="C960" s="7"/>
@@ -29475,7 +29519,7 @@
       <c r="AA960" s="1"/>
       <c r="AB960" s="1"/>
     </row>
-    <row r="961">
+    <row r="961" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A961" s="1"/>
       <c r="B961" s="1"/>
       <c r="C961" s="7"/>
@@ -29505,7 +29549,7 @@
       <c r="AA961" s="1"/>
       <c r="AB961" s="1"/>
     </row>
-    <row r="962">
+    <row r="962" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A962" s="1"/>
       <c r="B962" s="1"/>
       <c r="C962" s="7"/>
@@ -29535,7 +29579,7 @@
       <c r="AA962" s="1"/>
       <c r="AB962" s="1"/>
     </row>
-    <row r="963">
+    <row r="963" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A963" s="1"/>
       <c r="B963" s="1"/>
       <c r="C963" s="7"/>
@@ -29565,7 +29609,7 @@
       <c r="AA963" s="1"/>
       <c r="AB963" s="1"/>
     </row>
-    <row r="964">
+    <row r="964" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A964" s="1"/>
       <c r="B964" s="1"/>
       <c r="C964" s="7"/>
@@ -29595,7 +29639,7 @@
       <c r="AA964" s="1"/>
       <c r="AB964" s="1"/>
     </row>
-    <row r="965">
+    <row r="965" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A965" s="1"/>
       <c r="B965" s="1"/>
       <c r="C965" s="7"/>
@@ -29625,7 +29669,7 @@
       <c r="AA965" s="1"/>
       <c r="AB965" s="1"/>
     </row>
-    <row r="966">
+    <row r="966" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A966" s="1"/>
       <c r="B966" s="1"/>
       <c r="C966" s="7"/>
@@ -29655,7 +29699,7 @@
       <c r="AA966" s="1"/>
       <c r="AB966" s="1"/>
     </row>
-    <row r="967">
+    <row r="967" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A967" s="1"/>
       <c r="B967" s="1"/>
       <c r="C967" s="7"/>
@@ -29685,7 +29729,7 @@
       <c r="AA967" s="1"/>
       <c r="AB967" s="1"/>
     </row>
-    <row r="968">
+    <row r="968" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A968" s="1"/>
       <c r="B968" s="1"/>
       <c r="C968" s="7"/>
@@ -29715,7 +29759,7 @@
       <c r="AA968" s="1"/>
       <c r="AB968" s="1"/>
     </row>
-    <row r="969">
+    <row r="969" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A969" s="1"/>
       <c r="B969" s="1"/>
       <c r="C969" s="7"/>
@@ -29745,7 +29789,7 @@
       <c r="AA969" s="1"/>
       <c r="AB969" s="1"/>
     </row>
-    <row r="970">
+    <row r="970" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A970" s="1"/>
       <c r="B970" s="1"/>
       <c r="C970" s="7"/>
@@ -29775,7 +29819,7 @@
       <c r="AA970" s="1"/>
       <c r="AB970" s="1"/>
     </row>
-    <row r="971">
+    <row r="971" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A971" s="1"/>
       <c r="B971" s="1"/>
       <c r="C971" s="7"/>
@@ -29805,7 +29849,7 @@
       <c r="AA971" s="1"/>
       <c r="AB971" s="1"/>
     </row>
-    <row r="972">
+    <row r="972" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A972" s="1"/>
       <c r="B972" s="1"/>
       <c r="C972" s="7"/>
@@ -29835,7 +29879,7 @@
       <c r="AA972" s="1"/>
       <c r="AB972" s="1"/>
     </row>
-    <row r="973">
+    <row r="973" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A973" s="1"/>
       <c r="B973" s="1"/>
       <c r="C973" s="7"/>
@@ -29865,7 +29909,7 @@
       <c r="AA973" s="1"/>
       <c r="AB973" s="1"/>
     </row>
-    <row r="974">
+    <row r="974" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A974" s="1"/>
       <c r="B974" s="1"/>
       <c r="C974" s="7"/>
@@ -29895,7 +29939,7 @@
       <c r="AA974" s="1"/>
       <c r="AB974" s="1"/>
     </row>
-    <row r="975">
+    <row r="975" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A975" s="1"/>
       <c r="B975" s="1"/>
       <c r="C975" s="7"/>
@@ -29925,7 +29969,7 @@
       <c r="AA975" s="1"/>
       <c r="AB975" s="1"/>
     </row>
-    <row r="976">
+    <row r="976" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A976" s="1"/>
       <c r="B976" s="1"/>
       <c r="C976" s="7"/>
@@ -29955,7 +29999,7 @@
       <c r="AA976" s="1"/>
       <c r="AB976" s="1"/>
     </row>
-    <row r="977">
+    <row r="977" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A977" s="1"/>
       <c r="B977" s="1"/>
       <c r="C977" s="7"/>
@@ -29985,7 +30029,7 @@
       <c r="AA977" s="1"/>
       <c r="AB977" s="1"/>
     </row>
-    <row r="978">
+    <row r="978" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A978" s="1"/>
       <c r="B978" s="1"/>
       <c r="C978" s="7"/>
@@ -30015,7 +30059,7 @@
       <c r="AA978" s="1"/>
       <c r="AB978" s="1"/>
     </row>
-    <row r="979">
+    <row r="979" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A979" s="1"/>
       <c r="B979" s="1"/>
       <c r="C979" s="7"/>
@@ -30045,7 +30089,7 @@
       <c r="AA979" s="1"/>
       <c r="AB979" s="1"/>
     </row>
-    <row r="980">
+    <row r="980" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A980" s="1"/>
       <c r="B980" s="1"/>
       <c r="C980" s="7"/>
@@ -30075,7 +30119,7 @@
       <c r="AA980" s="1"/>
       <c r="AB980" s="1"/>
     </row>
-    <row r="981">
+    <row r="981" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A981" s="1"/>
       <c r="B981" s="1"/>
       <c r="C981" s="7"/>
@@ -30105,7 +30149,7 @@
       <c r="AA981" s="1"/>
       <c r="AB981" s="1"/>
     </row>
-    <row r="982">
+    <row r="982" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A982" s="1"/>
       <c r="B982" s="1"/>
       <c r="C982" s="7"/>
@@ -30135,7 +30179,7 @@
       <c r="AA982" s="1"/>
       <c r="AB982" s="1"/>
     </row>
-    <row r="983">
+    <row r="983" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A983" s="1"/>
       <c r="B983" s="1"/>
       <c r="C983" s="7"/>
@@ -30165,7 +30209,7 @@
       <c r="AA983" s="1"/>
       <c r="AB983" s="1"/>
     </row>
-    <row r="984">
+    <row r="984" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A984" s="1"/>
       <c r="B984" s="1"/>
       <c r="C984" s="7"/>
@@ -30195,7 +30239,7 @@
       <c r="AA984" s="1"/>
       <c r="AB984" s="1"/>
     </row>
-    <row r="985">
+    <row r="985" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A985" s="1"/>
       <c r="B985" s="1"/>
       <c r="C985" s="7"/>
@@ -30225,7 +30269,7 @@
       <c r="AA985" s="1"/>
       <c r="AB985" s="1"/>
     </row>
-    <row r="986">
+    <row r="986" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A986" s="1"/>
       <c r="B986" s="1"/>
       <c r="C986" s="7"/>
@@ -30255,7 +30299,7 @@
       <c r="AA986" s="1"/>
       <c r="AB986" s="1"/>
     </row>
-    <row r="987">
+    <row r="987" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A987" s="1"/>
       <c r="B987" s="1"/>
       <c r="C987" s="7"/>
@@ -30285,7 +30329,7 @@
       <c r="AA987" s="1"/>
       <c r="AB987" s="1"/>
     </row>
-    <row r="988">
+    <row r="988" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A988" s="1"/>
       <c r="B988" s="1"/>
       <c r="C988" s="7"/>
@@ -30315,7 +30359,7 @@
       <c r="AA988" s="1"/>
       <c r="AB988" s="1"/>
     </row>
-    <row r="989">
+    <row r="989" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A989" s="1"/>
       <c r="B989" s="1"/>
       <c r="C989" s="7"/>
@@ -30345,7 +30389,7 @@
       <c r="AA989" s="1"/>
       <c r="AB989" s="1"/>
     </row>
-    <row r="990">
+    <row r="990" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A990" s="1"/>
       <c r="B990" s="1"/>
       <c r="C990" s="7"/>
@@ -30376,12 +30420,8 @@
       <c r="AB990" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="$B$1:$F$29">
-    <sortState ref="B1:F29">
-      <sortCondition ref="C1:C29"/>
-      <sortCondition ref="B1:B29"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="B1:F29" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>